--- a/AAII_Financials/Quarterly/ALL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ALL_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="92">
   <si>
     <t>ALL</t>
   </si>
@@ -656,401 +656,413 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="32" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="6" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="33" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>14832000</v>
+      </c>
+      <c r="E8" s="3">
         <v>14497000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>13979000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>13786000</v>
       </c>
-      <c r="G8" s="3">
-        <v>13647000</v>
-      </c>
       <c r="H8" s="3">
+        <v>13648000</v>
+      </c>
+      <c r="I8" s="3">
         <v>13208000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>12219000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>12336000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>13011000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>12480000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>12646000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>12451000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>10962000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>10678000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>10403000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>9866000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>11476000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>11085000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>11156000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>11006000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>9486000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>10469000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>10103000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>9770000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>9854000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>9686000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>9634000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>9496000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>9350000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>9294000</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1904000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1841000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1789000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1744000</v>
       </c>
-      <c r="G9" s="3">
-        <v>1731000</v>
-      </c>
       <c r="H9" s="3">
+        <v>1725000</v>
+      </c>
+      <c r="I9" s="3">
         <v>1683000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1618000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1608000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1602000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1582000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1545000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1523000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1382000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1386000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1344000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1365000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1382000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1425000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1362000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1364000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1336000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1317000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1296000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1273000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1239000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1200000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1176000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1169000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1157000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1138000</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>12928000</v>
+      </c>
+      <c r="E10" s="3">
         <v>12656000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>12190000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>12042000</v>
       </c>
-      <c r="G10" s="3">
-        <v>11916000</v>
-      </c>
       <c r="H10" s="3">
+        <v>11923000</v>
+      </c>
+      <c r="I10" s="3">
         <v>11525000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>10601000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>10728000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>11409000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>10898000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>11101000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>10928000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>9580000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>9292000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>9059000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>8501000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>10094000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>9660000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>9794000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>9642000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>8150000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>9152000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>8807000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>8497000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>8615000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>8486000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>8458000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>8327000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>8193000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>8156000</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1083,8 +1095,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1175,8 +1188,11 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1267,100 +1283,106 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E14" s="3">
         <v>87000</v>
-      </c>
-      <c r="E14" s="3">
-        <v>27000</v>
       </c>
       <c r="F14" s="3">
         <v>27000</v>
       </c>
       <c r="G14" s="3">
+        <v>27000</v>
+      </c>
+      <c r="H14" s="3">
         <v>24000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>14000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>12000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>25000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>23000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>100000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>73000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>39000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>195000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>750000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>213000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>66000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>16000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>74000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>33000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>15000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>16000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>25000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>18000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>163000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>39000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>88000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>70000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>80000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>77000</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1368,52 +1390,52 @@
         <v>83000</v>
       </c>
       <c r="E15" s="3">
+        <v>83000</v>
+      </c>
+      <c r="F15" s="3">
         <v>82000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>81000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>89000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>90000</v>
-      </c>
-      <c r="I15" s="3">
-        <v>87000</v>
       </c>
       <c r="J15" s="3">
         <v>87000</v>
       </c>
       <c r="K15" s="3">
-        <v>109000</v>
+        <v>87000</v>
       </c>
       <c r="L15" s="3">
         <v>109000</v>
       </c>
       <c r="M15" s="3">
+        <v>109000</v>
+      </c>
+      <c r="N15" s="3">
         <v>105000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>53000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>30000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>31000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>29000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>28000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>30000</v>
-      </c>
-      <c r="T15" s="3">
-        <v>32000</v>
       </c>
       <c r="U15" s="3">
         <v>32000</v>
@@ -1422,19 +1444,19 @@
         <v>32000</v>
       </c>
       <c r="W15" s="3">
+        <v>32000</v>
+      </c>
+      <c r="X15" s="3">
         <v>36000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>24000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>23000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>22000</v>
-      </c>
-      <c r="AA15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AB15" s="3" t="s">
         <v>8</v>
@@ -1442,8 +1464,8 @@
       <c r="AC15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD15" s="3">
-        <v>0</v>
+      <c r="AD15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE15" s="3">
         <v>0</v>
@@ -1451,8 +1473,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1482,192 +1507,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>13005000</v>
+      </c>
+      <c r="E17" s="3">
         <v>14518000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>15727000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>14192000</v>
       </c>
-      <c r="G17" s="3">
-        <v>14067000</v>
-      </c>
       <c r="H17" s="3">
+        <v>14058000</v>
+      </c>
+      <c r="I17" s="3">
         <v>14118000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>13530000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>11535000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>11618000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>12254000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>10849000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>9419000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>8098000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>9150000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>9024000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>8835000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>9245000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>9925000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>10078000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>9386000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>10196000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>9291000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>9206000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>8507000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>8697000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>8715000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>8783000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>8484000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>8092000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>8529000</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1827000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-21000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1748000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-406000</v>
       </c>
-      <c r="G18" s="3">
-        <v>-420000</v>
-      </c>
       <c r="H18" s="3">
+        <v>-410000</v>
+      </c>
+      <c r="I18" s="3">
         <v>-910000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1311000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>801000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1393000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>226000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1797000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3032000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2864000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1528000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1379000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1031000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2231000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1160000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1078000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1620000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-710000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1178000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>897000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1263000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1157000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>971000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>851000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1012000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1258000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>765000</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1700,8 +1732,9 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1792,100 +1825,106 @@
       <c r="AF20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1992000</v>
+      </c>
+      <c r="E21" s="3">
         <v>155000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-1562000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-229000</v>
       </c>
-      <c r="G21" s="3">
-        <v>-219000</v>
-      </c>
       <c r="H21" s="3">
+        <v>-209000</v>
+      </c>
+      <c r="I21" s="3">
         <v>-716000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-1095000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1037000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1661000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>473000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2108000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3292000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3050000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1710000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1542000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1186000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2402000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1319000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1238000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1777000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-575000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1306000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1023000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1385000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1282000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1091000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>970000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1131000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1355000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>862000</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1976,192 +2015,201 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1827000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-21000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1748000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-406000</v>
       </c>
-      <c r="G23" s="3">
-        <v>-420000</v>
-      </c>
       <c r="H23" s="3">
+        <v>-410000</v>
+      </c>
+      <c r="I23" s="3">
         <v>-910000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1311000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>801000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1393000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>226000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1797000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3032000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2864000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1528000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1379000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1031000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2231000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1160000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1078000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1620000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-710000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1178000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>897000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1263000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1157000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>971000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>851000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1012000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1258000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>765000</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>340000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-17000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-373000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-85000</v>
       </c>
-      <c r="G24" s="3">
-        <v>-117000</v>
-      </c>
       <c r="H24" s="3">
+        <v>-114000</v>
+      </c>
+      <c r="I24" s="3">
         <v>-236000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-289000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>151000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>281000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>20000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>362000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>626000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>594000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>312000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>273000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>194000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>458000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>229000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>227000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>328000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-170000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>230000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>180000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>257000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>414000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>305000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>272000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>317000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>418000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>245000</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2252,192 +2300,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1487000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-4000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1375000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-321000</v>
       </c>
-      <c r="G26" s="3">
-        <v>-303000</v>
-      </c>
       <c r="H26" s="3">
+        <v>-296000</v>
+      </c>
+      <c r="I26" s="3">
         <v>-674000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1022000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>650000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1112000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>206000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1435000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2406000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2270000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1216000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1106000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>837000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1773000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>931000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>851000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1292000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-540000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>948000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>717000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1006000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>743000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>666000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>579000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>695000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>840000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>520000</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1460000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-41000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1389000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-346000</v>
       </c>
-      <c r="G27" s="3">
-        <v>-310000</v>
-      </c>
       <c r="H27" s="3">
+        <v>-303000</v>
+      </c>
+      <c r="I27" s="3">
         <v>-685000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1040000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>634000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1111000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>183000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1399000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2385000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2244000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1189000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1080000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>801000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1707000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>889000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>821000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1261000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-583000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>911000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>678000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>977000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>714000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>637000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>550000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>666000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>811000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>491000</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2528,8 +2585,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2545,8 +2605,8 @@
       <c r="G29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H29" s="3">
-        <v>0</v>
+      <c r="H29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I29" s="3">
         <v>0</v>
@@ -2555,31 +2615,31 @@
         <v>0</v>
       </c>
       <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
         <v>-321000</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>325000</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>196000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-3793000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>354000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-63000</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>144000</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-288000</v>
-      </c>
-      <c r="S29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>8</v>
@@ -2590,23 +2650,23 @@
       <c r="V29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W29" s="3">
+      <c r="W29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X29" s="3">
         <v>-2000</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>31000</v>
-      </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB29" s="3">
         <v>506000</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -2620,8 +2680,11 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2712,8 +2775,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2804,8 +2870,11 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2896,100 +2965,106 @@
       <c r="AF32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1460000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-41000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1389000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-346000</v>
       </c>
-      <c r="G33" s="3">
-        <v>-310000</v>
-      </c>
       <c r="H33" s="3">
+        <v>-303000</v>
+      </c>
+      <c r="I33" s="3">
         <v>-685000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1040000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>634000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>790000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>508000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1595000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1408000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2598000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1126000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1224000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>513000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1707000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>889000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>821000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1261000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-585000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>942000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>678000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>977000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1220000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>637000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>550000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>666000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>811000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>491000</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3080,197 +3155,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1460000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-41000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1389000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-346000</v>
       </c>
-      <c r="G35" s="3">
-        <v>-310000</v>
-      </c>
       <c r="H35" s="3">
+        <v>-303000</v>
+      </c>
+      <c r="I35" s="3">
         <v>-685000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1040000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>634000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>790000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>508000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1595000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1408000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2598000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1126000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1224000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>513000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1707000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>889000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>821000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1261000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-585000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>942000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>678000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>977000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1220000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>637000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>550000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>666000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>811000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>491000</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3303,8 +3387,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3337,100 +3422,104 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>722000</v>
+      </c>
+      <c r="E41" s="3">
         <v>860000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>699000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>662000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>736000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>786000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>766000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1130000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>763000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>690000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>656000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>709000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>377000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>370000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>547000</v>
-      </c>
-      <c r="R41" s="3">
-        <v>338000</v>
       </c>
       <c r="S41" s="3">
         <v>338000</v>
       </c>
       <c r="T41" s="3">
+        <v>338000</v>
+      </c>
+      <c r="U41" s="3">
         <v>587000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>599000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>551000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>499000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>460000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>489000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>450000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>617000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>690000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>482000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>442000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>436000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>389000</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3521,100 +3610,106 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>10044000</v>
+      </c>
+      <c r="E43" s="3">
         <v>10102000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>9713000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>9483000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>9165000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>9150000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>8824000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>8874000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>8364000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>8406000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>8146000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>7921000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>6479000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>6609000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>6367000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>6401000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>6472000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>6558000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>6380000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>6201000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>6154000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>6196000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>5953000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>5856000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>5786000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>5922000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>5693000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>5649000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>5597000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>5799000</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3705,8 +3800,11 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3797,8 +3895,11 @@
       <c r="AF45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3889,192 +3990,201 @@
       <c r="AF46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>66677000</v>
+      </c>
+      <c r="E47" s="3">
         <v>63359000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>63668000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>63475000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>61829000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>61006000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>61055000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>61768000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>64701000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>61840000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>62570000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>60076000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>94237000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>91197000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>89637000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>84783000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>88221000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>89158000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>86345000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>84018000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>81136000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>83855000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>83140000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>83195000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>82677000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>82680000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>81203000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>81050000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>81707000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>81038000</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1022000</v>
+      </c>
+      <c r="E48" s="3">
         <v>909000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>945000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>971000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1221000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1008000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>975000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>966000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1253000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>965000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1026000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1002000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1057000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1076000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1100000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1123000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1628000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1535000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1519000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1521000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1045000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1032000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1040000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1060000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1072000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1067000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1072000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1067000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1065000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1013000</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4094,25 +4204,25 @@
         <v>3502000</v>
       </c>
       <c r="I49" s="3">
+        <v>3502000</v>
+      </c>
+      <c r="J49" s="3">
         <v>3496000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3497000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3502000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3389000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3349000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3350000</v>
-      </c>
-      <c r="O49" s="3">
-        <v>2544000</v>
       </c>
       <c r="P49" s="3">
         <v>2544000</v>
@@ -4124,22 +4234,22 @@
         <v>2544000</v>
       </c>
       <c r="S49" s="3">
-        <v>2545000</v>
+        <v>2544000</v>
       </c>
       <c r="T49" s="3">
         <v>2545000</v>
       </c>
       <c r="U49" s="3">
-        <v>2547000</v>
+        <v>2545000</v>
       </c>
       <c r="V49" s="3">
         <v>2547000</v>
       </c>
       <c r="W49" s="3">
+        <v>2547000</v>
+      </c>
+      <c r="X49" s="3">
         <v>2530000</v>
-      </c>
-      <c r="X49" s="3">
-        <v>2189000</v>
       </c>
       <c r="Y49" s="3">
         <v>2189000</v>
@@ -4148,25 +4258,28 @@
         <v>2189000</v>
       </c>
       <c r="AA49" s="3">
+        <v>2189000</v>
+      </c>
+      <c r="AB49" s="3">
         <v>2181000</v>
-      </c>
-      <c r="AB49" s="3">
-        <v>2309000</v>
       </c>
       <c r="AC49" s="3">
         <v>2309000</v>
       </c>
       <c r="AD49" s="3">
+        <v>2309000</v>
+      </c>
+      <c r="AE49" s="3">
         <v>2295000</v>
-      </c>
-      <c r="AE49" s="3">
-        <v>1219000</v>
       </c>
       <c r="AF49" s="3">
         <v>1219000</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>1219000</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4257,8 +4370,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4349,46 +4465,49 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>219000</v>
+      </c>
+      <c r="E52" s="3">
         <v>816000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>480000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>345000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>382000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>492000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>118000</v>
       </c>
-      <c r="J52" s="3" t="s">
+      <c r="K52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
       <c r="L52" s="3">
+        <v>0</v>
+      </c>
+      <c r="M52" s="3">
         <v>36803000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>36969000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>36829000</v>
-      </c>
-      <c r="O52" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P52" s="3" t="s">
         <v>8</v>
@@ -4405,8 +4524,8 @@
       <c r="T52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U52" s="3">
-        <v>0</v>
+      <c r="U52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V52" s="3">
         <v>0</v>
@@ -4441,8 +4560,11 @@
       <c r="AF52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4533,100 +4655,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>103362000</v>
+      </c>
+      <c r="E54" s="3">
         <v>101176000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>100514000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>99631000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>97989000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>97676000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>96350000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>97150000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>99440000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>133440000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>132643000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>129811000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>125987000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>122750000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>121266000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>116107000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>119950000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>121073000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>118374000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>115834000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>112249000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>114490000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>113369000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>113289000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>112422000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>113632000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>110865000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>110243000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>108610000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>108537000</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4659,8 +4787,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4693,8 +4822,9 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4785,8 +4915,11 @@
       <c r="AF57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4877,100 +5010,106 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>27209000</v>
+      </c>
+      <c r="E59" s="3">
         <v>26711000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>25575000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>24715000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>24843000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>24211000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>23229000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>22429000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>22490000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>21753000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>20853000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>20274000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>49274000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>49140000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>48221000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>46664000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>48503000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>48555000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>48232000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>48055000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>47670000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>48313000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>47936000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>47972000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>48614000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>48542000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>48216000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>48129000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>48185000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>48745000</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5061,100 +5200,106 @@
       <c r="AF60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7942000</v>
+      </c>
+      <c r="E61" s="3">
         <v>7946000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7949000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>8452000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7964000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>7967000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>7970000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>7973000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>7976000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>7980000</v>
-      </c>
-      <c r="M61" s="3">
-        <v>7996000</v>
       </c>
       <c r="N61" s="3">
         <v>7996000</v>
       </c>
       <c r="O61" s="3">
+        <v>7996000</v>
+      </c>
+      <c r="P61" s="3">
         <v>7825000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>6635000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>6634000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>6633000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>6631000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>6630000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>6628000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>6453000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>6451000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>6450000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>6448000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>6847000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>6350000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>6349000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>6348000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>6346000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>6347000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>5110000</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5167,8 +5312,8 @@
       <c r="F62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G62" s="3">
-        <v>0</v>
+      <c r="G62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H62" s="3">
         <v>0</v>
@@ -5177,76 +5322,79 @@
         <v>0</v>
       </c>
       <c r="J62" s="3">
+        <v>0</v>
+      </c>
+      <c r="K62" s="3">
         <v>402000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>833000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>33132000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>33533000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>33876000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1355000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>905000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>842000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>331000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1154000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1079000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>997000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>817000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>425000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>660000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>723000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>725000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>782000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1249000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1104000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>833000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>487000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>935000</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5337,8 +5485,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5429,8 +5580,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5521,100 +5675,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>85592000</v>
+      </c>
+      <c r="E66" s="3">
         <v>86583000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>84997000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>82137000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>80501000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>80003000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>76235000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>73938000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>74261000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>106711000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>104436000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>102992000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>95770000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>95487000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>94280000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>91934000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>93952000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>94933000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>93898000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>92416000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>90937000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>90857000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>90247000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>90012000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>89871000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>91513000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>89364000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>89085000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>88037000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>87603000</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5647,8 +5807,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5739,8 +5900,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5831,8 +5995,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5843,7 +6010,7 @@
         <v>2001000</v>
       </c>
       <c r="F70" s="3">
-        <v>1970000</v>
+        <v>2001000</v>
       </c>
       <c r="G70" s="3">
         <v>1970000</v>
@@ -5864,13 +6031,13 @@
         <v>1970000</v>
       </c>
       <c r="M70" s="3">
-        <v>2170000</v>
+        <v>1970000</v>
       </c>
       <c r="N70" s="3">
         <v>2170000</v>
       </c>
       <c r="O70" s="3">
-        <v>1970000</v>
+        <v>2170000</v>
       </c>
       <c r="P70" s="3">
         <v>1970000</v>
@@ -5882,13 +6049,13 @@
         <v>1970000</v>
       </c>
       <c r="S70" s="3">
+        <v>1970000</v>
+      </c>
+      <c r="T70" s="3">
         <v>2248000</v>
       </c>
-      <c r="T70" s="3">
+      <c r="U70" s="3">
         <v>3052000</v>
-      </c>
-      <c r="U70" s="3">
-        <v>1930000</v>
       </c>
       <c r="V70" s="3">
         <v>1930000</v>
@@ -5897,7 +6064,7 @@
         <v>1930000</v>
       </c>
       <c r="X70" s="3">
-        <v>2303000</v>
+        <v>1930000</v>
       </c>
       <c r="Y70" s="3">
         <v>2303000</v>
@@ -5906,7 +6073,7 @@
         <v>2303000</v>
       </c>
       <c r="AA70" s="3">
-        <v>1746000</v>
+        <v>2303000</v>
       </c>
       <c r="AB70" s="3">
         <v>1746000</v>
@@ -5923,8 +6090,11 @@
       <c r="AF70" s="3">
         <v>1746000</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>1746000</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6015,100 +6185,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>49716000</v>
+      </c>
+      <c r="E72" s="3">
         <v>48491000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>48766000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>50388000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>50970000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>51490000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>52412000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>53688000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>53294000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>52736000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>52464000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>51107000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>52767000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>50336000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>49380000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>48326000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>48074000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>46527000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>45803000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>45148000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>45708000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>46178000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>45508000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>45031000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>43162000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>42125000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>41622000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>41208000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>40678000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>39990000</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6199,8 +6375,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6291,8 +6470,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6383,100 +6565,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>15769000</v>
+      </c>
+      <c r="E76" s="3">
         <v>12592000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>13516000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>15524000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>15518000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>15703000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>18145000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>21242000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>23209000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>24759000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>26037000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>24649000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>28247000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>25293000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>25016000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>22203000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>23750000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>23088000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>22546000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>21488000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>19382000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>21330000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>20819000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>20974000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>20805000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>20373000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>19755000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>19412000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>18827000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>19188000</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6567,197 +6755,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1460000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-41000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1389000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-346000</v>
       </c>
-      <c r="G81" s="3">
-        <v>-310000</v>
-      </c>
       <c r="H81" s="3">
+        <v>-303000</v>
+      </c>
+      <c r="I81" s="3">
         <v>-685000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1040000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>634000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>790000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>508000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1595000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1408000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2598000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1126000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1224000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>513000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1707000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>889000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>821000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1261000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-585000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>942000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>678000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>977000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1220000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>637000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>550000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>666000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>811000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>491000</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6790,100 +6987,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>165000</v>
+      </c>
+      <c r="E83" s="3">
         <v>176000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>186000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>177000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>201000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>194000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>216000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>236000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>268000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>247000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>311000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>260000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>186000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>182000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>163000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>155000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>171000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>159000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>160000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>157000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>135000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>128000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>126000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>122000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>125000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>120000</v>
-      </c>
-      <c r="AC83" s="3">
-        <v>119000</v>
       </c>
       <c r="AD83" s="3">
         <v>119000</v>
       </c>
       <c r="AE83" s="3">
-        <v>97000</v>
+        <v>119000</v>
       </c>
       <c r="AF83" s="3">
         <v>97000</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>97000</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6974,8 +7175,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7066,8 +7270,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7158,8 +7365,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7250,8 +7460,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7342,100 +7555,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1225000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1233000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1169000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>601000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>970000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2046000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1673000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>432000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>871000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1329000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1551000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1365000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1319000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1296000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1849000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1027000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1234000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1833000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1348000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>714000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1357000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1728000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1464000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>626000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1100000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1866000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>491000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>857000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1251000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1384000</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7468,100 +7687,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-71000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-55000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-62000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-79000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-68000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-124000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-98000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-130000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-59000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-89000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-136000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-61000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-73000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-69000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-101000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-65000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-140000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-120000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-93000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-80000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-82000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-67000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-66000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-62000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-83000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-70000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-72000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-74000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-123000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7652,8 +7875,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7744,100 +7970,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1105000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-845000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-253000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-796000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-447000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1143000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1119000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>981000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>221000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>446000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-670000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>513000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2198000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-285000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1026000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>68000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>428000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-2093000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-879000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-263000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>737000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1145000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-60000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1251000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-140000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1127000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>337000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-280000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1868000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-834000</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7870,8 +8102,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7879,91 +8112,94 @@
         <v>-233000</v>
       </c>
       <c r="E96" s="3">
+        <v>-233000</v>
+      </c>
+      <c r="F96" s="3">
         <v>-235000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-224000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-228000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-232000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-236000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-230000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-235000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-241000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-245000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-164000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-168000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-169000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-172000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-159000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-163000</v>
-      </c>
-      <c r="T96" s="3">
-        <v>-166000</v>
       </c>
       <c r="U96" s="3">
         <v>-166000</v>
       </c>
       <c r="V96" s="3">
+        <v>-166000</v>
+      </c>
+      <c r="W96" s="3">
         <v>-158000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-159000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-160000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-163000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-132000</v>
-      </c>
-      <c r="AA96" s="3">
-        <v>-134000</v>
       </c>
       <c r="AB96" s="3">
         <v>-134000</v>
       </c>
       <c r="AC96" s="3">
+        <v>-134000</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-135000</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>-122000</v>
       </c>
       <c r="AE96" s="3">
         <v>-122000</v>
       </c>
       <c r="AF96" s="3">
+        <v>-122000</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-124000</v>
       </c>
     </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8054,8 +8290,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8146,8 +8385,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8238,100 +8480,106 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-258000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-227000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-879000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>121000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-573000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-883000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-918000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1046000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1175000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1743000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-842000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1480000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>886000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1188000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-614000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1095000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1911000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>248000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-421000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-399000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-2055000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-612000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1365000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>458000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1033000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-531000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-788000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-571000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>664000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-607000</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8422,96 +8670,102 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-138000</v>
+      </c>
+      <c r="E102" s="3">
         <v>161000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>37000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-74000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-50000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>20000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-364000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>367000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-83000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>32000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>39000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>398000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>7000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-177000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>209000</v>
       </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
       <c r="S102" s="3">
+        <v>0</v>
+      </c>
+      <c r="T102" s="3">
         <v>-249000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-12000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>48000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>52000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>39000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-29000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>39000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-167000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-73000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>208000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>40000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>6000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>47000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-57000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ALL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ALL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="92">
   <si>
     <t>ALL</t>
   </si>
@@ -656,413 +656,425 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="33" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="7" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="34" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>15259000</v>
+      </c>
+      <c r="E8" s="3">
         <v>14832000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>14497000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>13979000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>13786000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>13648000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>13208000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>12219000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>12336000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>13011000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>12480000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>12646000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>12451000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>10962000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>10678000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>10403000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>9866000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>11476000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>11085000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>11156000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>11006000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>9486000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>10469000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>10103000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>9770000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>9854000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>9686000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>9634000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>9496000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>9350000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>9294000</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1939000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1904000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1841000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1789000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1744000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1725000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1683000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1618000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1608000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1602000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1582000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1545000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1523000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1382000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1386000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1344000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1365000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1382000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1425000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1362000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1364000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1336000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1317000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1296000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1273000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1239000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1200000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1176000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1169000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1157000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1138000</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>13320000</v>
+      </c>
+      <c r="E10" s="3">
         <v>12928000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>12656000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>12190000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>12042000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>11923000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>11525000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>10601000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>10728000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>11409000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>10898000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>11101000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>10928000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>9580000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>9292000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>9059000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>8501000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>10094000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>9660000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>9794000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>9642000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>8150000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>9152000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>8807000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>8497000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>8615000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>8486000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>8458000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>8327000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>8193000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>8156000</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1096,8 +1108,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1191,8 +1204,11 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1286,159 +1302,165 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E14" s="3">
         <v>28000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>87000</v>
-      </c>
-      <c r="F14" s="3">
-        <v>27000</v>
       </c>
       <c r="G14" s="3">
         <v>27000</v>
       </c>
       <c r="H14" s="3">
+        <v>27000</v>
+      </c>
+      <c r="I14" s="3">
         <v>24000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>14000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>12000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>25000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>23000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>100000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>73000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>39000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>195000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>750000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>213000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>66000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>16000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>74000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>33000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>15000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>16000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>25000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>18000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>163000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>39000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>88000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>70000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>80000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>77000</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>83000</v>
+        <v>69000</v>
       </c>
       <c r="E15" s="3">
         <v>83000</v>
       </c>
       <c r="F15" s="3">
+        <v>83000</v>
+      </c>
+      <c r="G15" s="3">
         <v>82000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>81000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>89000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>90000</v>
-      </c>
-      <c r="J15" s="3">
-        <v>87000</v>
       </c>
       <c r="K15" s="3">
         <v>87000</v>
       </c>
       <c r="L15" s="3">
-        <v>109000</v>
+        <v>87000</v>
       </c>
       <c r="M15" s="3">
         <v>109000</v>
       </c>
       <c r="N15" s="3">
+        <v>109000</v>
+      </c>
+      <c r="O15" s="3">
         <v>105000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>53000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>30000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>31000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>29000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>28000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>30000</v>
-      </c>
-      <c r="U15" s="3">
-        <v>32000</v>
       </c>
       <c r="V15" s="3">
         <v>32000</v>
@@ -1447,19 +1469,19 @@
         <v>32000</v>
       </c>
       <c r="X15" s="3">
+        <v>32000</v>
+      </c>
+      <c r="Y15" s="3">
         <v>36000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>24000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>23000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>22000</v>
-      </c>
-      <c r="AB15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC15" s="3" t="s">
         <v>8</v>
@@ -1467,8 +1489,8 @@
       <c r="AD15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE15" s="3">
-        <v>0</v>
+      <c r="AE15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF15" s="3">
         <v>0</v>
@@ -1476,8 +1498,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1508,198 +1533,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>13795000</v>
+      </c>
+      <c r="E17" s="3">
         <v>13005000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>14518000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>15727000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>14192000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>14058000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>14118000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>13530000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>11535000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>11618000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>12254000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>10849000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>9419000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>8098000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>9150000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>9024000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>8835000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>9245000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>9925000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>10078000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>9386000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>10196000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>9291000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>9206000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>8507000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>8697000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>8715000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>8783000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>8484000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>8092000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>8529000</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1464000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1827000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-21000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1748000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-406000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-410000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-910000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1311000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>801000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1393000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>226000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1797000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3032000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2864000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1528000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1379000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1031000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2231000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1160000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1078000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1620000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-710000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1178000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>897000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1263000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1157000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>971000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>851000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1012000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1258000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>765000</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1733,8 +1765,9 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1828,103 +1861,109 @@
       <c r="AG20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1596000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1992000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>155000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1562000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-229000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-209000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-716000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-1095000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1037000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1661000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>473000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2108000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3292000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3050000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1710000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1542000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1186000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2402000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1319000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1238000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1777000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-575000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1306000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1023000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1385000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1282000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1091000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>970000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1131000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1355000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>862000</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2018,198 +2057,207 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1464000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1827000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-21000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1748000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-406000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-410000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-910000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1311000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>801000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1393000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>226000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1797000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3032000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2864000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1528000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1379000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1031000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2231000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1160000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1078000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1620000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-710000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1178000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>897000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1263000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1157000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>971000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>851000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1012000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1258000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>765000</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>266000</v>
+      </c>
+      <c r="E24" s="3">
         <v>340000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-17000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-373000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-85000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-114000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-236000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-289000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>151000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>281000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>20000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>362000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>626000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>594000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>312000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>273000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>194000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>458000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>229000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>227000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>328000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-170000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>230000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>180000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>257000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>414000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>305000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>272000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>317000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>418000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>245000</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2303,198 +2351,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1198000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1487000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-4000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1375000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-321000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-296000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-674000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1022000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>650000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1112000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>206000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1435000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2406000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2270000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1216000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1106000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>837000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1773000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>931000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>851000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1292000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-540000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>948000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>717000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1006000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>743000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>666000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>579000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>695000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>840000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>520000</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1189000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1460000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-41000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1389000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-346000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-303000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-685000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1040000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>634000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1111000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>183000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1399000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2385000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2244000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1189000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1080000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>801000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1707000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>889000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>821000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1261000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-583000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>911000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>678000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>977000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>714000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>637000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>550000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>666000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>811000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>491000</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2588,8 +2645,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2608,8 +2668,8 @@
       <c r="H29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I29" s="3">
-        <v>0</v>
+      <c r="I29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J29" s="3">
         <v>0</v>
@@ -2618,31 +2678,31 @@
         <v>0</v>
       </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>-321000</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>325000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>196000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-3793000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>354000</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-63000</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>144000</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-288000</v>
-      </c>
-      <c r="T29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>8</v>
@@ -2653,23 +2713,23 @@
       <c r="W29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X29" s="3">
+      <c r="X29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y29" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>31000</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC29" s="3">
         <v>506000</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -2683,8 +2743,11 @@
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2778,8 +2841,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2873,8 +2939,11 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2968,103 +3037,109 @@
       <c r="AG32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1189000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1460000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-41000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1389000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-346000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-303000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-685000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1040000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>634000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>790000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>508000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1595000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1408000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2598000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1126000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1224000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>513000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1707000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>889000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>821000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1261000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-585000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>942000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>678000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>977000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1220000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>637000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>550000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>666000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>811000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>491000</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3158,203 +3233,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1189000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1460000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-41000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1389000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-346000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-303000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-685000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1040000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>634000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>790000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>508000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1595000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1408000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2598000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1126000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1224000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>513000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1707000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>889000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>821000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1261000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-585000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>942000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>678000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>977000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1220000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>637000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>550000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>666000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>811000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>491000</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3388,8 +3472,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3423,103 +3508,107 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>850000</v>
+      </c>
+      <c r="E41" s="3">
         <v>722000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>860000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>699000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>662000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>736000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>786000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>766000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1130000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>763000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>690000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>656000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>709000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>377000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>370000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>547000</v>
-      </c>
-      <c r="S41" s="3">
-        <v>338000</v>
       </c>
       <c r="T41" s="3">
         <v>338000</v>
       </c>
       <c r="U41" s="3">
+        <v>338000</v>
+      </c>
+      <c r="V41" s="3">
         <v>587000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>599000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>551000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>499000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>460000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>489000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>450000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>617000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>690000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>482000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>442000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>436000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>389000</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3613,103 +3702,109 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>10573000</v>
+      </c>
+      <c r="E43" s="3">
         <v>10044000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>10102000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>9713000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>9483000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>9165000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>9150000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>8824000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>8874000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>8364000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>8406000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>8146000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>7921000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>6479000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>6609000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>6367000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>6401000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>6472000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>6558000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>6380000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>6201000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>6154000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>6196000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>5953000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>5856000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>5786000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>5922000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>5693000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>5649000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>5597000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>5799000</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3803,8 +3898,11 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3898,8 +3996,11 @@
       <c r="AG45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3993,198 +4094,207 @@
       <c r="AG46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>67859000</v>
+      </c>
+      <c r="E47" s="3">
         <v>66677000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>63359000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>63668000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>63475000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>61829000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>61006000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>61055000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>61768000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>64701000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>61840000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>62570000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>60076000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>94237000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>91197000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>89637000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>84783000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>88221000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>89158000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>86345000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>84018000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>81136000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>83855000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>83140000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>83195000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>82677000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>82680000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>81203000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>81050000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>81707000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>81038000</v>
       </c>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>802000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1022000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>909000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>945000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>971000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1221000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1008000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>975000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>966000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1253000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>965000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1026000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1002000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1057000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1076000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1100000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1123000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1628000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1535000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1519000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1521000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1045000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1032000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1040000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1060000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1072000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1067000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1072000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1067000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1065000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1013000</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4207,25 +4317,25 @@
         <v>3502000</v>
       </c>
       <c r="J49" s="3">
+        <v>3502000</v>
+      </c>
+      <c r="K49" s="3">
         <v>3496000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3497000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3502000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3389000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3349000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3350000</v>
-      </c>
-      <c r="P49" s="3">
-        <v>2544000</v>
       </c>
       <c r="Q49" s="3">
         <v>2544000</v>
@@ -4237,22 +4347,22 @@
         <v>2544000</v>
       </c>
       <c r="T49" s="3">
-        <v>2545000</v>
+        <v>2544000</v>
       </c>
       <c r="U49" s="3">
         <v>2545000</v>
       </c>
       <c r="V49" s="3">
-        <v>2547000</v>
+        <v>2545000</v>
       </c>
       <c r="W49" s="3">
         <v>2547000</v>
       </c>
       <c r="X49" s="3">
+        <v>2547000</v>
+      </c>
+      <c r="Y49" s="3">
         <v>2530000</v>
-      </c>
-      <c r="Y49" s="3">
-        <v>2189000</v>
       </c>
       <c r="Z49" s="3">
         <v>2189000</v>
@@ -4261,25 +4371,28 @@
         <v>2189000</v>
       </c>
       <c r="AB49" s="3">
+        <v>2189000</v>
+      </c>
+      <c r="AC49" s="3">
         <v>2181000</v>
-      </c>
-      <c r="AC49" s="3">
-        <v>2309000</v>
       </c>
       <c r="AD49" s="3">
         <v>2309000</v>
       </c>
       <c r="AE49" s="3">
+        <v>2309000</v>
+      </c>
+      <c r="AF49" s="3">
         <v>2295000</v>
-      </c>
-      <c r="AF49" s="3">
-        <v>1219000</v>
       </c>
       <c r="AG49" s="3">
         <v>1219000</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3">
+        <v>1219000</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4373,8 +4486,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4468,49 +4584,52 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>161000</v>
+      </c>
+      <c r="E52" s="3">
         <v>219000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>816000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>480000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>345000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>382000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>492000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>118000</v>
       </c>
-      <c r="K52" s="3" t="s">
+      <c r="L52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
-      </c>
       <c r="M52" s="3">
+        <v>0</v>
+      </c>
+      <c r="N52" s="3">
         <v>36803000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>36969000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>36829000</v>
-      </c>
-      <c r="P52" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>8</v>
@@ -4527,8 +4646,8 @@
       <c r="U52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V52" s="3">
-        <v>0</v>
+      <c r="V52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W52" s="3">
         <v>0</v>
@@ -4563,8 +4682,11 @@
       <c r="AG52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4658,103 +4780,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>105241000</v>
+      </c>
+      <c r="E54" s="3">
         <v>103362000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>101176000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>100514000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>99631000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>97989000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>97676000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>96350000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>97150000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>99440000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>133440000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>132643000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>129811000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>125987000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>122750000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>121266000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>116107000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>119950000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>121073000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>118374000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>115834000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>112249000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>114490000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>113369000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>113289000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>112422000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>113632000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>110865000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>110243000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>108610000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>108537000</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4788,8 +4916,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4823,8 +4952,9 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4918,8 +5048,11 @@
       <c r="AG57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5013,103 +5146,109 @@
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>27160000</v>
+      </c>
+      <c r="E59" s="3">
         <v>27209000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>26711000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>25575000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>24715000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>24843000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>24211000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>23229000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>22429000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>22490000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>21753000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>20853000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>20274000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>49274000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>49140000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>48221000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>46664000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>48503000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>48555000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>48232000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>48055000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>47670000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>48313000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>47936000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>47972000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>48614000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>48542000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>48216000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>48129000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>48185000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>48745000</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5203,117 +5342,123 @@
       <c r="AG60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7938000</v>
+      </c>
+      <c r="E61" s="3">
         <v>7942000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7946000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7949000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>8452000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>7964000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>7967000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>7970000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>7973000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>7976000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>7980000</v>
-      </c>
-      <c r="N61" s="3">
-        <v>7996000</v>
       </c>
       <c r="O61" s="3">
         <v>7996000</v>
       </c>
       <c r="P61" s="3">
+        <v>7996000</v>
+      </c>
+      <c r="Q61" s="3">
         <v>7825000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>6635000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>6634000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>6633000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>6631000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>6630000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>6628000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>6453000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>6451000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>6450000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>6448000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>6847000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>6350000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>6349000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>6348000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>6346000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>6347000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>5110000</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>8</v>
+      <c r="D62" s="3">
+        <v>0</v>
+      </c>
+      <c r="E62" s="3">
+        <v>0</v>
+      </c>
+      <c r="F62" s="3">
+        <v>0</v>
+      </c>
+      <c r="G62" s="3">
+        <v>0</v>
       </c>
       <c r="H62" s="3">
         <v>0</v>
@@ -5325,76 +5470,79 @@
         <v>0</v>
       </c>
       <c r="K62" s="3">
+        <v>0</v>
+      </c>
+      <c r="L62" s="3">
         <v>402000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>833000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>33132000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>33533000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>33876000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1355000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>905000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>842000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>331000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1154000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1079000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>997000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>817000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>425000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>660000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>723000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>725000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>782000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1249000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1104000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>833000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>487000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>935000</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5488,8 +5636,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5583,8 +5734,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5678,103 +5832,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>86602000</v>
+      </c>
+      <c r="E66" s="3">
         <v>85592000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>86583000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>84997000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>82137000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>80501000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>80003000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>76235000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>73938000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>74261000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>106711000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>104436000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>102992000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>95770000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>95487000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>94280000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>91934000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>93952000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>94933000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>93898000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>92416000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>90937000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>90857000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>90247000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>90012000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>89871000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>91513000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>89364000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>89085000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>88037000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>87603000</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5808,8 +5968,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5903,8 +6064,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5998,8 +6162,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6013,7 +6180,7 @@
         <v>2001000</v>
       </c>
       <c r="G70" s="3">
-        <v>1970000</v>
+        <v>2001000</v>
       </c>
       <c r="H70" s="3">
         <v>1970000</v>
@@ -6034,13 +6201,13 @@
         <v>1970000</v>
       </c>
       <c r="N70" s="3">
-        <v>2170000</v>
+        <v>1970000</v>
       </c>
       <c r="O70" s="3">
         <v>2170000</v>
       </c>
       <c r="P70" s="3">
-        <v>1970000</v>
+        <v>2170000</v>
       </c>
       <c r="Q70" s="3">
         <v>1970000</v>
@@ -6052,13 +6219,13 @@
         <v>1970000</v>
       </c>
       <c r="T70" s="3">
+        <v>1970000</v>
+      </c>
+      <c r="U70" s="3">
         <v>2248000</v>
       </c>
-      <c r="U70" s="3">
+      <c r="V70" s="3">
         <v>3052000</v>
-      </c>
-      <c r="V70" s="3">
-        <v>1930000</v>
       </c>
       <c r="W70" s="3">
         <v>1930000</v>
@@ -6067,7 +6234,7 @@
         <v>1930000</v>
       </c>
       <c r="Y70" s="3">
-        <v>2303000</v>
+        <v>1930000</v>
       </c>
       <c r="Z70" s="3">
         <v>2303000</v>
@@ -6076,7 +6243,7 @@
         <v>2303000</v>
       </c>
       <c r="AB70" s="3">
-        <v>1746000</v>
+        <v>2303000</v>
       </c>
       <c r="AC70" s="3">
         <v>1746000</v>
@@ -6093,8 +6260,11 @@
       <c r="AG70" s="3">
         <v>1746000</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>1746000</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6188,103 +6358,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>50662000</v>
+      </c>
+      <c r="E72" s="3">
         <v>49716000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>48491000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>48766000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>50388000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>50970000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>51490000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>52412000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>53688000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>53294000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>52736000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>52464000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>51107000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>52767000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>50336000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>49380000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>48326000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>48074000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>46527000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>45803000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>45148000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>45708000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>46178000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>45508000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>45031000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>43162000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>42125000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>41622000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>41208000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>40678000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>39990000</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6378,8 +6554,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6473,8 +6652,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6568,103 +6750,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>16638000</v>
+      </c>
+      <c r="E76" s="3">
         <v>15769000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>12592000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>13516000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>15524000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>15518000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>15703000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>18145000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>21242000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>23209000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>24759000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>26037000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>24649000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>28247000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>25293000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>25016000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>22203000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>23750000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>23088000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>22546000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>21488000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>19382000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>21330000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>20819000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>20974000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>20805000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>20373000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>19755000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>19412000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>18827000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>19188000</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6758,203 +6946,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1189000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1460000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-41000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1389000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-346000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-303000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-685000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1040000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>634000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>790000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>508000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1595000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1408000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2598000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1126000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1224000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>513000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1707000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>889000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>821000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1261000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-585000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>942000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>678000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>977000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1220000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>637000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>550000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>666000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>811000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>491000</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6988,103 +7185,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>132000</v>
+      </c>
+      <c r="E83" s="3">
         <v>165000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>176000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>186000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>177000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>201000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>194000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>216000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>236000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>268000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>247000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>311000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>260000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>186000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>182000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>163000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>155000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>171000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>159000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>160000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>157000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>135000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>128000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>126000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>122000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>125000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>120000</v>
-      </c>
-      <c r="AD83" s="3">
-        <v>119000</v>
       </c>
       <c r="AE83" s="3">
         <v>119000</v>
       </c>
       <c r="AF83" s="3">
-        <v>97000</v>
+        <v>119000</v>
       </c>
       <c r="AG83" s="3">
         <v>97000</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3">
+        <v>97000</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7178,8 +7379,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7273,8 +7477,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7368,8 +7575,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7463,8 +7673,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7558,103 +7771,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1666000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1225000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1233000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1169000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>601000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>970000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2046000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1673000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>432000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>871000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1329000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1551000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1365000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1319000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1296000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1849000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1027000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1234000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1833000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1348000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>714000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1357000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1728000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1464000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>626000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1100000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1866000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>491000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>857000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1251000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1384000</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7688,103 +7907,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-41000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-71000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-55000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-62000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-79000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-68000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-124000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-98000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-130000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-59000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-89000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-136000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-61000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-73000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-69000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-101000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-65000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-140000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-120000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-93000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-80000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-82000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-67000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-66000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-62000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-83000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-70000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-72000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-74000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-123000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7878,8 +8101,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7973,103 +8199,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1372000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1105000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-845000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-253000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-796000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-447000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1143000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1119000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>981000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>221000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>446000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-670000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>513000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2198000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-285000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1026000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>68000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>428000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2093000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-879000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-263000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>737000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1145000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-60000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1251000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-140000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1127000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>337000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-280000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1868000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-834000</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8103,8 +8335,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8115,91 +8348,94 @@
         <v>-233000</v>
       </c>
       <c r="F96" s="3">
+        <v>-233000</v>
+      </c>
+      <c r="G96" s="3">
         <v>-235000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-224000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-228000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-232000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-236000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-230000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-235000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-241000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-245000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-164000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-168000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-169000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-172000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-159000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-163000</v>
-      </c>
-      <c r="U96" s="3">
-        <v>-166000</v>
       </c>
       <c r="V96" s="3">
         <v>-166000</v>
       </c>
       <c r="W96" s="3">
+        <v>-166000</v>
+      </c>
+      <c r="X96" s="3">
         <v>-158000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-159000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-160000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-163000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-132000</v>
-      </c>
-      <c r="AB96" s="3">
-        <v>-134000</v>
       </c>
       <c r="AC96" s="3">
         <v>-134000</v>
       </c>
       <c r="AD96" s="3">
+        <v>-134000</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-135000</v>
-      </c>
-      <c r="AE96" s="3">
-        <v>-122000</v>
       </c>
       <c r="AF96" s="3">
         <v>-122000</v>
       </c>
       <c r="AG96" s="3">
+        <v>-122000</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-124000</v>
       </c>
     </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8293,8 +8529,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8388,8 +8627,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8483,103 +8725,109 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-166000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-258000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-227000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-879000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>121000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-573000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-883000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-918000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1046000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1175000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1743000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-842000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1480000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>886000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1188000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-614000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1095000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1911000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>248000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-421000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-399000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-2055000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-612000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1365000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>458000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1033000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-531000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-788000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-571000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>664000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-607000</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8673,99 +8921,105 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>128000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-138000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>161000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>37000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-74000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-50000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>20000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-364000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>367000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-83000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>32000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>39000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>398000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>7000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-177000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>209000</v>
       </c>
-      <c r="S102" s="3">
-        <v>0</v>
-      </c>
       <c r="T102" s="3">
+        <v>0</v>
+      </c>
+      <c r="U102" s="3">
         <v>-249000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-12000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>48000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>52000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>39000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-29000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>39000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-167000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-73000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>208000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>40000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>6000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>47000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-57000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ALL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ALL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="92">
   <si>
     <t>ALL</t>
   </si>
@@ -656,425 +656,437 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="34" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="8" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="35" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>15714000</v>
+      </c>
+      <c r="E8" s="3">
         <v>15259000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>14832000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>14497000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>13979000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>13786000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>13648000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>13208000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>12219000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>12336000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>13011000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>12480000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>12646000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>12451000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>10962000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>10678000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>10403000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>9866000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>11476000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>11085000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>11156000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>11006000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>9486000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>10469000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>10103000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>9770000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>9854000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>9686000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>9634000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>9496000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>9350000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>9294000</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2001000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1939000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1904000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1841000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1789000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1744000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1725000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1683000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1618000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1608000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1602000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1582000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1545000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1523000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1382000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1386000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1344000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1365000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1382000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1425000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1362000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1364000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1336000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1317000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1296000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1273000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1239000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1200000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1176000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1169000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1157000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1138000</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>13713000</v>
+      </c>
+      <c r="E10" s="3">
         <v>13320000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>12928000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>12656000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>12190000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>12042000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>11923000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>11525000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>10601000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>10728000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>11409000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>10898000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>11101000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>10928000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>9580000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>9292000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>9059000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>8501000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>10094000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>9660000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>9794000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>9642000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>8150000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>9152000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>8807000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>8497000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>8615000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>8486000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>8458000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>8327000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>8193000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>8156000</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1109,8 +1121,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1207,8 +1220,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1305,165 +1321,171 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E14" s="3">
         <v>10000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>28000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>87000</v>
-      </c>
-      <c r="G14" s="3">
-        <v>27000</v>
       </c>
       <c r="H14" s="3">
         <v>27000</v>
       </c>
       <c r="I14" s="3">
+        <v>27000</v>
+      </c>
+      <c r="J14" s="3">
         <v>24000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>14000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>12000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>25000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>23000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>100000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>73000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>39000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>195000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>750000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>213000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>66000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>16000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>74000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>33000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>15000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>16000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>25000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>18000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>163000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>39000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>88000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>70000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>80000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>77000</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>70000</v>
+      </c>
+      <c r="E15" s="3">
         <v>69000</v>
-      </c>
-      <c r="E15" s="3">
-        <v>83000</v>
       </c>
       <c r="F15" s="3">
         <v>83000</v>
       </c>
       <c r="G15" s="3">
+        <v>83000</v>
+      </c>
+      <c r="H15" s="3">
         <v>82000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>81000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>89000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>90000</v>
-      </c>
-      <c r="K15" s="3">
-        <v>87000</v>
       </c>
       <c r="L15" s="3">
         <v>87000</v>
       </c>
       <c r="M15" s="3">
-        <v>109000</v>
+        <v>87000</v>
       </c>
       <c r="N15" s="3">
         <v>109000</v>
       </c>
       <c r="O15" s="3">
+        <v>109000</v>
+      </c>
+      <c r="P15" s="3">
         <v>105000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>53000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>30000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>31000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>29000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>28000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>30000</v>
-      </c>
-      <c r="V15" s="3">
-        <v>32000</v>
       </c>
       <c r="W15" s="3">
         <v>32000</v>
@@ -1472,19 +1494,19 @@
         <v>32000</v>
       </c>
       <c r="Y15" s="3">
+        <v>32000</v>
+      </c>
+      <c r="Z15" s="3">
         <v>36000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>24000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>23000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>22000</v>
-      </c>
-      <c r="AC15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD15" s="3" t="s">
         <v>8</v>
@@ -1492,8 +1514,8 @@
       <c r="AE15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF15" s="3">
-        <v>0</v>
+      <c r="AF15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG15" s="3">
         <v>0</v>
@@ -1501,8 +1523,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1534,204 +1559,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>15284000</v>
+      </c>
+      <c r="E17" s="3">
         <v>13795000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>13005000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>14518000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>15727000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>14192000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>14058000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>14118000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>13530000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>11535000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>11618000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>12254000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>10849000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>9419000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>8098000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>9150000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>9024000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>8835000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>9245000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>9925000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>10078000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>9386000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>10196000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>9291000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>9206000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>8507000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>8697000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>8715000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>8783000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>8484000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>8092000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>8529000</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>430000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1464000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1827000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-21000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1748000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-406000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-410000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-910000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1311000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>801000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1393000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>226000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1797000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3032000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2864000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1528000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1379000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1031000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2231000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1160000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1078000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1620000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-710000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1178000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>897000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1263000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1157000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>971000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>851000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1012000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1258000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>765000</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1766,8 +1798,9 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1864,106 +1897,112 @@
       <c r="AH20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>562000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1596000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1992000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>155000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-1562000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-229000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-209000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-716000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1095000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1037000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1661000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>473000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2108000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3292000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>3050000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1710000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1542000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1186000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2402000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1319000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1238000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1777000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-575000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1306000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1023000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1385000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1282000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1091000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>970000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1131000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1355000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>862000</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2060,204 +2099,213 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>430000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1464000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1827000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-21000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1748000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-406000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-410000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-910000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1311000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>801000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1393000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>226000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1797000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3032000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2864000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1528000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1379000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1031000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2231000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1160000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1078000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1620000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-710000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1178000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>897000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1263000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1157000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>971000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>851000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1012000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1258000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>765000</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>83000</v>
+      </c>
+      <c r="E24" s="3">
         <v>266000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>340000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-17000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-373000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-85000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-114000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-236000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-289000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>151000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>281000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>20000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>362000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>626000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>594000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>312000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>273000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>194000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>458000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>229000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>227000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>328000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-170000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>230000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>180000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>257000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>414000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>305000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>272000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>317000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>418000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>245000</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2354,204 +2402,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>347000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1198000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1487000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-4000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1375000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-321000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-296000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-674000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1022000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>650000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1112000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>206000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1435000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2406000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2270000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1216000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1106000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>837000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1773000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>931000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>851000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1292000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-540000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>948000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>717000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1006000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>743000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>666000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>579000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>695000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>840000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>520000</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>301000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1189000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1460000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-41000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1389000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-346000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-303000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-685000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1040000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>634000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1111000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>183000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1399000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2385000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2244000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1189000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1080000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>801000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1707000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>889000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>821000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1261000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-583000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>911000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>678000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>977000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>714000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>637000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>550000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>666000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>811000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>491000</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2648,8 +2705,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2671,8 +2731,8 @@
       <c r="I29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J29" s="3">
-        <v>0</v>
+      <c r="J29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -2681,31 +2741,31 @@
         <v>0</v>
       </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>-321000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>325000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>196000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-3793000</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>354000</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-63000</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>144000</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-288000</v>
-      </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>8</v>
@@ -2716,23 +2776,23 @@
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Y29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z29" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>31000</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3">
         <v>506000</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
@@ -2746,8 +2806,11 @@
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2844,8 +2907,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2942,8 +3008,11 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3040,106 +3109,112 @@
       <c r="AH32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>301000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1189000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1460000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-41000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1389000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-346000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-303000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-685000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1040000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>634000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>790000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>508000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1595000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1408000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2598000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1126000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1224000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>513000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1707000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>889000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>821000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1261000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-585000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>942000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>678000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>977000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1220000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>637000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>550000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>666000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>811000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>491000</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3236,209 +3311,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>301000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1189000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1460000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-41000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1389000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-346000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-303000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-685000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1040000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>634000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>790000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>508000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1595000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1408000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2598000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1126000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1224000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>513000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1707000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>889000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>821000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1261000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-585000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>942000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>678000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>977000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1220000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>637000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>550000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>666000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>811000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>491000</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3473,8 +3557,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3509,106 +3594,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>599000</v>
+      </c>
+      <c r="E41" s="3">
         <v>850000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>722000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>860000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>699000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>662000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>736000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>786000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>766000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1130000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>763000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>690000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>656000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>709000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>377000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>370000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>547000</v>
-      </c>
-      <c r="T41" s="3">
-        <v>338000</v>
       </c>
       <c r="U41" s="3">
         <v>338000</v>
       </c>
       <c r="V41" s="3">
+        <v>338000</v>
+      </c>
+      <c r="W41" s="3">
         <v>587000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>599000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>551000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>499000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>460000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>489000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>450000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>617000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>690000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>482000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>442000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>436000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>389000</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3705,106 +3794,112 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>10762000</v>
+      </c>
+      <c r="E43" s="3">
         <v>10573000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>10044000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>10102000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>9713000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>9483000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>9165000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>9150000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>8824000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>8874000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>8364000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>8406000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>8146000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>7921000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>6479000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>6609000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>6367000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>6401000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>6472000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>6558000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>6380000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>6201000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>6154000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>6196000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>5953000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>5856000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>5786000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>5922000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>5693000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>5649000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>5597000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>5799000</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3901,8 +3996,11 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3999,8 +4097,11 @@
       <c r="AH45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -4097,204 +4198,213 @@
       <c r="AH46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>70604000</v>
+      </c>
+      <c r="E47" s="3">
         <v>67859000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>66677000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>63359000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>63668000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>63475000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>61829000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>61006000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>61055000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>61768000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>64701000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>61840000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>62570000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>60076000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>94237000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>91197000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>89637000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>84783000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>88221000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>89158000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>86345000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>84018000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>81136000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>83855000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>83140000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>83195000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>82677000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>82680000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>81203000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>81050000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>81707000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>81038000</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>777000</v>
+      </c>
+      <c r="E48" s="3">
         <v>802000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1022000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>909000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>945000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>971000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1221000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1008000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>975000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>966000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1253000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>965000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1026000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1002000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1057000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1076000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1100000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1123000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1628000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1535000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1519000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1521000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1045000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1032000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1040000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1060000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1072000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1067000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1072000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1067000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1065000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1013000</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4320,25 +4430,25 @@
         <v>3502000</v>
       </c>
       <c r="K49" s="3">
+        <v>3502000</v>
+      </c>
+      <c r="L49" s="3">
         <v>3496000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3497000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3502000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3389000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3349000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3350000</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>2544000</v>
       </c>
       <c r="R49" s="3">
         <v>2544000</v>
@@ -4350,22 +4460,22 @@
         <v>2544000</v>
       </c>
       <c r="U49" s="3">
-        <v>2545000</v>
+        <v>2544000</v>
       </c>
       <c r="V49" s="3">
         <v>2545000</v>
       </c>
       <c r="W49" s="3">
-        <v>2547000</v>
+        <v>2545000</v>
       </c>
       <c r="X49" s="3">
         <v>2547000</v>
       </c>
       <c r="Y49" s="3">
+        <v>2547000</v>
+      </c>
+      <c r="Z49" s="3">
         <v>2530000</v>
-      </c>
-      <c r="Z49" s="3">
-        <v>2189000</v>
       </c>
       <c r="AA49" s="3">
         <v>2189000</v>
@@ -4374,25 +4484,28 @@
         <v>2189000</v>
       </c>
       <c r="AC49" s="3">
+        <v>2189000</v>
+      </c>
+      <c r="AD49" s="3">
         <v>2181000</v>
-      </c>
-      <c r="AD49" s="3">
-        <v>2309000</v>
       </c>
       <c r="AE49" s="3">
         <v>2309000</v>
       </c>
       <c r="AF49" s="3">
+        <v>2309000</v>
+      </c>
+      <c r="AG49" s="3">
         <v>2295000</v>
-      </c>
-      <c r="AG49" s="3">
-        <v>1219000</v>
       </c>
       <c r="AH49" s="3">
         <v>1219000</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3">
+        <v>1219000</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4489,8 +4602,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4587,52 +4703,55 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>212000</v>
+      </c>
+      <c r="E52" s="3">
         <v>161000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>219000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>816000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>480000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>345000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>382000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>492000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>118000</v>
       </c>
-      <c r="L52" s="3" t="s">
+      <c r="M52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
-      </c>
       <c r="N52" s="3">
+        <v>0</v>
+      </c>
+      <c r="O52" s="3">
         <v>36803000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>36969000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>36829000</v>
-      </c>
-      <c r="Q52" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="R52" s="3" t="s">
         <v>8</v>
@@ -4649,8 +4768,8 @@
       <c r="V52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W52" s="3">
-        <v>0</v>
+      <c r="W52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X52" s="3">
         <v>0</v>
@@ -4685,8 +4804,11 @@
       <c r="AH52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4783,106 +4905,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>108368000</v>
+      </c>
+      <c r="E54" s="3">
         <v>105241000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>103362000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>101176000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>100514000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>99631000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>97989000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>97676000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>96350000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>97150000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>99440000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>133440000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>132643000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>129811000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>125987000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>122750000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>121266000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>116107000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>119950000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>121073000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>118374000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>115834000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>112249000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>114490000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>113369000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>113289000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>112422000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>113632000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>110865000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>110243000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>108610000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>108537000</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4917,8 +5045,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4953,8 +5082,9 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -5051,8 +5181,11 @@
       <c r="AH57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5149,106 +5282,112 @@
       <c r="AH58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>28164000</v>
+      </c>
+      <c r="E59" s="3">
         <v>27160000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>27209000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>26711000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>25575000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>24715000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>24843000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>24211000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>23229000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>22429000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>22490000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>21753000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>20853000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>20274000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>49274000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>49140000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>48221000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>46664000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>48503000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>48555000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>48232000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>48055000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>47670000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>48313000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>47936000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>47972000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>48614000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>48542000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>48216000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>48129000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>48185000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>48745000</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5345,106 +5484,112 @@
       <c r="AH60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>8082000</v>
+      </c>
+      <c r="E61" s="3">
         <v>7938000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7942000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7946000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7949000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>8452000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>7964000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>7967000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>7970000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>7973000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>7976000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>7980000</v>
-      </c>
-      <c r="O61" s="3">
-        <v>7996000</v>
       </c>
       <c r="P61" s="3">
         <v>7996000</v>
       </c>
       <c r="Q61" s="3">
+        <v>7996000</v>
+      </c>
+      <c r="R61" s="3">
         <v>7825000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>6635000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>6634000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>6633000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>6631000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>6630000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>6628000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>6453000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>6451000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>6450000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>6448000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>6847000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>6350000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>6349000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>6348000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>6346000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>6347000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>5110000</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5473,76 +5618,79 @@
         <v>0</v>
       </c>
       <c r="L62" s="3">
+        <v>0</v>
+      </c>
+      <c r="M62" s="3">
         <v>402000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>833000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>33132000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>33533000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>33876000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1355000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>905000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>842000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>331000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1154000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1079000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>997000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>817000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>425000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>660000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>723000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>725000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>782000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1249000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1104000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>833000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>487000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>935000</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5639,8 +5787,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5737,8 +5888,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5835,106 +5989,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>89775000</v>
+      </c>
+      <c r="E66" s="3">
         <v>86602000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>85592000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>86583000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>84997000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>82137000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>80501000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>80003000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>76235000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>73938000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>74261000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>106711000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>104436000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>102992000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>95770000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>95487000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>94280000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>91934000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>93952000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>94933000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>93898000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>92416000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>90937000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>90857000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>90247000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>90012000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>89871000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>91513000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>89364000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>89085000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>88037000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>87603000</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5969,8 +6129,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6067,8 +6228,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6165,8 +6329,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6183,7 +6350,7 @@
         <v>2001000</v>
       </c>
       <c r="H70" s="3">
-        <v>1970000</v>
+        <v>2001000</v>
       </c>
       <c r="I70" s="3">
         <v>1970000</v>
@@ -6204,13 +6371,13 @@
         <v>1970000</v>
       </c>
       <c r="O70" s="3">
-        <v>2170000</v>
+        <v>1970000</v>
       </c>
       <c r="P70" s="3">
         <v>2170000</v>
       </c>
       <c r="Q70" s="3">
-        <v>1970000</v>
+        <v>2170000</v>
       </c>
       <c r="R70" s="3">
         <v>1970000</v>
@@ -6222,13 +6389,13 @@
         <v>1970000</v>
       </c>
       <c r="U70" s="3">
+        <v>1970000</v>
+      </c>
+      <c r="V70" s="3">
         <v>2248000</v>
       </c>
-      <c r="V70" s="3">
+      <c r="W70" s="3">
         <v>3052000</v>
-      </c>
-      <c r="W70" s="3">
-        <v>1930000</v>
       </c>
       <c r="X70" s="3">
         <v>1930000</v>
@@ -6237,7 +6404,7 @@
         <v>1930000</v>
       </c>
       <c r="Z70" s="3">
-        <v>2303000</v>
+        <v>1930000</v>
       </c>
       <c r="AA70" s="3">
         <v>2303000</v>
@@ -6246,7 +6413,7 @@
         <v>2303000</v>
       </c>
       <c r="AC70" s="3">
-        <v>1746000</v>
+        <v>2303000</v>
       </c>
       <c r="AD70" s="3">
         <v>1746000</v>
@@ -6263,8 +6430,11 @@
       <c r="AH70" s="3">
         <v>1746000</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>1746000</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6361,106 +6531,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>50718000</v>
+      </c>
+      <c r="E72" s="3">
         <v>50662000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>49716000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>48491000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>48766000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>50388000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>50970000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>51490000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>52412000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>53688000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>53294000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>52736000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>52464000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>51107000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>52767000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>50336000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>49380000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>48326000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>48074000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>46527000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>45803000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>45148000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>45708000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>46178000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>45508000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>45031000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>43162000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>42125000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>41622000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>41208000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>40678000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>39990000</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6557,8 +6733,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6655,8 +6834,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6753,106 +6935,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>16592000</v>
+      </c>
+      <c r="E76" s="3">
         <v>16638000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>15769000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>12592000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>13516000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>15524000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>15518000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>15703000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>18145000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>21242000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>23209000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>24759000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>26037000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>24649000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>28247000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>25293000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>25016000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>22203000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>23750000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>23088000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>22546000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>21488000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>19382000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>21330000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>20819000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>20974000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>20805000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>20373000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>19755000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>19412000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>18827000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>19188000</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6949,209 +7137,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>301000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1189000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1460000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-41000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1389000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-346000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-303000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-685000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1040000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>634000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>790000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>508000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1595000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1408000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2598000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1126000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1224000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>513000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1707000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>889000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>821000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1261000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-585000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>942000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>678000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>977000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1220000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>637000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>550000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>666000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>811000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>491000</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7186,8 +7383,9 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7195,97 +7393,100 @@
         <v>132000</v>
       </c>
       <c r="E83" s="3">
+        <v>132000</v>
+      </c>
+      <c r="F83" s="3">
         <v>165000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>176000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>186000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>177000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>201000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>194000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>216000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>236000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>268000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>247000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>311000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>260000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>186000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>182000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>163000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>155000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>171000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>159000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>160000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>157000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>135000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>128000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>126000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>122000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>125000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>120000</v>
-      </c>
-      <c r="AE83" s="3">
-        <v>119000</v>
       </c>
       <c r="AF83" s="3">
         <v>119000</v>
       </c>
       <c r="AG83" s="3">
-        <v>97000</v>
+        <v>119000</v>
       </c>
       <c r="AH83" s="3">
         <v>97000</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3">
+        <v>97000</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7382,8 +7583,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7480,8 +7684,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7578,8 +7785,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7676,8 +7886,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7774,106 +7987,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2359000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1666000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1225000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1233000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1169000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>601000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>970000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2046000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1673000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>432000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>871000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1329000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1551000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1365000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1319000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1296000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1849000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1027000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1234000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1833000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1348000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>714000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1357000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1728000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1464000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>626000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1100000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1866000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>491000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>857000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1251000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1384000</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7908,106 +8127,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-56000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-41000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-71000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-55000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-62000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-79000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-68000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-124000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-98000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-130000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-59000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-89000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-136000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-61000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-73000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-69000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-101000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-65000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-140000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-120000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-93000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-80000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-82000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-67000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-66000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-62000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-83000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-70000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-72000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-74000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-123000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8104,8 +8327,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8202,106 +8428,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2524000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1372000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1105000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-845000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-253000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-796000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-447000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1143000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1119000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>981000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>221000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>446000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-670000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>513000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2198000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-285000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1026000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>68000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>428000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-2093000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-879000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-263000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>737000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1145000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-60000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1251000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-140000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1127000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>337000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-280000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1868000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-834000</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8336,13 +8568,14 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-233000</v>
+        <v>-243000</v>
       </c>
       <c r="E96" s="3">
         <v>-233000</v>
@@ -8351,91 +8584,94 @@
         <v>-233000</v>
       </c>
       <c r="G96" s="3">
+        <v>-233000</v>
+      </c>
+      <c r="H96" s="3">
         <v>-235000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-224000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-228000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-232000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-236000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-230000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-235000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-241000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-245000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-164000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-168000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-169000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-172000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-159000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-163000</v>
-      </c>
-      <c r="V96" s="3">
-        <v>-166000</v>
       </c>
       <c r="W96" s="3">
         <v>-166000</v>
       </c>
       <c r="X96" s="3">
+        <v>-166000</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-158000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-159000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-160000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-163000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-132000</v>
-      </c>
-      <c r="AC96" s="3">
-        <v>-134000</v>
       </c>
       <c r="AD96" s="3">
         <v>-134000</v>
       </c>
       <c r="AE96" s="3">
+        <v>-134000</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-135000</v>
-      </c>
-      <c r="AF96" s="3">
-        <v>-122000</v>
       </c>
       <c r="AG96" s="3">
         <v>-122000</v>
       </c>
       <c r="AH96" s="3">
+        <v>-122000</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-124000</v>
       </c>
     </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8532,8 +8768,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8630,8 +8869,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8728,106 +8970,112 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-86000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-166000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-258000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-227000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-879000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>121000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-573000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-883000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-918000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1046000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1175000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1743000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-842000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1480000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>886000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1188000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-614000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1095000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1911000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>248000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-421000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-399000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-2055000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-612000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1365000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>458000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1033000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-531000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-788000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-571000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>664000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-607000</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8924,102 +9172,108 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-251000</v>
+      </c>
+      <c r="E102" s="3">
         <v>128000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-138000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>161000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>37000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-74000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-50000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>20000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-364000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>367000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-83000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>32000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>39000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>398000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>7000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-177000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>209000</v>
       </c>
-      <c r="T102" s="3">
-        <v>0</v>
-      </c>
       <c r="U102" s="3">
+        <v>0</v>
+      </c>
+      <c r="V102" s="3">
         <v>-249000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-12000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>48000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>52000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>39000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-29000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>39000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-167000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-73000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>208000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>40000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>6000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>47000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-57000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ALL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ALL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="92">
   <si>
     <t>ALL</t>
   </si>
@@ -656,437 +656,449 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="35" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="36" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>16627000</v>
+      </c>
+      <c r="E8" s="3">
         <v>15714000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>15259000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>14832000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>14497000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>13979000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>13786000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>13648000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>13208000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>12219000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>12336000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>13011000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>12480000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>12646000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>12451000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>10962000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>10678000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>10403000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>9866000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>11476000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>11085000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>11156000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>11006000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>9486000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>10469000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>10103000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>9770000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>9854000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>9686000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>9634000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>9496000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>9350000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>9294000</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>2001000</v>
+        <v>12763000</v>
       </c>
       <c r="E9" s="3">
-        <v>1939000</v>
+        <v>13093000</v>
       </c>
       <c r="F9" s="3">
-        <v>1904000</v>
+        <v>11736000</v>
       </c>
       <c r="G9" s="3">
-        <v>1841000</v>
+        <v>10970000</v>
       </c>
       <c r="H9" s="3">
-        <v>1789000</v>
+        <v>12340000</v>
       </c>
       <c r="I9" s="3">
-        <v>1744000</v>
+        <v>13774000</v>
       </c>
       <c r="J9" s="3">
+        <v>12335000</v>
+      </c>
+      <c r="K9" s="3">
         <v>1725000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1683000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1618000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1608000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1602000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1582000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1545000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1523000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1382000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1386000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1344000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1365000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1382000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1425000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1362000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1364000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1336000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1317000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1296000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1273000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1239000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1200000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1176000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1169000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1157000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1138000</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>13713000</v>
+        <v>3864000</v>
       </c>
       <c r="E10" s="3">
-        <v>13320000</v>
+        <v>2621000</v>
       </c>
       <c r="F10" s="3">
-        <v>12928000</v>
+        <v>3523000</v>
       </c>
       <c r="G10" s="3">
-        <v>12656000</v>
+        <v>3862000</v>
       </c>
       <c r="H10" s="3">
-        <v>12190000</v>
+        <v>2157000</v>
       </c>
       <c r="I10" s="3">
-        <v>12042000</v>
+        <v>205000</v>
       </c>
       <c r="J10" s="3">
+        <v>1451000</v>
+      </c>
+      <c r="K10" s="3">
         <v>11923000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>11525000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>10601000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>10728000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>11409000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>10898000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>11101000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>10928000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>9580000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>9292000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>9059000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>8501000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>10094000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>9660000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>9794000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>9642000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>8150000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>9152000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>8807000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>8497000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>8615000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>8486000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>8458000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>8327000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>8193000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>8156000</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1122,8 +1134,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1223,8 +1236,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1324,171 +1340,177 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E14" s="3">
         <v>13000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>10000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>28000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>87000</v>
-      </c>
-      <c r="H14" s="3">
-        <v>27000</v>
       </c>
       <c r="I14" s="3">
         <v>27000</v>
       </c>
       <c r="J14" s="3">
+        <v>27000</v>
+      </c>
+      <c r="K14" s="3">
         <v>24000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>14000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>12000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>25000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>23000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>100000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>73000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>39000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>195000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>750000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>213000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>66000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>16000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>74000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>33000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>15000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>16000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>25000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>18000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>163000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>39000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>88000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>70000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>80000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>77000</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>71000</v>
+      </c>
+      <c r="E15" s="3">
         <v>70000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>69000</v>
-      </c>
-      <c r="F15" s="3">
-        <v>83000</v>
       </c>
       <c r="G15" s="3">
         <v>83000</v>
       </c>
       <c r="H15" s="3">
+        <v>83000</v>
+      </c>
+      <c r="I15" s="3">
         <v>82000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>81000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>89000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>90000</v>
-      </c>
-      <c r="L15" s="3">
-        <v>87000</v>
       </c>
       <c r="M15" s="3">
         <v>87000</v>
       </c>
       <c r="N15" s="3">
-        <v>109000</v>
+        <v>87000</v>
       </c>
       <c r="O15" s="3">
         <v>109000</v>
       </c>
       <c r="P15" s="3">
+        <v>109000</v>
+      </c>
+      <c r="Q15" s="3">
         <v>105000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>53000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>30000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>31000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>29000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>28000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>30000</v>
-      </c>
-      <c r="W15" s="3">
-        <v>32000</v>
       </c>
       <c r="X15" s="3">
         <v>32000</v>
@@ -1497,19 +1519,19 @@
         <v>32000</v>
       </c>
       <c r="Z15" s="3">
+        <v>32000</v>
+      </c>
+      <c r="AA15" s="3">
         <v>36000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>24000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>23000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>22000</v>
-      </c>
-      <c r="AD15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE15" s="3" t="s">
         <v>8</v>
@@ -1517,8 +1539,8 @@
       <c r="AF15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG15" s="3">
-        <v>0</v>
+      <c r="AG15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH15" s="3">
         <v>0</v>
@@ -1526,8 +1548,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1560,210 +1585,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>15284000</v>
+        <v>15077000</v>
       </c>
       <c r="E17" s="3">
-        <v>13795000</v>
+        <v>15173000</v>
       </c>
       <c r="F17" s="3">
-        <v>13005000</v>
+        <v>13688000</v>
       </c>
       <c r="G17" s="3">
-        <v>14518000</v>
+        <v>12870000</v>
       </c>
       <c r="H17" s="3">
-        <v>15727000</v>
+        <v>14343000</v>
       </c>
       <c r="I17" s="3">
-        <v>14192000</v>
+        <v>15602000</v>
       </c>
       <c r="J17" s="3">
+        <v>14079000</v>
+      </c>
+      <c r="K17" s="3">
         <v>14058000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>14118000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>13530000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>11535000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>11618000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>12254000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>10849000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>9419000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>8098000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>9150000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>9024000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>8835000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>9245000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>9925000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>10078000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>9386000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>10196000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>9291000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>9206000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>8507000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>8697000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>8715000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>8783000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>8484000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>8092000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>8529000</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>430000</v>
+        <v>1550000</v>
       </c>
       <c r="E18" s="3">
-        <v>1464000</v>
+        <v>541000</v>
       </c>
       <c r="F18" s="3">
-        <v>1827000</v>
+        <v>1571000</v>
       </c>
       <c r="G18" s="3">
-        <v>-21000</v>
+        <v>1962000</v>
       </c>
       <c r="H18" s="3">
-        <v>-1748000</v>
+        <v>154000</v>
       </c>
       <c r="I18" s="3">
-        <v>-406000</v>
+        <v>-1623000</v>
       </c>
       <c r="J18" s="3">
+        <v>-293000</v>
+      </c>
+      <c r="K18" s="3">
         <v>-410000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-910000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1311000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>801000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1393000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>226000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1797000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3032000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2864000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1528000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1379000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1031000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2231000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1160000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1078000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1620000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-710000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1178000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>897000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1263000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1157000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>971000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>851000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1012000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1258000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>765000</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1799,31 +1831,32 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1900,132 +1933,138 @@
       <c r="AI20" s="3">
         <v>0</v>
       </c>
+      <c r="AJ20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>562000</v>
+        <v>1621000</v>
       </c>
       <c r="E21" s="3">
-        <v>1596000</v>
+        <v>611000</v>
       </c>
       <c r="F21" s="3">
-        <v>1992000</v>
+        <v>1640000</v>
       </c>
       <c r="G21" s="3">
-        <v>155000</v>
+        <v>2045000</v>
       </c>
       <c r="H21" s="3">
-        <v>-1562000</v>
+        <v>237000</v>
       </c>
       <c r="I21" s="3">
-        <v>-229000</v>
+        <v>-1541000</v>
       </c>
       <c r="J21" s="3">
+        <v>-212000</v>
+      </c>
+      <c r="K21" s="3">
         <v>-209000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-716000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-1095000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1037000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1661000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>473000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2108000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>3292000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>3050000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1710000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1542000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1186000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2402000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1319000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1238000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1777000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-575000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1306000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1023000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1385000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1282000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1091000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>970000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1131000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1355000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>862000</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>104000</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>98000</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
+        <v>97000</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
+        <v>107000</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
+        <v>88000</v>
       </c>
       <c r="I22" s="3">
-        <v>0</v>
+        <v>98000</v>
       </c>
       <c r="J22" s="3">
-        <v>0</v>
+        <v>86000</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -2102,210 +2141,219 @@
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1418000</v>
+      </c>
+      <c r="E23" s="3">
         <v>430000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1464000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1827000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-21000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1748000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-406000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-410000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-910000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1311000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>801000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1393000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>226000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1797000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3032000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2864000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1528000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1379000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1031000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2231000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1160000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1078000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1620000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-710000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1178000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>897000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1263000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1157000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>971000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>851000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1012000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1258000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>765000</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>254000</v>
+      </c>
+      <c r="E24" s="3">
         <v>83000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>266000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>340000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-17000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-373000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-85000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-114000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-236000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-289000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>151000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>281000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>20000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>362000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>626000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>594000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>312000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>273000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>194000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>458000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>229000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>227000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>328000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-170000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>230000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>180000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>257000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>414000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>305000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>272000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>317000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>418000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>245000</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2405,210 +2453,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1164000</v>
+      </c>
+      <c r="E26" s="3">
         <v>347000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1198000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1487000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-4000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1375000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-321000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-296000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-674000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1022000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>650000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1112000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>206000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1435000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2406000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2270000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1216000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1106000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>837000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1773000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>931000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>851000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1292000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-540000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>948000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>717000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1006000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>743000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>666000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>579000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>695000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>840000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>520000</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1161000</v>
+      </c>
+      <c r="E27" s="3">
         <v>301000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1189000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1460000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-41000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1389000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-346000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-303000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-685000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1040000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>634000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1111000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>183000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1399000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2385000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2244000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1189000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1080000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>801000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1707000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>889000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>821000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1261000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-583000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>911000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>678000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>977000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>714000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>637000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>550000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>666000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>811000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>491000</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2708,35 +2765,38 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
       <c r="L29" s="3">
         <v>0</v>
       </c>
@@ -2744,31 +2804,31 @@
         <v>0</v>
       </c>
       <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
         <v>-321000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>325000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>196000</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-3793000</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>354000</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-63000</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>144000</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-288000</v>
-      </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>8</v>
@@ -2779,23 +2839,23 @@
       <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="Z29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA29" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>31000</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE29" s="3">
         <v>506000</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
@@ -2809,8 +2869,11 @@
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2910,8 +2973,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3011,31 +3077,34 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -3112,109 +3181,115 @@
       <c r="AI32" s="3">
         <v>0</v>
       </c>
+      <c r="AJ32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>301000</v>
+        <v>1190000</v>
       </c>
       <c r="E33" s="3">
-        <v>1189000</v>
+        <v>331000</v>
       </c>
       <c r="F33" s="3">
-        <v>1460000</v>
+        <v>1218000</v>
       </c>
       <c r="G33" s="3">
-        <v>-41000</v>
+        <v>1489000</v>
       </c>
       <c r="H33" s="3">
-        <v>-1389000</v>
+        <v>-5000</v>
       </c>
       <c r="I33" s="3">
-        <v>-346000</v>
+        <v>-1352000</v>
       </c>
       <c r="J33" s="3">
+        <v>-320000</v>
+      </c>
+      <c r="K33" s="3">
         <v>-303000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-685000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1040000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>634000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>790000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>508000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1595000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1408000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2598000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1126000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1224000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>513000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1707000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>889000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>821000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1261000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-585000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>942000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>678000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>977000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1220000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>637000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>550000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>666000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>811000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>491000</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3314,215 +3389,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>301000</v>
+        <v>1190000</v>
       </c>
       <c r="E35" s="3">
-        <v>1189000</v>
+        <v>331000</v>
       </c>
       <c r="F35" s="3">
-        <v>1460000</v>
+        <v>1218000</v>
       </c>
       <c r="G35" s="3">
-        <v>-41000</v>
+        <v>1489000</v>
       </c>
       <c r="H35" s="3">
-        <v>-1389000</v>
+        <v>-5000</v>
       </c>
       <c r="I35" s="3">
-        <v>-346000</v>
+        <v>-1352000</v>
       </c>
       <c r="J35" s="3">
+        <v>-320000</v>
+      </c>
+      <c r="K35" s="3">
         <v>-303000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-685000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1040000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>634000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>790000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>508000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1595000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1408000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2598000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1126000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1224000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>513000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1707000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>889000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>821000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1261000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-585000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>942000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>678000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>977000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1220000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>637000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>550000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>666000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>811000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>491000</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3558,8 +3642,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3595,132 +3680,136 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>816000</v>
+      </c>
+      <c r="E41" s="3">
         <v>599000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>850000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>722000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>860000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>699000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>662000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>736000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>786000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>766000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1130000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>763000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>690000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>656000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>709000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>377000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>370000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>547000</v>
-      </c>
-      <c r="U41" s="3">
-        <v>338000</v>
       </c>
       <c r="V41" s="3">
         <v>338000</v>
       </c>
       <c r="W41" s="3">
+        <v>338000</v>
+      </c>
+      <c r="X41" s="3">
         <v>587000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>599000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>551000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>499000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>460000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>489000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>450000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>617000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>690000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>482000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>442000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>436000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>389000</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>6995000</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>5289000</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>4319000</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>5146000</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>3369000</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>5137000</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>6724000</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -3797,132 +3886,138 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>11041000</v>
+      </c>
+      <c r="E43" s="3">
         <v>10762000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>10573000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>10044000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>10102000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>9713000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>9483000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>9165000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>9150000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>8824000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>8874000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>8364000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>8406000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>8146000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>7921000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>6479000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>6609000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>6367000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>6401000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>6472000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>6558000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>6380000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>6201000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>6154000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>6196000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>5953000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>5856000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>5786000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>5922000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>5693000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>5649000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>5597000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>5799000</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3999,31 +4094,34 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>12904000</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>9461000</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>9416000</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>9473000</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>9731000</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>9728000</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>10088000</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -4100,31 +4198,34 @@
       <c r="AI45" s="3">
         <v>0</v>
       </c>
+      <c r="AJ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>31756000</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>26111000</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>25158000</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>25385000</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>24062000</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>25277000</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>26957000</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -4201,257 +4302,266 @@
       <c r="AI46" s="3">
         <v>0</v>
       </c>
+      <c r="AJ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>70604000</v>
+        <v>64978000</v>
       </c>
       <c r="E47" s="3">
-        <v>67859000</v>
+        <v>63524000</v>
       </c>
       <c r="F47" s="3">
-        <v>66677000</v>
+        <v>61724000</v>
       </c>
       <c r="G47" s="3">
-        <v>63359000</v>
+        <v>59658000</v>
       </c>
       <c r="H47" s="3">
-        <v>63668000</v>
+        <v>57656000</v>
       </c>
       <c r="I47" s="3">
-        <v>63475000</v>
+        <v>56095000</v>
       </c>
       <c r="J47" s="3">
+        <v>54354000</v>
+      </c>
+      <c r="K47" s="3">
         <v>61829000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>61006000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>61055000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>61768000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>64701000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>61840000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>62570000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>60076000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>94237000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>91197000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>89637000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>84783000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>88221000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>89158000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>86345000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>84018000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>81136000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>83855000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>83140000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>83195000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>82677000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>82680000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>81203000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>81050000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>81707000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>81038000</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>714000</v>
+      </c>
+      <c r="E48" s="3">
         <v>777000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>802000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1022000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>909000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>945000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>971000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1221000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1008000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>975000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>966000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1253000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>965000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1026000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1002000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1057000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1076000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1100000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1123000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1628000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1535000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1519000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1521000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1045000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1032000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1040000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1060000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1072000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1067000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1072000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1067000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1065000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1013000</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>3502000</v>
+        <v>8957000</v>
       </c>
       <c r="E49" s="3">
-        <v>3502000</v>
+        <v>9614000</v>
       </c>
       <c r="F49" s="3">
-        <v>3502000</v>
+        <v>9448000</v>
       </c>
       <c r="G49" s="3">
-        <v>3502000</v>
+        <v>10408000</v>
       </c>
       <c r="H49" s="3">
-        <v>3502000</v>
+        <v>9326000</v>
       </c>
       <c r="I49" s="3">
-        <v>3502000</v>
+        <v>9109000</v>
       </c>
       <c r="J49" s="3">
-        <v>3502000</v>
+        <v>8973000</v>
       </c>
       <c r="K49" s="3">
         <v>3502000</v>
       </c>
       <c r="L49" s="3">
+        <v>3502000</v>
+      </c>
+      <c r="M49" s="3">
         <v>3496000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3497000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3502000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3389000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3349000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3350000</v>
-      </c>
-      <c r="R49" s="3">
-        <v>2544000</v>
       </c>
       <c r="S49" s="3">
         <v>2544000</v>
@@ -4463,22 +4573,22 @@
         <v>2544000</v>
       </c>
       <c r="V49" s="3">
-        <v>2545000</v>
+        <v>2544000</v>
       </c>
       <c r="W49" s="3">
         <v>2545000</v>
       </c>
       <c r="X49" s="3">
-        <v>2547000</v>
+        <v>2545000</v>
       </c>
       <c r="Y49" s="3">
         <v>2547000</v>
       </c>
       <c r="Z49" s="3">
+        <v>2547000</v>
+      </c>
+      <c r="AA49" s="3">
         <v>2530000</v>
-      </c>
-      <c r="AA49" s="3">
-        <v>2189000</v>
       </c>
       <c r="AB49" s="3">
         <v>2189000</v>
@@ -4487,25 +4597,28 @@
         <v>2189000</v>
       </c>
       <c r="AD49" s="3">
+        <v>2189000</v>
+      </c>
+      <c r="AE49" s="3">
         <v>2181000</v>
-      </c>
-      <c r="AE49" s="3">
-        <v>2309000</v>
       </c>
       <c r="AF49" s="3">
         <v>2309000</v>
       </c>
       <c r="AG49" s="3">
+        <v>2309000</v>
+      </c>
+      <c r="AH49" s="3">
         <v>2295000</v>
-      </c>
-      <c r="AH49" s="3">
-        <v>1219000</v>
       </c>
       <c r="AI49" s="3">
         <v>1219000</v>
       </c>
+      <c r="AJ49" s="3">
+        <v>1219000</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4605,8 +4718,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4706,55 +4822,58 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>212000</v>
+        <v>6386000</v>
       </c>
       <c r="E52" s="3">
-        <v>161000</v>
+        <v>7046000</v>
       </c>
       <c r="F52" s="3">
-        <v>219000</v>
+        <v>6849000</v>
       </c>
       <c r="G52" s="3">
-        <v>816000</v>
+        <v>5505000</v>
       </c>
       <c r="H52" s="3">
-        <v>480000</v>
+        <v>6776000</v>
       </c>
       <c r="I52" s="3">
-        <v>345000</v>
+        <v>6997000</v>
       </c>
       <c r="J52" s="3">
+        <v>6432000</v>
+      </c>
+      <c r="K52" s="3">
         <v>382000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>492000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>118000</v>
       </c>
-      <c r="M52" s="3" t="s">
+      <c r="N52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N52" s="3">
-        <v>0</v>
-      </c>
       <c r="O52" s="3">
+        <v>0</v>
+      </c>
+      <c r="P52" s="3">
         <v>36803000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>36969000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>36829000</v>
-      </c>
-      <c r="R52" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="S52" s="3" t="s">
         <v>8</v>
@@ -4771,8 +4890,8 @@
       <c r="W52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X52" s="3">
-        <v>0</v>
+      <c r="X52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y52" s="3">
         <v>0</v>
@@ -4807,8 +4926,11 @@
       <c r="AI52" s="3">
         <v>0</v>
       </c>
+      <c r="AJ52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4908,109 +5030,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>113743000</v>
+      </c>
+      <c r="E54" s="3">
         <v>108368000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>105241000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>103362000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>101176000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>100514000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>99631000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>97989000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>97676000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>96350000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>97150000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>99440000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>133440000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>132643000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>129811000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>125987000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>122750000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>121266000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>116107000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>119950000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>121073000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>118374000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>115834000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>112249000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>114490000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>113369000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>113289000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>112422000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>113632000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>110865000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>110243000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>108610000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>108537000</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5046,8 +5174,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5083,31 +5212,32 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>0</v>
+        <v>44470000</v>
       </c>
       <c r="E57" s="3">
-        <v>0</v>
+        <v>43128000</v>
       </c>
       <c r="F57" s="3">
-        <v>0</v>
+        <v>41634000</v>
       </c>
       <c r="G57" s="3">
-        <v>0</v>
+        <v>41211000</v>
       </c>
       <c r="H57" s="3">
-        <v>0</v>
+        <v>42139000</v>
       </c>
       <c r="I57" s="3">
-        <v>0</v>
+        <v>41918000</v>
       </c>
       <c r="J57" s="3">
-        <v>0</v>
+        <v>39977000</v>
       </c>
       <c r="K57" s="3">
         <v>0</v>
@@ -5184,31 +5314,34 @@
       <c r="AI57" s="3">
         <v>0</v>
       </c>
+      <c r="AJ57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>443000</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -5285,132 +5418,138 @@
       <c r="AI58" s="3">
         <v>0</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>28164000</v>
+        <v>29230000</v>
       </c>
       <c r="E59" s="3">
-        <v>27160000</v>
+        <v>25932000</v>
       </c>
       <c r="F59" s="3">
-        <v>27209000</v>
+        <v>24945000</v>
       </c>
       <c r="G59" s="3">
-        <v>26711000</v>
+        <v>24714000</v>
       </c>
       <c r="H59" s="3">
-        <v>25575000</v>
+        <v>24527000</v>
       </c>
       <c r="I59" s="3">
-        <v>24715000</v>
+        <v>23380000</v>
       </c>
       <c r="J59" s="3">
+        <v>22502000</v>
+      </c>
+      <c r="K59" s="3">
         <v>24843000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>24211000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>23229000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>22429000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>22490000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>21753000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>20853000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>20274000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>49274000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>49140000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>48221000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>46664000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>48503000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>48555000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>48232000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>48055000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>47670000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>48313000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>47936000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>47972000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>48614000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>48542000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>48216000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>48129000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>48185000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>48745000</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>73709000</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>69062000</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>66581000</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>66368000</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>66668000</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>65300000</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>62482000</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -5487,132 +5626,138 @@
       <c r="AI60" s="3">
         <v>0</v>
       </c>
+      <c r="AJ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>8083000</v>
+      </c>
+      <c r="E61" s="3">
         <v>8082000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7938000</v>
       </c>
-      <c r="F61" s="3">
-        <v>7942000</v>
-      </c>
       <c r="G61" s="3">
+        <v>7765000</v>
+      </c>
+      <c r="H61" s="3">
         <v>7946000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>7949000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>8452000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>7964000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>7967000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>7970000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>7973000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>7976000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>7980000</v>
-      </c>
-      <c r="P61" s="3">
-        <v>7996000</v>
       </c>
       <c r="Q61" s="3">
         <v>7996000</v>
       </c>
       <c r="R61" s="3">
+        <v>7996000</v>
+      </c>
+      <c r="S61" s="3">
         <v>7825000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>6635000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>6634000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>6633000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>6631000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>6630000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>6628000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>6453000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>6451000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>6450000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>6448000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>6847000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>6350000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>6349000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>6348000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>6346000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>6347000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>5110000</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>10902000</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
+        <v>12651000</v>
       </c>
       <c r="F62" s="3">
-        <v>0</v>
+        <v>12242000</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
+        <v>11414000</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
+        <v>12115000</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
+        <v>11893000</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>11324000</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -5621,76 +5766,79 @@
         <v>0</v>
       </c>
       <c r="M62" s="3">
+        <v>0</v>
+      </c>
+      <c r="N62" s="3">
         <v>402000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>833000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>33132000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>33533000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>33876000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1355000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>905000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>842000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>331000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1154000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1079000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>997000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>817000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>425000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>660000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>723000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>725000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>782000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1249000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1104000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>833000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>487000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>935000</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5790,8 +5938,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5891,8 +6042,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5992,109 +6146,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>89775000</v>
+        <v>92905000</v>
       </c>
       <c r="E66" s="3">
-        <v>86602000</v>
+        <v>89795000</v>
       </c>
       <c r="F66" s="3">
-        <v>85592000</v>
+        <v>86761000</v>
       </c>
       <c r="G66" s="3">
-        <v>86583000</v>
+        <v>85732000</v>
       </c>
       <c r="H66" s="3">
-        <v>84997000</v>
+        <v>86729000</v>
       </c>
       <c r="I66" s="3">
-        <v>82137000</v>
+        <v>85142000</v>
       </c>
       <c r="J66" s="3">
+        <v>82258000</v>
+      </c>
+      <c r="K66" s="3">
         <v>80501000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>80003000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>76235000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>73938000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>74261000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>106711000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>104436000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>102992000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>95770000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>95487000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>94280000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>91934000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>93952000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>94933000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>93898000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>92416000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>90937000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>90857000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>90247000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>90012000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>89871000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>91513000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>89364000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>89085000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>88037000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>87603000</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6130,8 +6290,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6231,8 +6392,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6332,8 +6496,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6353,7 +6520,7 @@
         <v>2001000</v>
       </c>
       <c r="I70" s="3">
-        <v>1970000</v>
+        <v>2001000</v>
       </c>
       <c r="J70" s="3">
         <v>1970000</v>
@@ -6374,13 +6541,13 @@
         <v>1970000</v>
       </c>
       <c r="P70" s="3">
-        <v>2170000</v>
+        <v>1970000</v>
       </c>
       <c r="Q70" s="3">
         <v>2170000</v>
       </c>
       <c r="R70" s="3">
-        <v>1970000</v>
+        <v>2170000</v>
       </c>
       <c r="S70" s="3">
         <v>1970000</v>
@@ -6392,13 +6559,13 @@
         <v>1970000</v>
       </c>
       <c r="V70" s="3">
+        <v>1970000</v>
+      </c>
+      <c r="W70" s="3">
         <v>2248000</v>
       </c>
-      <c r="W70" s="3">
+      <c r="X70" s="3">
         <v>3052000</v>
-      </c>
-      <c r="X70" s="3">
-        <v>1930000</v>
       </c>
       <c r="Y70" s="3">
         <v>1930000</v>
@@ -6407,7 +6574,7 @@
         <v>1930000</v>
       </c>
       <c r="AA70" s="3">
-        <v>2303000</v>
+        <v>1930000</v>
       </c>
       <c r="AB70" s="3">
         <v>2303000</v>
@@ -6416,7 +6583,7 @@
         <v>2303000</v>
       </c>
       <c r="AD70" s="3">
-        <v>1746000</v>
+        <v>2303000</v>
       </c>
       <c r="AE70" s="3">
         <v>1746000</v>
@@ -6433,8 +6600,11 @@
       <c r="AI70" s="3">
         <v>1746000</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>1746000</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6534,109 +6704,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>51635000</v>
+      </c>
+      <c r="E72" s="3">
         <v>50718000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>50662000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>49716000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>48491000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>48766000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>50388000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>50970000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>51490000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>52412000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>53688000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>53294000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>52736000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>52464000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>51107000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>52767000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>50336000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>49380000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>48326000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>48074000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>46527000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>45803000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>45148000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>45708000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>46178000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>45508000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>45031000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>43162000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>42125000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>41622000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>41208000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>40678000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>39990000</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6736,8 +6912,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6837,8 +7016,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6938,109 +7120,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>18876000</v>
+      </c>
+      <c r="E76" s="3">
         <v>16592000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>16638000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>15769000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>12592000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>13516000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>15524000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>15518000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>15703000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>18145000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>21242000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>23209000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>24759000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>26037000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>24649000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>28247000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>25293000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>25016000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>22203000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>23750000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>23088000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>22546000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>21488000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>19382000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>21330000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>20819000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>20974000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>20805000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>20373000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>19755000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>19412000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>18827000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>19188000</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7140,215 +7328,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>301000</v>
+        <v>1190000</v>
       </c>
       <c r="E81" s="3">
-        <v>1189000</v>
+        <v>331000</v>
       </c>
       <c r="F81" s="3">
-        <v>1460000</v>
+        <v>1218000</v>
       </c>
       <c r="G81" s="3">
-        <v>-41000</v>
+        <v>1489000</v>
       </c>
       <c r="H81" s="3">
-        <v>-1389000</v>
+        <v>-5000</v>
       </c>
       <c r="I81" s="3">
-        <v>-346000</v>
+        <v>-1352000</v>
       </c>
       <c r="J81" s="3">
+        <v>-320000</v>
+      </c>
+      <c r="K81" s="3">
         <v>-303000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-685000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1040000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>634000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>790000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>508000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1595000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1408000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2598000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1126000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1224000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>513000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1707000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>889000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>821000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1261000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-585000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>942000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>678000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>977000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1220000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>637000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>550000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>666000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>811000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>491000</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7384,109 +7581,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>132000</v>
+        <v>93000</v>
       </c>
       <c r="E83" s="3">
-        <v>132000</v>
+        <v>104000</v>
       </c>
       <c r="F83" s="3">
-        <v>165000</v>
+        <v>96000</v>
       </c>
       <c r="G83" s="3">
-        <v>176000</v>
+        <v>112000</v>
       </c>
       <c r="H83" s="3">
+        <v>104000</v>
+      </c>
+      <c r="I83" s="3">
+        <v>129000</v>
+      </c>
+      <c r="J83" s="3">
+        <v>149000</v>
+      </c>
+      <c r="K83" s="3">
+        <v>201000</v>
+      </c>
+      <c r="L83" s="3">
+        <v>194000</v>
+      </c>
+      <c r="M83" s="3">
+        <v>216000</v>
+      </c>
+      <c r="N83" s="3">
+        <v>236000</v>
+      </c>
+      <c r="O83" s="3">
+        <v>268000</v>
+      </c>
+      <c r="P83" s="3">
+        <v>247000</v>
+      </c>
+      <c r="Q83" s="3">
+        <v>311000</v>
+      </c>
+      <c r="R83" s="3">
+        <v>260000</v>
+      </c>
+      <c r="S83" s="3">
         <v>186000</v>
       </c>
-      <c r="I83" s="3">
-        <v>177000</v>
-      </c>
-      <c r="J83" s="3">
-        <v>201000</v>
-      </c>
-      <c r="K83" s="3">
-        <v>194000</v>
-      </c>
-      <c r="L83" s="3">
-        <v>216000</v>
-      </c>
-      <c r="M83" s="3">
-        <v>236000</v>
-      </c>
-      <c r="N83" s="3">
-        <v>268000</v>
-      </c>
-      <c r="O83" s="3">
-        <v>247000</v>
-      </c>
-      <c r="P83" s="3">
-        <v>311000</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>260000</v>
-      </c>
-      <c r="R83" s="3">
-        <v>186000</v>
-      </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>182000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>163000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>155000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>171000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>159000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>160000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>157000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>135000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>128000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>126000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>122000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>125000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>120000</v>
-      </c>
-      <c r="AF83" s="3">
-        <v>119000</v>
       </c>
       <c r="AG83" s="3">
         <v>119000</v>
       </c>
       <c r="AH83" s="3">
-        <v>97000</v>
+        <v>119000</v>
       </c>
       <c r="AI83" s="3">
         <v>97000</v>
       </c>
+      <c r="AJ83" s="3">
+        <v>97000</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7586,8 +7787,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7687,8 +7891,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7788,8 +7995,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7889,8 +8099,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7990,109 +8203,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3201000</v>
+      </c>
+      <c r="E89" s="3">
         <v>2359000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1666000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1225000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1233000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1169000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>601000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>970000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2046000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1673000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>432000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>871000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1329000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1551000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1365000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1319000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1296000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1849000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1027000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1234000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1833000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1348000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>714000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1357000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1728000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1464000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>626000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1100000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1866000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>491000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>857000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1251000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1384000</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8128,109 +8347,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-63000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-56000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-41000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-71000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-55000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-62000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-79000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-68000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-124000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-98000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-130000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-59000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-89000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-136000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-61000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-73000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-69000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-101000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-65000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-140000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-120000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-93000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-80000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-82000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-67000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-66000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-62000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-83000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-70000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-72000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-74000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-123000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8330,8 +8553,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8431,109 +8657,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2685000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2524000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1372000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1105000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-845000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-253000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-796000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-447000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1143000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1119000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>981000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>221000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>446000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-670000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>513000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2198000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-285000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1026000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>68000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>428000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2093000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-879000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-263000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>737000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1145000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-60000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1251000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-140000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1127000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>337000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-280000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1868000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-834000</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8569,109 +8801,113 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-243000</v>
+        <v>243000</v>
       </c>
       <c r="E96" s="3">
-        <v>-233000</v>
+        <v>243000</v>
       </c>
       <c r="F96" s="3">
-        <v>-233000</v>
+        <v>233000</v>
       </c>
       <c r="G96" s="3">
-        <v>-233000</v>
+        <v>233000</v>
       </c>
       <c r="H96" s="3">
+        <v>233000</v>
+      </c>
+      <c r="I96" s="3">
+        <v>235000</v>
+      </c>
+      <c r="J96" s="3">
+        <v>224000</v>
+      </c>
+      <c r="K96" s="3">
+        <v>-228000</v>
+      </c>
+      <c r="L96" s="3">
+        <v>-232000</v>
+      </c>
+      <c r="M96" s="3">
+        <v>-236000</v>
+      </c>
+      <c r="N96" s="3">
+        <v>-230000</v>
+      </c>
+      <c r="O96" s="3">
         <v>-235000</v>
       </c>
-      <c r="I96" s="3">
-        <v>-224000</v>
-      </c>
-      <c r="J96" s="3">
-        <v>-228000</v>
-      </c>
-      <c r="K96" s="3">
-        <v>-232000</v>
-      </c>
-      <c r="L96" s="3">
-        <v>-236000</v>
-      </c>
-      <c r="M96" s="3">
-        <v>-230000</v>
-      </c>
-      <c r="N96" s="3">
-        <v>-235000</v>
-      </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-241000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-245000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-164000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-168000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-169000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-172000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-159000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-163000</v>
-      </c>
-      <c r="W96" s="3">
-        <v>-166000</v>
       </c>
       <c r="X96" s="3">
         <v>-166000</v>
       </c>
       <c r="Y96" s="3">
+        <v>-166000</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-158000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-159000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-160000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-163000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-132000</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>-134000</v>
       </c>
       <c r="AE96" s="3">
         <v>-134000</v>
       </c>
       <c r="AF96" s="3">
+        <v>-134000</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-135000</v>
-      </c>
-      <c r="AG96" s="3">
-        <v>-122000</v>
       </c>
       <c r="AH96" s="3">
         <v>-122000</v>
       </c>
       <c r="AI96" s="3">
+        <v>-122000</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-124000</v>
       </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8771,8 +9007,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8872,8 +9111,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8973,132 +9215,138 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-185000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-86000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-166000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-258000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-227000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-879000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>121000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-573000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-883000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-918000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1046000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1175000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1743000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-842000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1480000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>886000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1188000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-614000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1095000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1911000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>248000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-421000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-399000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-2055000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-612000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1365000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>458000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1033000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-531000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-788000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-571000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>664000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-607000</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -9175,105 +9423,111 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>331000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-251000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>128000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-138000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>161000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>37000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-74000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-50000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>20000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-364000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>367000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-83000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>32000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>39000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>398000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>7000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-177000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>209000</v>
       </c>
-      <c r="U102" s="3">
-        <v>0</v>
-      </c>
       <c r="V102" s="3">
+        <v>0</v>
+      </c>
+      <c r="W102" s="3">
         <v>-249000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-12000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>48000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>52000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>39000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-29000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>39000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-167000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-73000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>208000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>40000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>6000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>47000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-57000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ALL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ALL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="92">
   <si>
     <t>ALL</t>
   </si>
@@ -656,449 +656,461 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="36" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="10" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="37" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>16506000</v>
+      </c>
+      <c r="E8" s="3">
         <v>16627000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>15714000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>15259000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>14832000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>14497000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>13979000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>13786000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>13648000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>13208000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>12219000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>12336000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>13011000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>12480000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>12646000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>12451000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>10962000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>10678000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>10403000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>9866000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>11476000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>11085000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>11156000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>11006000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>9486000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>10469000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>10103000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>9770000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>9854000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>9686000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>9634000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>9496000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>9350000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>9294000</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>11423000</v>
+      </c>
+      <c r="E9" s="3">
         <v>12763000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>13093000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>11736000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>10970000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>12340000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>13774000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>12335000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1725000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1683000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1618000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1608000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1602000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1582000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1545000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1523000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1382000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1386000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1344000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1365000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1382000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1425000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1362000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1364000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1336000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1317000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1296000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1273000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1239000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1200000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1176000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1169000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1157000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1138000</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>5083000</v>
+      </c>
+      <c r="E10" s="3">
         <v>3864000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2621000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3523000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3862000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2157000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>205000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1451000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>11923000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>11525000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>10601000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>10728000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>11409000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>10898000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>11101000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>10928000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>9580000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>9292000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>9059000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>8501000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>10094000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>9660000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>9794000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>9642000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>8150000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>9152000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>8807000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>8497000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>8615000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>8486000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>8458000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>8327000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>8193000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>8156000</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1135,8 +1147,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1239,8 +1252,11 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1343,177 +1359,183 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E14" s="3">
         <v>28000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>13000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>10000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>28000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>87000</v>
-      </c>
-      <c r="I14" s="3">
-        <v>27000</v>
       </c>
       <c r="J14" s="3">
         <v>27000</v>
       </c>
       <c r="K14" s="3">
+        <v>27000</v>
+      </c>
+      <c r="L14" s="3">
         <v>24000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>14000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>12000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>25000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>23000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>100000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>73000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>39000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>195000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>750000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>213000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>66000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>16000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>74000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>33000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>15000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>16000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>25000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>18000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>163000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>39000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>88000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>70000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>80000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>77000</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>70000</v>
+      </c>
+      <c r="E15" s="3">
         <v>71000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>70000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>69000</v>
-      </c>
-      <c r="G15" s="3">
-        <v>83000</v>
       </c>
       <c r="H15" s="3">
         <v>83000</v>
       </c>
       <c r="I15" s="3">
+        <v>83000</v>
+      </c>
+      <c r="J15" s="3">
         <v>82000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>81000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>89000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>90000</v>
-      </c>
-      <c r="M15" s="3">
-        <v>87000</v>
       </c>
       <c r="N15" s="3">
         <v>87000</v>
       </c>
       <c r="O15" s="3">
-        <v>109000</v>
+        <v>87000</v>
       </c>
       <c r="P15" s="3">
         <v>109000</v>
       </c>
       <c r="Q15" s="3">
+        <v>109000</v>
+      </c>
+      <c r="R15" s="3">
         <v>105000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>53000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>30000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>31000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>29000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>28000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>30000</v>
-      </c>
-      <c r="X15" s="3">
-        <v>32000</v>
       </c>
       <c r="Y15" s="3">
         <v>32000</v>
@@ -1522,19 +1544,19 @@
         <v>32000</v>
       </c>
       <c r="AA15" s="3">
+        <v>32000</v>
+      </c>
+      <c r="AB15" s="3">
         <v>36000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>24000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>23000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>22000</v>
-      </c>
-      <c r="AE15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AF15" s="3" t="s">
         <v>8</v>
@@ -1542,8 +1564,8 @@
       <c r="AG15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH15" s="3">
-        <v>0</v>
+      <c r="AH15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AI15" s="3">
         <v>0</v>
@@ -1551,8 +1573,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1586,216 +1611,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>13946000</v>
+      </c>
+      <c r="E17" s="3">
         <v>15077000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>15173000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>13688000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>12870000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>14343000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>15602000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>14079000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>14058000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>14118000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>13530000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>11535000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>11618000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>12254000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>10849000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>9419000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>8098000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>9150000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>9024000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>8835000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>9245000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>9925000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>10078000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>9386000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>10196000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>9291000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>9206000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>8507000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>8697000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>8715000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>8783000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>8484000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>8092000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>8529000</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2560000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1550000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>541000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1571000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1962000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>154000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1623000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-293000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-410000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-910000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1311000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>801000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1393000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>226000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1797000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>3032000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2864000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1528000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1379000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1031000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2231000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1160000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1078000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1620000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-710000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1178000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>897000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1263000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1157000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>971000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>851000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1012000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1258000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>765000</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1832,8 +1864,9 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1858,8 +1891,8 @@
       <c r="J20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
+      <c r="K20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L20" s="3">
         <v>0</v>
@@ -1936,139 +1969,145 @@
       <c r="AJ20" s="3">
         <v>0</v>
       </c>
+      <c r="AK20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2630000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1621000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>611000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1640000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2045000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>237000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-1541000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-212000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-209000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-716000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-1095000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1037000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1661000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>473000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2108000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>3292000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>3050000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1710000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1542000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1186000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2402000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1319000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1238000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1777000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-575000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1306000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1023000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1385000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1282000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1091000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>970000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1131000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1355000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>862000</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>101000</v>
+      </c>
+      <c r="E22" s="3">
         <v>104000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>98000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>97000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>107000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>88000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>98000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>86000</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
       <c r="L22" s="3">
         <v>0</v>
       </c>
@@ -2144,216 +2183,225 @@
       <c r="AJ22" s="3">
         <v>0</v>
       </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2449000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1418000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>430000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1464000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1827000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-21000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1748000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-406000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-410000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-910000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1311000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>801000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1393000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>226000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1797000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>3032000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2864000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1528000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1379000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1031000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2231000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1160000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1078000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1620000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-710000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1178000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>897000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1263000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1157000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>971000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>851000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1012000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1258000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>765000</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>559000</v>
+      </c>
+      <c r="E24" s="3">
         <v>254000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>83000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>266000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>340000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-17000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-373000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-85000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-114000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-236000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-289000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>151000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>281000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>20000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>362000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>626000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>594000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>312000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>273000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>194000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>458000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>229000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>227000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>328000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-170000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>230000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>180000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>257000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>414000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>305000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>272000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>317000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>418000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>245000</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2456,216 +2504,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1890000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1164000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>347000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1198000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1487000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-4000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1375000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-321000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-296000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-674000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1022000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>650000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1112000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>206000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1435000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2406000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2270000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1216000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1106000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>837000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1773000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>931000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>851000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1292000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-540000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>948000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>717000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1006000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>743000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>666000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>579000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>695000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>840000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>520000</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1899000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1161000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>301000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1189000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1460000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-41000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1389000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-346000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-303000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-685000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1040000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>634000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1111000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>183000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1399000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2385000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2244000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1189000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1080000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>801000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1707000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>889000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>821000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1261000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-583000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>911000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>678000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>977000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>714000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>637000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>550000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>666000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>811000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>491000</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2768,8 +2825,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2794,12 +2854,12 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
       <c r="M29" s="3">
         <v>0</v>
       </c>
@@ -2807,31 +2867,31 @@
         <v>0</v>
       </c>
       <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
         <v>-321000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>325000</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>196000</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-3793000</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>354000</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-63000</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>144000</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-288000</v>
-      </c>
-      <c r="W29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
@@ -2842,23 +2902,23 @@
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>31000</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF29" s="3">
         <v>506000</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
@@ -2872,8 +2932,11 @@
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2976,8 +3039,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3080,8 +3146,11 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3106,8 +3175,8 @@
       <c r="J32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
+      <c r="K32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L32" s="3">
         <v>0</v>
@@ -3184,112 +3253,118 @@
       <c r="AJ32" s="3">
         <v>0</v>
       </c>
+      <c r="AK32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1928000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1190000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>331000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1218000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1489000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-5000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1352000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-320000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-303000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-685000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1040000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>634000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>790000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>508000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1595000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1408000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2598000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1126000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1224000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>513000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1707000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>889000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>821000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1261000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-585000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>942000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>678000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>977000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1220000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>637000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>550000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>666000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>811000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>491000</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3392,221 +3467,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1928000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1190000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>331000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1218000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1489000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-5000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1352000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-320000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-303000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-685000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1040000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>634000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>790000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>508000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1595000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1408000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2598000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1126000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1224000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>513000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1707000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>889000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>821000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1261000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-585000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>942000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>678000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>977000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1220000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>637000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>550000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>666000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>811000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>491000</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3643,8 +3727,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3681,139 +3766,143 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>704000</v>
+      </c>
+      <c r="E41" s="3">
         <v>816000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>599000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>850000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>722000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>860000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>699000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>662000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>736000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>786000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>766000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1130000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>763000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>690000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>656000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>709000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>377000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>370000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>547000</v>
-      </c>
-      <c r="V41" s="3">
-        <v>338000</v>
       </c>
       <c r="W41" s="3">
         <v>338000</v>
       </c>
       <c r="X41" s="3">
+        <v>338000</v>
+      </c>
+      <c r="Y41" s="3">
         <v>587000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>599000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>551000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>499000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>460000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>489000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>450000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>617000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>690000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>482000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>442000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>436000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>389000</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>4537000</v>
+      </c>
+      <c r="E42" s="3">
         <v>6995000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>5289000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>4319000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>5146000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>3369000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>5137000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>6724000</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -3889,112 +3978,118 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>10614000</v>
+      </c>
+      <c r="E43" s="3">
         <v>11041000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>10762000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>10573000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>10044000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>10102000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>9713000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>9483000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>9165000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>9150000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>8824000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>8874000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>8364000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>8406000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>8146000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>7921000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>6479000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>6609000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>6367000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>6401000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>6472000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>6558000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>6380000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>6201000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>6154000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>6196000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>5953000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>5856000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>5786000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>5922000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>5693000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>5649000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>5597000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>5799000</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4019,8 +4114,8 @@
       <c r="J44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -4097,35 +4192,38 @@
       <c r="AJ44" s="3">
         <v>0</v>
       </c>
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>12765000</v>
+      </c>
+      <c r="E45" s="3">
         <v>12904000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>9461000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>9416000</v>
       </c>
-      <c r="G45" s="3">
-        <v>9473000</v>
-      </c>
       <c r="H45" s="3">
+        <v>9472000</v>
+      </c>
+      <c r="I45" s="3">
         <v>9731000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>9728000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>10088000</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
       <c r="L45" s="3">
         <v>0</v>
       </c>
@@ -4201,35 +4299,38 @@
       <c r="AJ45" s="3">
         <v>0</v>
       </c>
+      <c r="AK45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>28620000</v>
+      </c>
+      <c r="E46" s="3">
         <v>31756000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>26111000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>25158000</v>
       </c>
-      <c r="G46" s="3">
-        <v>25385000</v>
-      </c>
       <c r="H46" s="3">
+        <v>25384000</v>
+      </c>
+      <c r="I46" s="3">
         <v>24062000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>25277000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>26957000</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -4305,266 +4406,275 @@
       <c r="AJ46" s="3">
         <v>0</v>
       </c>
+      <c r="AK46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>66468000</v>
+      </c>
+      <c r="E47" s="3">
         <v>64978000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>63524000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>61724000</v>
       </c>
-      <c r="G47" s="3">
-        <v>59658000</v>
-      </c>
       <c r="H47" s="3">
+        <v>59659000</v>
+      </c>
+      <c r="I47" s="3">
         <v>57656000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>56095000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>54354000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>61829000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>61006000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>61055000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>61768000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>64701000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>61840000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>62570000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>60076000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>94237000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>91197000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>89637000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>84783000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>88221000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>89158000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>86345000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>84018000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>81136000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>83855000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>83140000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>83195000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>82677000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>82680000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>81203000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>81050000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>81707000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>81038000</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>834000</v>
+      </c>
+      <c r="E48" s="3">
         <v>714000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>777000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>802000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1022000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>909000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>945000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>971000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1221000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1008000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>975000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>966000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1253000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>965000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1026000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1002000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1057000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1076000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1100000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1123000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1628000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1535000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1519000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1521000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1045000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1032000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1040000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1060000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1072000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1067000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1072000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1067000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1065000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>1013000</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>9772000</v>
+      </c>
+      <c r="E49" s="3">
         <v>8957000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>9614000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>9448000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>10408000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>9326000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>9109000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8973000</v>
-      </c>
-      <c r="K49" s="3">
-        <v>3502000</v>
       </c>
       <c r="L49" s="3">
         <v>3502000</v>
       </c>
       <c r="M49" s="3">
+        <v>3502000</v>
+      </c>
+      <c r="N49" s="3">
         <v>3496000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3497000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3502000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3389000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3349000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3350000</v>
-      </c>
-      <c r="S49" s="3">
-        <v>2544000</v>
       </c>
       <c r="T49" s="3">
         <v>2544000</v>
@@ -4576,22 +4686,22 @@
         <v>2544000</v>
       </c>
       <c r="W49" s="3">
-        <v>2545000</v>
+        <v>2544000</v>
       </c>
       <c r="X49" s="3">
         <v>2545000</v>
       </c>
       <c r="Y49" s="3">
-        <v>2547000</v>
+        <v>2545000</v>
       </c>
       <c r="Z49" s="3">
         <v>2547000</v>
       </c>
       <c r="AA49" s="3">
+        <v>2547000</v>
+      </c>
+      <c r="AB49" s="3">
         <v>2530000</v>
-      </c>
-      <c r="AB49" s="3">
-        <v>2189000</v>
       </c>
       <c r="AC49" s="3">
         <v>2189000</v>
@@ -4600,25 +4710,28 @@
         <v>2189000</v>
       </c>
       <c r="AE49" s="3">
+        <v>2189000</v>
+      </c>
+      <c r="AF49" s="3">
         <v>2181000</v>
-      </c>
-      <c r="AF49" s="3">
-        <v>2309000</v>
       </c>
       <c r="AG49" s="3">
         <v>2309000</v>
       </c>
       <c r="AH49" s="3">
+        <v>2309000</v>
+      </c>
+      <c r="AI49" s="3">
         <v>2295000</v>
-      </c>
-      <c r="AI49" s="3">
-        <v>1219000</v>
       </c>
       <c r="AJ49" s="3">
         <v>1219000</v>
       </c>
+      <c r="AK49" s="3">
+        <v>1219000</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4721,8 +4834,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4825,58 +4941,61 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4707000</v>
+      </c>
+      <c r="E52" s="3">
         <v>6386000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>7046000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>6849000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5505000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>6776000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>6997000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>6432000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>382000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>492000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>118000</v>
       </c>
-      <c r="N52" s="3" t="s">
+      <c r="O52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
-      </c>
       <c r="P52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="3">
         <v>36803000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>36969000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>36829000</v>
-      </c>
-      <c r="S52" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="T52" s="3" t="s">
         <v>8</v>
@@ -4893,8 +5012,8 @@
       <c r="X52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y52" s="3">
-        <v>0</v>
+      <c r="Y52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z52" s="3">
         <v>0</v>
@@ -4929,8 +5048,11 @@
       <c r="AJ52" s="3">
         <v>0</v>
       </c>
+      <c r="AK52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5033,112 +5155,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>111617000</v>
+      </c>
+      <c r="E54" s="3">
         <v>113743000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>108368000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>105241000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>103362000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>101176000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>100514000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>99631000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>97989000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>97676000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>96350000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>97150000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>99440000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>133440000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>132643000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>129811000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>125987000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>122750000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>121266000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>116107000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>119950000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>121073000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>118374000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>115834000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>112249000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>114490000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>113369000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>113289000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>112422000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>113632000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>110865000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>110243000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>108610000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>108537000</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5175,8 +5303,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5213,35 +5342,36 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>43484000</v>
+      </c>
+      <c r="E57" s="3">
         <v>44470000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>43128000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>41634000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>41211000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>42139000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>41918000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>39977000</v>
       </c>
-      <c r="K57" s="3">
-        <v>0</v>
-      </c>
       <c r="L57" s="3">
         <v>0</v>
       </c>
@@ -5317,35 +5447,38 @@
       <c r="AJ57" s="3">
         <v>0</v>
       </c>
+      <c r="AK57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>684000</v>
+      </c>
+      <c r="E58" s="3">
         <v>9000</v>
-      </c>
-      <c r="E58" s="3">
-        <v>2000</v>
       </c>
       <c r="F58" s="3">
         <v>2000</v>
       </c>
       <c r="G58" s="3">
-        <v>443000</v>
+        <v>2000</v>
       </c>
       <c r="H58" s="3">
-        <v>2000</v>
+        <v>351000</v>
       </c>
       <c r="I58" s="3">
         <v>2000</v>
       </c>
       <c r="J58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="K58" s="3">
         <v>3000</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -5421,139 +5554,145 @@
       <c r="AJ58" s="3">
         <v>0</v>
       </c>
+      <c r="AK58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>29022000</v>
+      </c>
+      <c r="E59" s="3">
         <v>29230000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>25932000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>24945000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>24714000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>24527000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>23380000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>22502000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>24843000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>24211000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>23229000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>22429000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>22490000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>21753000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>20853000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>20274000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>49274000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>49140000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>48221000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>46664000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>48503000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>48555000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>48232000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>48055000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>47670000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>48313000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>47936000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>47972000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>48614000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>48542000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>48216000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>48129000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>48185000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>48745000</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>73190000</v>
+      </c>
+      <c r="E60" s="3">
         <v>73709000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>69062000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>66581000</v>
       </c>
-      <c r="G60" s="3">
-        <v>66368000</v>
-      </c>
       <c r="H60" s="3">
+        <v>66276000</v>
+      </c>
+      <c r="I60" s="3">
         <v>66668000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>65300000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>62482000</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -5629,139 +5768,145 @@
       <c r="AJ60" s="3">
         <v>0</v>
       </c>
+      <c r="AK60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7637000</v>
+      </c>
+      <c r="E61" s="3">
         <v>8083000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>8082000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7938000</v>
       </c>
-      <c r="G61" s="3">
-        <v>7765000</v>
-      </c>
       <c r="H61" s="3">
+        <v>7857000</v>
+      </c>
+      <c r="I61" s="3">
         <v>7946000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>7949000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>8452000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>7964000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>7967000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>7970000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>7973000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>7976000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>7980000</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>7996000</v>
       </c>
       <c r="R61" s="3">
         <v>7996000</v>
       </c>
       <c r="S61" s="3">
+        <v>7996000</v>
+      </c>
+      <c r="T61" s="3">
         <v>7825000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>6635000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>6634000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>6633000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>6631000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>6630000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>6628000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>6453000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>6451000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>6450000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>6448000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>6847000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>6350000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>6349000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>6348000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>6346000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>6347000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>5110000</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>9187000</v>
+      </c>
+      <c r="E62" s="3">
         <v>10902000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>12651000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>12242000</v>
       </c>
-      <c r="G62" s="3">
-        <v>11414000</v>
-      </c>
       <c r="H62" s="3">
+        <v>11270000</v>
+      </c>
+      <c r="I62" s="3">
         <v>12115000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>11893000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>11324000</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
@@ -5769,76 +5914,79 @@
         <v>0</v>
       </c>
       <c r="N62" s="3">
+        <v>0</v>
+      </c>
+      <c r="O62" s="3">
         <v>402000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>833000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>33132000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>33533000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>33876000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1355000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>905000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>842000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>331000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1154000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1079000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>997000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>817000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>425000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>660000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>723000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>725000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>782000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1249000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1104000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>833000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>487000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>935000</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5941,8 +6089,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6045,8 +6196,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6149,112 +6303,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>90250000</v>
+      </c>
+      <c r="E66" s="3">
         <v>92905000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>89795000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>86761000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>85732000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>86729000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>85142000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>82258000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>80501000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>80003000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>76235000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>73938000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>74261000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>106711000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>104436000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>102992000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>95770000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>95487000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>94280000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>91934000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>93952000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>94933000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>93898000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>92416000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>90937000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>90857000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>90247000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>90012000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>89871000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>91513000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>89364000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>89085000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>88037000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>87603000</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6291,8 +6451,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6395,8 +6556,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6499,8 +6663,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6523,7 +6690,7 @@
         <v>2001000</v>
       </c>
       <c r="J70" s="3">
-        <v>1970000</v>
+        <v>2001000</v>
       </c>
       <c r="K70" s="3">
         <v>1970000</v>
@@ -6544,13 +6711,13 @@
         <v>1970000</v>
       </c>
       <c r="Q70" s="3">
-        <v>2170000</v>
+        <v>1970000</v>
       </c>
       <c r="R70" s="3">
         <v>2170000</v>
       </c>
       <c r="S70" s="3">
-        <v>1970000</v>
+        <v>2170000</v>
       </c>
       <c r="T70" s="3">
         <v>1970000</v>
@@ -6562,13 +6729,13 @@
         <v>1970000</v>
       </c>
       <c r="W70" s="3">
+        <v>1970000</v>
+      </c>
+      <c r="X70" s="3">
         <v>2248000</v>
       </c>
-      <c r="X70" s="3">
+      <c r="Y70" s="3">
         <v>3052000</v>
-      </c>
-      <c r="Y70" s="3">
-        <v>1930000</v>
       </c>
       <c r="Z70" s="3">
         <v>1930000</v>
@@ -6577,7 +6744,7 @@
         <v>1930000</v>
       </c>
       <c r="AB70" s="3">
-        <v>2303000</v>
+        <v>1930000</v>
       </c>
       <c r="AC70" s="3">
         <v>2303000</v>
@@ -6586,7 +6753,7 @@
         <v>2303000</v>
       </c>
       <c r="AE70" s="3">
-        <v>1746000</v>
+        <v>2303000</v>
       </c>
       <c r="AF70" s="3">
         <v>1746000</v>
@@ -6603,8 +6770,11 @@
       <c r="AJ70" s="3">
         <v>1746000</v>
       </c>
+      <c r="AK70" s="3">
+        <v>1746000</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6707,112 +6877,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>53288000</v>
+      </c>
+      <c r="E72" s="3">
         <v>51635000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>50718000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>50662000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>49716000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>48491000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>48766000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>50388000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>50970000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>51490000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>52412000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>53688000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>53294000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>52736000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>52464000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>51107000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>52767000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>50336000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>49380000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>48326000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>48074000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>46527000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>45803000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>45148000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>45708000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>46178000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>45508000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>45031000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>43162000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>42125000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>41622000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>41208000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>40678000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>39990000</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6915,8 +7091,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7019,8 +7198,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7123,112 +7305,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>19441000</v>
+      </c>
+      <c r="E76" s="3">
         <v>18876000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>16592000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>16638000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>15769000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>12592000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>13516000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>15524000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>15518000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>15703000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>18145000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>21242000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>23209000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>24759000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>26037000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>24649000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>28247000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>25293000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>25016000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>22203000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>23750000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>23088000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>22546000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>21488000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>19382000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>21330000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>20819000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>20974000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>20805000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>20373000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>19755000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>19412000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>18827000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>19188000</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7331,221 +7519,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1928000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1190000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>331000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1218000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1489000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-5000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1352000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-320000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-303000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-685000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1040000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>634000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>790000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>508000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1595000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1408000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2598000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1126000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1224000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>513000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1707000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>889000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>821000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1261000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-585000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>942000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>678000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>977000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1220000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>637000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>550000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>666000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>811000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>491000</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7582,112 +7779,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>82000</v>
+      </c>
+      <c r="E83" s="3">
         <v>93000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>104000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>96000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>112000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>104000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>129000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>149000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>201000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>194000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>216000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>236000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>268000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>247000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>311000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>260000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>186000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>182000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>163000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>155000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>171000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>159000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>160000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>157000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>135000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>128000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>126000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>122000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>125000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>120000</v>
-      </c>
-      <c r="AG83" s="3">
-        <v>119000</v>
       </c>
       <c r="AH83" s="3">
         <v>119000</v>
       </c>
       <c r="AI83" s="3">
-        <v>97000</v>
+        <v>119000</v>
       </c>
       <c r="AJ83" s="3">
         <v>97000</v>
       </c>
+      <c r="AK83" s="3">
+        <v>97000</v>
+      </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7790,8 +7991,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7894,8 +8098,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7998,8 +8205,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8102,8 +8312,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8206,112 +8419,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1705000</v>
+      </c>
+      <c r="E89" s="3">
         <v>3201000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2359000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1666000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1225000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1233000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1169000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>601000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>970000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2046000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1673000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>432000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>871000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1329000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1551000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1365000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1319000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1296000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1849000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1027000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1234000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1833000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1348000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>714000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1357000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1728000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1464000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>626000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1100000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1866000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>491000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>857000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1251000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1384000</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8348,112 +8567,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-50000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-63000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-56000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-41000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-71000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-55000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-62000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-79000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-68000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-124000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-98000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-130000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-59000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-89000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-136000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-61000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-73000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-69000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-101000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-65000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-140000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-120000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-93000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-80000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-82000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-67000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-66000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-62000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-83000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-70000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-72000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-74000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-123000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8556,8 +8779,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8660,112 +8886,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1671000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2685000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2524000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1372000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1105000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-845000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-253000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-796000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-447000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1143000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1119000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>981000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>221000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>446000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-670000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>513000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2198000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-285000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1026000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>68000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>428000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-2093000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-879000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-263000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>737000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1145000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-60000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1251000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-140000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1127000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>337000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-280000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1868000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-834000</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8802,8 +9034,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8814,7 +9047,7 @@
         <v>243000</v>
       </c>
       <c r="F96" s="3">
-        <v>233000</v>
+        <v>243000</v>
       </c>
       <c r="G96" s="3">
         <v>233000</v>
@@ -8823,91 +9056,94 @@
         <v>233000</v>
       </c>
       <c r="I96" s="3">
+        <v>233000</v>
+      </c>
+      <c r="J96" s="3">
         <v>235000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>224000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-228000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-232000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-236000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-230000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-235000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-241000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-245000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-164000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-168000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-169000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-172000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-159000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-163000</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-166000</v>
       </c>
       <c r="Y96" s="3">
         <v>-166000</v>
       </c>
       <c r="Z96" s="3">
+        <v>-166000</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-158000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-159000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-160000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-163000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-132000</v>
-      </c>
-      <c r="AE96" s="3">
-        <v>-134000</v>
       </c>
       <c r="AF96" s="3">
         <v>-134000</v>
       </c>
       <c r="AG96" s="3">
+        <v>-134000</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-135000</v>
-      </c>
-      <c r="AH96" s="3">
-        <v>-122000</v>
       </c>
       <c r="AI96" s="3">
         <v>-122000</v>
       </c>
       <c r="AJ96" s="3">
+        <v>-122000</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-124000</v>
       </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9010,8 +9246,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9114,8 +9353,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9218,112 +9460,118 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-260000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-185000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-86000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-166000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-258000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-227000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-879000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>121000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-573000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-883000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-918000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1046000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1175000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1743000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-842000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1480000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>886000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1188000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-614000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1095000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1911000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>248000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-421000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-399000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-2055000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-612000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1365000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>458000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1033000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-531000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-788000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-571000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>664000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-607000</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9348,8 +9596,8 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -9426,108 +9674,114 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-226000</v>
+      </c>
+      <c r="E102" s="3">
         <v>331000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-251000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>128000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-138000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>161000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>37000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-74000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-50000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>20000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-364000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>367000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-83000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>32000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>39000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>398000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>7000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-177000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>209000</v>
       </c>
-      <c r="V102" s="3">
-        <v>0</v>
-      </c>
       <c r="W102" s="3">
+        <v>0</v>
+      </c>
+      <c r="X102" s="3">
         <v>-249000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-12000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>48000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>52000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>39000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-29000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>39000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-167000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-73000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>208000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>40000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>6000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>47000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-57000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ALL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ALL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="92">
   <si>
     <t>ALL</t>
   </si>
@@ -656,461 +656,473 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="37" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="38" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>16452000</v>
+      </c>
+      <c r="E8" s="3">
         <v>16506000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>16627000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>15714000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>15259000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>14832000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>14497000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>13979000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>13786000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>13648000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>13208000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>12219000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>12336000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>13011000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>12480000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>12646000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>12451000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>10962000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>10678000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>10403000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>9866000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>11476000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>11085000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>11156000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>11006000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>9486000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>10469000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>10103000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>9770000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>9854000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>9686000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>9634000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>9496000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>9350000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>9294000</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>13235000</v>
+      </c>
+      <c r="E9" s="3">
         <v>11423000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>12763000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>13093000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>11736000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>10970000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>12340000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>13774000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>12335000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1725000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1683000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1618000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1608000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1602000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1582000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1545000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1523000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1382000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1386000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1344000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1365000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1382000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1425000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1362000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1364000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1336000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1317000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1296000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1273000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1239000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1200000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1176000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1169000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1157000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1138000</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>3217000</v>
+      </c>
+      <c r="E10" s="3">
         <v>5083000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3864000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2621000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3523000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>3862000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2157000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>205000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1451000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>11923000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>11525000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>10601000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>10728000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>11409000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>10898000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>11101000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>10928000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>9580000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>9292000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>9059000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>8501000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>10094000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>9660000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>9794000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>9642000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>8150000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>9152000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>8807000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>8497000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>8615000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>8486000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>8458000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>8327000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>8193000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>8156000</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1148,8 +1160,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1255,8 +1268,11 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1362,183 +1378,189 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E14" s="3">
         <v>10000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>28000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>13000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>10000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>28000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>87000</v>
-      </c>
-      <c r="J14" s="3">
-        <v>27000</v>
       </c>
       <c r="K14" s="3">
         <v>27000</v>
       </c>
       <c r="L14" s="3">
+        <v>27000</v>
+      </c>
+      <c r="M14" s="3">
         <v>24000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>14000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>12000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>25000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>23000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>100000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>73000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>39000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>195000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>750000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>213000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>66000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>16000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>74000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>33000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>15000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>16000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>25000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>18000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>163000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>39000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>88000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>70000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>80000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>77000</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>59000</v>
+      </c>
+      <c r="E15" s="3">
         <v>70000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>71000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>70000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>69000</v>
-      </c>
-      <c r="H15" s="3">
-        <v>83000</v>
       </c>
       <c r="I15" s="3">
         <v>83000</v>
       </c>
       <c r="J15" s="3">
+        <v>83000</v>
+      </c>
+      <c r="K15" s="3">
         <v>82000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>81000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>89000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>90000</v>
-      </c>
-      <c r="N15" s="3">
-        <v>87000</v>
       </c>
       <c r="O15" s="3">
         <v>87000</v>
       </c>
       <c r="P15" s="3">
-        <v>109000</v>
+        <v>87000</v>
       </c>
       <c r="Q15" s="3">
         <v>109000</v>
       </c>
       <c r="R15" s="3">
+        <v>109000</v>
+      </c>
+      <c r="S15" s="3">
         <v>105000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>53000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>30000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>31000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>29000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>28000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>30000</v>
-      </c>
-      <c r="Y15" s="3">
-        <v>32000</v>
       </c>
       <c r="Z15" s="3">
         <v>32000</v>
@@ -1547,19 +1569,19 @@
         <v>32000</v>
       </c>
       <c r="AB15" s="3">
+        <v>32000</v>
+      </c>
+      <c r="AC15" s="3">
         <v>36000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>24000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>23000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>22000</v>
-      </c>
-      <c r="AF15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AG15" s="3" t="s">
         <v>8</v>
@@ -1567,8 +1589,8 @@
       <c r="AH15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI15" s="3">
-        <v>0</v>
+      <c r="AI15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AJ15" s="3">
         <v>0</v>
@@ -1576,8 +1598,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1612,222 +1637,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>15617000</v>
+      </c>
+      <c r="E17" s="3">
         <v>13946000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>15077000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>15173000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>13688000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>12870000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>14343000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>15602000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>14079000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>14058000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>14118000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>13530000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>11535000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>11618000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>12254000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>10849000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>9419000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>8098000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>9150000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>9024000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>8835000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>9245000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>9925000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>10078000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>9386000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>10196000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>9291000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>9206000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>8507000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>8697000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>8715000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>8783000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>8484000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>8092000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>8529000</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>835000</v>
+      </c>
+      <c r="E18" s="3">
         <v>2560000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1550000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>541000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1571000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1962000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>154000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1623000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-293000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-410000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-910000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1311000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>801000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1393000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>226000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1797000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>3032000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2864000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1528000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1379000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1031000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2231000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1160000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1078000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1620000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-710000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1178000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>897000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1263000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1157000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>971000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>851000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1012000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1258000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>765000</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1865,8 +1897,9 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1894,8 +1927,8 @@
       <c r="K20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
+      <c r="L20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M20" s="3">
         <v>0</v>
@@ -1972,145 +2005,151 @@
       <c r="AK20" s="3">
         <v>0</v>
       </c>
+      <c r="AL20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>894000</v>
+      </c>
+      <c r="E21" s="3">
         <v>2630000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1621000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>611000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1640000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2045000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>237000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-1541000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-212000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-209000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-716000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-1095000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1037000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1661000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>473000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2108000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>3292000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>3050000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1710000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1542000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1186000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2402000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1319000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1238000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1777000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-575000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1306000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1023000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1385000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1282000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1091000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>970000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1131000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1355000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>862000</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>100000</v>
+      </c>
+      <c r="E22" s="3">
         <v>101000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>104000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>98000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>97000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>107000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>88000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>98000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>86000</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
       <c r="M22" s="3">
         <v>0</v>
       </c>
@@ -2186,222 +2225,231 @@
       <c r="AK22" s="3">
         <v>0</v>
       </c>
+      <c r="AL22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>719000</v>
+      </c>
+      <c r="E23" s="3">
         <v>2449000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1418000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>430000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1464000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1827000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-21000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1748000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-406000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-410000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-910000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1311000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>801000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1393000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>226000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1797000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>3032000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2864000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1528000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1379000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1031000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2231000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1160000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1078000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1620000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-710000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1178000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>897000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1263000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1157000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>971000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>851000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1012000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1258000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>765000</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>123000</v>
+      </c>
+      <c r="E24" s="3">
         <v>559000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>254000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>83000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>266000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>340000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-17000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-373000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-85000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-114000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-236000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-289000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>151000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>281000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>20000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>362000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>626000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>594000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>312000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>273000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>194000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>458000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>229000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>227000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>328000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-170000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>230000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>180000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>257000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>414000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>305000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>272000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>317000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>418000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>245000</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2507,222 +2555,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>596000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1890000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1164000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>347000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1198000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1487000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-4000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1375000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-321000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-296000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-674000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1022000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>650000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1112000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>206000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1435000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2406000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2270000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1216000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1106000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>837000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1773000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>931000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>851000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1292000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-540000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>948000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>717000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1006000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>743000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>666000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>579000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>695000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>840000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>520000</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>566000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1899000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1161000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>301000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1189000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1460000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-41000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1389000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-346000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-303000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-685000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1040000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>634000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1111000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>183000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1399000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2385000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2244000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1189000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1080000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>801000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1707000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>889000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>821000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1261000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-583000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>911000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>678000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>977000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>714000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>637000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>550000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>666000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>811000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>491000</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2828,8 +2885,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2857,12 +2917,12 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
       <c r="N29" s="3">
         <v>0</v>
       </c>
@@ -2870,31 +2930,31 @@
         <v>0</v>
       </c>
       <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
         <v>-321000</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>325000</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>196000</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-3793000</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>354000</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-63000</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>144000</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-288000</v>
-      </c>
-      <c r="X29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>8</v>
@@ -2905,23 +2965,23 @@
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC29" s="3">
         <v>-2000</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>31000</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG29" s="3">
         <v>506000</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>8</v>
@@ -2935,8 +2995,11 @@
       <c r="AK29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3042,8 +3105,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3149,8 +3215,11 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3178,8 +3247,8 @@
       <c r="K32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
+      <c r="L32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M32" s="3">
         <v>0</v>
@@ -3256,115 +3325,121 @@
       <c r="AK32" s="3">
         <v>0</v>
       </c>
+      <c r="AL32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>595000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1928000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1190000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>331000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1218000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1489000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-5000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1352000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-320000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-303000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-685000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1040000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>634000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>790000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>508000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1595000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1408000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2598000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1126000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1224000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>513000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1707000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>889000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>821000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1261000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-585000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>942000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>678000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>977000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1220000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>637000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>550000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>666000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>811000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>491000</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3470,227 +3545,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>595000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1928000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1190000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>331000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1218000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1489000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-5000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1352000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-320000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-303000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-685000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1040000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>634000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>790000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>508000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1595000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1408000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2598000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1126000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1224000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>513000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1707000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>889000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>821000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1261000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-585000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>942000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>678000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>977000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1220000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>637000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>550000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>666000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>811000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>491000</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3728,8 +3812,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3767,145 +3852,149 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>840000</v>
+      </c>
+      <c r="E41" s="3">
         <v>704000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>816000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>599000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>850000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>722000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>860000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>699000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>662000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>736000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>786000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>766000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1130000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>763000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>690000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>656000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>709000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>377000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>370000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>547000</v>
-      </c>
-      <c r="W41" s="3">
-        <v>338000</v>
       </c>
       <c r="X41" s="3">
         <v>338000</v>
       </c>
       <c r="Y41" s="3">
+        <v>338000</v>
+      </c>
+      <c r="Z41" s="3">
         <v>587000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>599000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>551000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>499000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>460000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>489000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>450000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>617000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>690000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>482000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>442000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>436000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>389000</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>6541000</v>
+      </c>
+      <c r="E42" s="3">
         <v>4537000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>6995000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>5289000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>4319000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>5146000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>3369000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>5137000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>6724000</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -3981,115 +4070,121 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>11053000</v>
+      </c>
+      <c r="E43" s="3">
         <v>10614000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>11041000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>10762000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>10573000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>10044000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>10102000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>9713000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>9483000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>9165000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>9150000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>8824000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>8874000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>8364000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>8406000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>8146000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>7921000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>6479000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>6609000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>6367000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>6401000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>6472000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>6558000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>6380000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>6201000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>6154000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>6196000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>5953000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>5856000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>5786000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>5922000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>5693000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>5649000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>5597000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>5799000</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4117,8 +4212,8 @@
       <c r="K44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -4195,38 +4290,41 @@
       <c r="AK44" s="3">
         <v>0</v>
       </c>
+      <c r="AL44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>14627000</v>
+      </c>
+      <c r="E45" s="3">
         <v>12765000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>12904000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>9461000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>9416000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>9472000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>9731000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>9728000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>10088000</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
         <v>0</v>
       </c>
@@ -4302,38 +4400,41 @@
       <c r="AK45" s="3">
         <v>0</v>
       </c>
+      <c r="AL45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>33061000</v>
+      </c>
+      <c r="E46" s="3">
         <v>28620000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>31756000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>26111000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>25158000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>25384000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>24062000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>25277000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>26957000</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -4409,275 +4510,284 @@
       <c r="AK46" s="3">
         <v>0</v>
       </c>
+      <c r="AL46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>65840000</v>
+      </c>
+      <c r="E47" s="3">
         <v>66468000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>64978000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>63524000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>61724000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>59659000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>57656000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>56095000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>54354000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>61829000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>61006000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>61055000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>61768000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>64701000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>61840000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>62570000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>60076000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>94237000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>91197000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>89637000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>84783000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>88221000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>89158000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>86345000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>84018000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>81136000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>83855000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>83140000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>83195000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>82677000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>82680000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>81203000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>81050000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>81707000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>81038000</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>632000</v>
+      </c>
+      <c r="E48" s="3">
         <v>834000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>714000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>777000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>802000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1022000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>909000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>945000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>971000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1221000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1008000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>975000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>966000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1253000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>965000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1026000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1002000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1057000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1076000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1100000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1123000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1628000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1535000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1519000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1521000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1045000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1032000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1040000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1060000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1072000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1067000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1072000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1067000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>1065000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>1013000</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>8902000</v>
+      </c>
+      <c r="E49" s="3">
         <v>9772000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>8957000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>9614000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>9448000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>10408000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>9326000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>9109000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8973000</v>
-      </c>
-      <c r="L49" s="3">
-        <v>3502000</v>
       </c>
       <c r="M49" s="3">
         <v>3502000</v>
       </c>
       <c r="N49" s="3">
+        <v>3502000</v>
+      </c>
+      <c r="O49" s="3">
         <v>3496000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3497000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3502000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3389000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3349000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3350000</v>
-      </c>
-      <c r="T49" s="3">
-        <v>2544000</v>
       </c>
       <c r="U49" s="3">
         <v>2544000</v>
@@ -4689,22 +4799,22 @@
         <v>2544000</v>
       </c>
       <c r="X49" s="3">
-        <v>2545000</v>
+        <v>2544000</v>
       </c>
       <c r="Y49" s="3">
         <v>2545000</v>
       </c>
       <c r="Z49" s="3">
-        <v>2547000</v>
+        <v>2545000</v>
       </c>
       <c r="AA49" s="3">
         <v>2547000</v>
       </c>
       <c r="AB49" s="3">
+        <v>2547000</v>
+      </c>
+      <c r="AC49" s="3">
         <v>2530000</v>
-      </c>
-      <c r="AC49" s="3">
-        <v>2189000</v>
       </c>
       <c r="AD49" s="3">
         <v>2189000</v>
@@ -4713,25 +4823,28 @@
         <v>2189000</v>
       </c>
       <c r="AF49" s="3">
+        <v>2189000</v>
+      </c>
+      <c r="AG49" s="3">
         <v>2181000</v>
-      </c>
-      <c r="AG49" s="3">
-        <v>2309000</v>
       </c>
       <c r="AH49" s="3">
         <v>2309000</v>
       </c>
       <c r="AI49" s="3">
+        <v>2309000</v>
+      </c>
+      <c r="AJ49" s="3">
         <v>2295000</v>
-      </c>
-      <c r="AJ49" s="3">
-        <v>1219000</v>
       </c>
       <c r="AK49" s="3">
         <v>1219000</v>
       </c>
+      <c r="AL49" s="3">
+        <v>1219000</v>
+      </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4837,8 +4950,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4944,61 +5060,64 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5453000</v>
+      </c>
+      <c r="E52" s="3">
         <v>4707000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>6386000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>7046000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>6849000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>5505000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>6776000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>6997000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>6432000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>382000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>492000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>118000</v>
       </c>
-      <c r="O52" s="3" t="s">
+      <c r="P52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P52" s="3">
-        <v>0</v>
-      </c>
       <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3">
         <v>36803000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>36969000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>36829000</v>
-      </c>
-      <c r="T52" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="U52" s="3" t="s">
         <v>8</v>
@@ -5015,8 +5134,8 @@
       <c r="Y52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z52" s="3">
-        <v>0</v>
+      <c r="Z52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA52" s="3">
         <v>0</v>
@@ -5051,8 +5170,11 @@
       <c r="AK52" s="3">
         <v>0</v>
       </c>
+      <c r="AL52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5158,115 +5280,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>115161000</v>
+      </c>
+      <c r="E54" s="3">
         <v>111617000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>113743000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>108368000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>105241000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>103362000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>101176000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>100514000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>99631000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>97989000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>97676000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>96350000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>97150000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>99440000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>133440000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>132643000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>129811000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>125987000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>122750000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>121266000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>116107000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>119950000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>121073000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>118374000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>115834000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>112249000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>114490000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>113369000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>113289000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>112422000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>113632000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>110865000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>110243000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>108610000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>108537000</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5304,8 +5432,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5343,38 +5472,39 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>45494000</v>
+      </c>
+      <c r="E57" s="3">
         <v>43484000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>44470000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>43128000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>41634000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>41211000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>42139000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>41918000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>39977000</v>
       </c>
-      <c r="L57" s="3">
-        <v>0</v>
-      </c>
       <c r="M57" s="3">
         <v>0</v>
       </c>
@@ -5450,38 +5580,41 @@
       <c r="AK57" s="3">
         <v>0</v>
       </c>
+      <c r="AL57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>551000</v>
+      </c>
+      <c r="E58" s="3">
         <v>684000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>9000</v>
-      </c>
-      <c r="F58" s="3">
-        <v>2000</v>
       </c>
       <c r="G58" s="3">
         <v>2000</v>
       </c>
       <c r="H58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I58" s="3">
         <v>351000</v>
-      </c>
-      <c r="I58" s="3">
-        <v>2000</v>
       </c>
       <c r="J58" s="3">
         <v>2000</v>
       </c>
       <c r="K58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="L58" s="3">
         <v>3000</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -5557,145 +5690,151 @@
       <c r="AK58" s="3">
         <v>0</v>
       </c>
+      <c r="AL58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>29543000</v>
+      </c>
+      <c r="E59" s="3">
         <v>29022000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>29230000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>25932000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>24945000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>24714000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>24527000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>23380000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>22502000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>24843000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>24211000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>23229000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>22429000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>22490000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>21753000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>20853000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>20274000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>49274000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>49140000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>48221000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>46664000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>48503000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>48555000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>48232000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>48055000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>47670000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>48313000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>47936000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>47972000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>48614000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>48542000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>48216000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>48129000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>48185000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>48745000</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>75588000</v>
+      </c>
+      <c r="E60" s="3">
         <v>73190000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>73709000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>69062000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>66581000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>66276000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>66668000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>65300000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>62482000</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -5771,145 +5910,151 @@
       <c r="AK60" s="3">
         <v>0</v>
       </c>
+      <c r="AL60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7536000</v>
+      </c>
+      <c r="E61" s="3">
         <v>7637000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>8083000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>8082000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7938000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>7857000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>7946000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>7949000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>8452000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>7964000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>7967000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>7970000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>7973000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>7976000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>7980000</v>
-      </c>
-      <c r="R61" s="3">
-        <v>7996000</v>
       </c>
       <c r="S61" s="3">
         <v>7996000</v>
       </c>
       <c r="T61" s="3">
+        <v>7996000</v>
+      </c>
+      <c r="U61" s="3">
         <v>7825000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>6635000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>6634000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>6633000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>6631000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>6630000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>6628000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>6453000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>6451000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>6450000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>6448000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>6847000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>6350000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>6349000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>6348000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>6346000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>6347000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>5110000</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>9985000</v>
+      </c>
+      <c r="E62" s="3">
         <v>9187000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>10902000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>12651000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>12242000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>11270000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>12115000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>11893000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>11324000</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
       <c r="M62" s="3">
         <v>0</v>
       </c>
@@ -5917,76 +6062,79 @@
         <v>0</v>
       </c>
       <c r="O62" s="3">
+        <v>0</v>
+      </c>
+      <c r="P62" s="3">
         <v>402000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>833000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>33132000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>33533000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>33876000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1355000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>905000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>842000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>331000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1154000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1079000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>997000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>817000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>425000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>660000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>723000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>725000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>782000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1249000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1104000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>833000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>487000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>935000</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6092,8 +6240,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6199,8 +6350,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6306,115 +6460,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>93109000</v>
+      </c>
+      <c r="E66" s="3">
         <v>90250000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>92905000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>89795000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>86761000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>85732000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>86729000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>85142000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>82258000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>80501000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>80003000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>76235000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>73938000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>74261000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>106711000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>104436000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>102992000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>95770000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>95487000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>94280000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>91934000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>93952000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>94933000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>93898000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>92416000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>90937000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>90857000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>90247000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>90012000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>89871000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>91513000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>89364000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>89085000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>88037000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>87603000</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6452,8 +6612,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6559,8 +6720,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6666,8 +6830,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6693,7 +6860,7 @@
         <v>2001000</v>
       </c>
       <c r="K70" s="3">
-        <v>1970000</v>
+        <v>2001000</v>
       </c>
       <c r="L70" s="3">
         <v>1970000</v>
@@ -6714,13 +6881,13 @@
         <v>1970000</v>
       </c>
       <c r="R70" s="3">
-        <v>2170000</v>
+        <v>1970000</v>
       </c>
       <c r="S70" s="3">
         <v>2170000</v>
       </c>
       <c r="T70" s="3">
-        <v>1970000</v>
+        <v>2170000</v>
       </c>
       <c r="U70" s="3">
         <v>1970000</v>
@@ -6732,13 +6899,13 @@
         <v>1970000</v>
       </c>
       <c r="X70" s="3">
+        <v>1970000</v>
+      </c>
+      <c r="Y70" s="3">
         <v>2248000</v>
       </c>
-      <c r="Y70" s="3">
+      <c r="Z70" s="3">
         <v>3052000</v>
-      </c>
-      <c r="Z70" s="3">
-        <v>1930000</v>
       </c>
       <c r="AA70" s="3">
         <v>1930000</v>
@@ -6747,7 +6914,7 @@
         <v>1930000</v>
       </c>
       <c r="AC70" s="3">
-        <v>2303000</v>
+        <v>1930000</v>
       </c>
       <c r="AD70" s="3">
         <v>2303000</v>
@@ -6756,7 +6923,7 @@
         <v>2303000</v>
       </c>
       <c r="AF70" s="3">
-        <v>1746000</v>
+        <v>2303000</v>
       </c>
       <c r="AG70" s="3">
         <v>1746000</v>
@@ -6773,8 +6940,11 @@
       <c r="AK70" s="3">
         <v>1746000</v>
       </c>
+      <c r="AL70" s="3">
+        <v>1746000</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6880,115 +7050,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>53586000</v>
+      </c>
+      <c r="E72" s="3">
         <v>53288000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>51635000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>50718000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>50662000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>49716000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>48491000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>48766000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>50388000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>50970000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>51490000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>52412000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>53688000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>53294000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>52736000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>52464000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>51107000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>52767000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>50336000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>49380000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>48326000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>48074000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>46527000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>45803000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>45148000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>45708000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>46178000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>45508000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>45031000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>43162000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>42125000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>41622000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>41208000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>40678000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>39990000</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7094,8 +7270,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7201,8 +7380,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7308,115 +7490,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>20054000</v>
+      </c>
+      <c r="E76" s="3">
         <v>19441000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>18876000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>16592000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>16638000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>15769000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>12592000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>13516000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>15524000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>15518000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>15703000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>18145000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>21242000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>23209000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>24759000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>26037000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>24649000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>28247000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>25293000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>25016000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>22203000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>23750000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>23088000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>22546000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>21488000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>19382000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>21330000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>20819000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>20974000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>20805000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>20373000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>19755000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>19412000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>18827000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>19188000</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7522,227 +7710,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>595000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1928000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1190000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>331000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1218000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1489000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-5000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1352000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-320000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-303000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-685000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1040000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>634000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>790000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>508000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1595000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1408000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2598000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1126000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1224000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>513000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1707000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>889000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>821000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1261000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-585000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>942000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>678000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>977000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1220000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>637000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>550000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>666000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>811000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>491000</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7780,115 +7977,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>63000</v>
+      </c>
+      <c r="E83" s="3">
         <v>82000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>93000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>104000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>96000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>112000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>104000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>129000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>149000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>201000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>194000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>216000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>236000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>268000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>247000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>311000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>260000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>186000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>182000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>163000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>155000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>171000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>159000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>160000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>157000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>135000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>128000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>126000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>122000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>125000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>120000</v>
-      </c>
-      <c r="AH83" s="3">
-        <v>119000</v>
       </c>
       <c r="AI83" s="3">
         <v>119000</v>
       </c>
       <c r="AJ83" s="3">
-        <v>97000</v>
+        <v>119000</v>
       </c>
       <c r="AK83" s="3">
         <v>97000</v>
       </c>
+      <c r="AL83" s="3">
+        <v>97000</v>
+      </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7994,8 +8195,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8101,8 +8305,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8208,8 +8415,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8315,8 +8525,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8422,115 +8635,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1964000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1705000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3201000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2359000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1666000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1225000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1233000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1169000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>601000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>970000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2046000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1673000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>432000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>871000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1329000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1551000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1365000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1319000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1296000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1849000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1027000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1234000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1833000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1348000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>714000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1357000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1728000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1464000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>626000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1100000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1866000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>491000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>857000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1251000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1384000</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8568,115 +8787,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-92000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-50000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-63000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-56000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-41000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-71000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-55000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-62000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-79000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-68000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-124000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-98000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-130000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-59000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-89000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-136000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-61000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-73000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-69000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-101000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-65000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-140000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-120000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-93000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-80000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-82000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-67000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-66000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-62000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-83000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-70000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-72000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-74000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-123000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8782,8 +9005,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8889,115 +9115,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1293000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1671000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2685000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2524000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1372000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1105000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-845000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-253000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-796000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-447000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1143000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1119000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>981000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>221000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>446000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-670000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>513000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-2198000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-285000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1026000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>68000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>428000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-2093000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-879000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-263000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>737000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1145000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-60000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1251000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-140000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1127000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>337000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-280000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-1868000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-834000</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9035,13 +9267,14 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>243000</v>
+        <v>244000</v>
       </c>
       <c r="E96" s="3">
         <v>243000</v>
@@ -9050,7 +9283,7 @@
         <v>243000</v>
       </c>
       <c r="G96" s="3">
-        <v>233000</v>
+        <v>243000</v>
       </c>
       <c r="H96" s="3">
         <v>233000</v>
@@ -9059,91 +9292,94 @@
         <v>233000</v>
       </c>
       <c r="J96" s="3">
+        <v>233000</v>
+      </c>
+      <c r="K96" s="3">
         <v>235000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>224000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-228000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-232000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-236000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-230000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-235000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-241000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-245000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-164000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-168000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-169000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-172000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-159000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-163000</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>-166000</v>
       </c>
       <c r="Z96" s="3">
         <v>-166000</v>
       </c>
       <c r="AA96" s="3">
+        <v>-166000</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-158000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-159000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-160000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-163000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-132000</v>
-      </c>
-      <c r="AF96" s="3">
-        <v>-134000</v>
       </c>
       <c r="AG96" s="3">
         <v>-134000</v>
       </c>
       <c r="AH96" s="3">
+        <v>-134000</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-135000</v>
-      </c>
-      <c r="AI96" s="3">
-        <v>-122000</v>
       </c>
       <c r="AJ96" s="3">
         <v>-122000</v>
       </c>
       <c r="AK96" s="3">
+        <v>-122000</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-124000</v>
       </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9249,8 +9485,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9356,8 +9595,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9463,115 +9705,121 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-334000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-260000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-185000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-86000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-166000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-258000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-227000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-879000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>121000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-573000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-883000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-918000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1046000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1175000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1743000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-842000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1480000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>886000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1188000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-614000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1095000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1911000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>248000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-421000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-399000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-2055000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-612000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1365000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>458000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1033000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-531000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-788000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-571000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>664000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-607000</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9599,8 +9847,8 @@
       <c r="K101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -9677,111 +9925,117 @@
       <c r="AK101" s="3">
         <v>0</v>
       </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>337000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-226000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>331000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-251000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>128000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-138000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>161000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>37000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-74000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-50000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>20000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-364000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>367000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-83000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>32000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>39000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>398000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>7000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-177000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>209000</v>
       </c>
-      <c r="W102" s="3">
-        <v>0</v>
-      </c>
       <c r="X102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="3">
         <v>-249000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-12000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>48000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>52000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>39000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-29000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>39000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-167000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-73000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>208000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>40000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>6000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>47000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-57000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ALL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ALL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="92">
   <si>
     <t>ALL</t>
   </si>
@@ -656,473 +656,485 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="38" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="39" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>16633000</v>
+      </c>
+      <c r="E8" s="3">
         <v>16452000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>16506000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>16627000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>15714000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>15259000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>14832000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>14497000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>13979000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>13786000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>13648000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>13208000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>12219000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>12336000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>13011000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>12480000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>12646000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>12451000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>10962000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>10678000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>10403000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>9866000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>11476000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>11085000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>11156000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>11006000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>9486000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>10469000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>10103000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>9770000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>9854000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>9686000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>9634000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>9496000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>9350000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>9294000</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>12513000</v>
+      </c>
+      <c r="E9" s="3">
         <v>13235000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>11423000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>12763000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>13093000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>11736000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>10970000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>12340000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>13774000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>12335000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1725000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1683000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1618000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1608000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1602000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1582000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1545000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1523000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1382000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1386000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1344000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1365000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1382000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1425000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1362000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1364000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1336000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1317000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1296000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1273000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1239000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1200000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1176000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1169000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1157000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1138000</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>4120000</v>
+      </c>
+      <c r="E10" s="3">
         <v>3217000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>5083000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3864000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2621000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>3523000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3862000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2157000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>205000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1451000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>11923000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>11525000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>10601000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>10728000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>11409000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>10898000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>11101000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>10928000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>9580000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>9292000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>9059000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>8501000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>10094000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>9660000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>9794000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>9642000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>8150000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>9152000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>8807000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>8497000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>8615000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>8486000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>8458000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>8327000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>8193000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>8156000</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1161,8 +1173,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1271,8 +1284,11 @@
       <c r="AL12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1381,189 +1397,195 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-875000</v>
+      </c>
+      <c r="E14" s="3">
         <v>16000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>10000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>28000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>13000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>10000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>28000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>87000</v>
-      </c>
-      <c r="K14" s="3">
-        <v>27000</v>
       </c>
       <c r="L14" s="3">
         <v>27000</v>
       </c>
       <c r="M14" s="3">
+        <v>27000</v>
+      </c>
+      <c r="N14" s="3">
         <v>24000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>14000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>12000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>25000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>23000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>100000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>73000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>39000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>195000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>750000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>213000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>66000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>16000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>74000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>33000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>15000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>16000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>25000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>18000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>163000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>39000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>88000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>70000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>80000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>77000</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>57000</v>
+      </c>
+      <c r="E15" s="3">
         <v>59000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>70000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>71000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>70000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>69000</v>
-      </c>
-      <c r="I15" s="3">
-        <v>83000</v>
       </c>
       <c r="J15" s="3">
         <v>83000</v>
       </c>
       <c r="K15" s="3">
+        <v>83000</v>
+      </c>
+      <c r="L15" s="3">
         <v>82000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>81000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>89000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>90000</v>
-      </c>
-      <c r="O15" s="3">
-        <v>87000</v>
       </c>
       <c r="P15" s="3">
         <v>87000</v>
       </c>
       <c r="Q15" s="3">
-        <v>109000</v>
+        <v>87000</v>
       </c>
       <c r="R15" s="3">
         <v>109000</v>
       </c>
       <c r="S15" s="3">
+        <v>109000</v>
+      </c>
+      <c r="T15" s="3">
         <v>105000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>53000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>30000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>31000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>29000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>28000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>30000</v>
-      </c>
-      <c r="Z15" s="3">
-        <v>32000</v>
       </c>
       <c r="AA15" s="3">
         <v>32000</v>
@@ -1572,19 +1594,19 @@
         <v>32000</v>
       </c>
       <c r="AC15" s="3">
+        <v>32000</v>
+      </c>
+      <c r="AD15" s="3">
         <v>36000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>24000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>23000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>22000</v>
-      </c>
-      <c r="AG15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AH15" s="3" t="s">
         <v>8</v>
@@ -1592,8 +1614,8 @@
       <c r="AI15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ15" s="3">
-        <v>0</v>
+      <c r="AJ15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AK15" s="3">
         <v>0</v>
@@ -1601,8 +1623,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1638,228 +1663,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>14705000</v>
+      </c>
+      <c r="E17" s="3">
         <v>15617000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>13946000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>15077000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>15173000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>13688000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>12870000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>14343000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>15602000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>14079000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>14058000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>14118000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>13530000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>11535000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>11618000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>12254000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>10849000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>9419000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>8098000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>9150000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>9024000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>8835000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>9245000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>9925000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>10078000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>9386000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>10196000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>9291000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>9206000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>8507000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>8697000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>8715000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>8783000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>8484000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>8092000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>8529000</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1928000</v>
+      </c>
+      <c r="E18" s="3">
         <v>835000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2560000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1550000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>541000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1571000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1962000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>154000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1623000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-293000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-410000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-910000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1311000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>801000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1393000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>226000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1797000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>3032000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2864000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1528000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1379000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1031000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2231000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1160000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1078000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1620000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-710000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1178000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>897000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1263000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1157000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>971000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>851000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1012000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>1258000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>765000</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1898,8 +1930,9 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1930,8 +1963,8 @@
       <c r="L20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
+      <c r="M20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N20" s="3">
         <v>0</v>
@@ -2008,118 +2041,124 @@
       <c r="AL20" s="3">
         <v>0</v>
       </c>
+      <c r="AM20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1985000</v>
+      </c>
+      <c r="E21" s="3">
         <v>894000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2630000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1621000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>611000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1640000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2045000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>237000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1541000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-212000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-209000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-716000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-1095000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1037000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1661000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>473000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2108000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>3292000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>3050000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1710000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1542000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1186000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2402000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1319000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1238000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1777000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-575000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1306000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1023000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1385000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1282000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1091000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>970000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1131000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1355000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>862000</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2127,32 +2166,32 @@
         <v>100000</v>
       </c>
       <c r="E22" s="3">
+        <v>100000</v>
+      </c>
+      <c r="F22" s="3">
         <v>101000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>104000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>98000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>97000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>107000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>88000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>98000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>86000</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
       <c r="N22" s="3">
         <v>0</v>
       </c>
@@ -2228,228 +2267,237 @@
       <c r="AL22" s="3">
         <v>0</v>
       </c>
+      <c r="AM22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2703000</v>
+      </c>
+      <c r="E23" s="3">
         <v>719000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2449000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1418000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>430000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1464000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1827000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-21000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1748000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-406000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-410000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-910000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1311000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>801000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1393000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>226000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1797000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>3032000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2864000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1528000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1379000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1031000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>2231000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1160000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1078000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1620000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-710000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1178000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>897000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1263000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1157000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>971000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>851000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1012000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>1258000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>765000</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>604000</v>
+      </c>
+      <c r="E24" s="3">
         <v>123000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>559000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>254000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>83000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>266000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>340000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-17000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-373000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-85000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-114000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-236000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-289000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>151000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>281000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>20000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>362000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>626000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>594000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>312000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>273000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>194000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>458000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>229000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>227000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>328000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-170000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>230000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>180000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>257000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>414000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>305000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>272000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>317000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>418000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>245000</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2558,228 +2606,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2099000</v>
+      </c>
+      <c r="E26" s="3">
         <v>596000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1890000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1164000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>347000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1198000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1487000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-4000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1375000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-321000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-296000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-674000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1022000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>650000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1112000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>206000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1435000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2406000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2270000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1216000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1106000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>837000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1773000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>931000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>851000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1292000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-540000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>948000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>717000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1006000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>743000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>666000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>579000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>695000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>840000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>520000</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2079000</v>
+      </c>
+      <c r="E27" s="3">
         <v>566000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1899000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1161000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>301000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1189000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1460000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-41000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1389000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-346000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-303000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-685000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1040000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>634000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1111000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>183000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1399000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2385000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2244000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1189000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1080000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>801000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1707000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>889000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>821000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1261000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-583000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>911000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>678000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>977000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>714000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>637000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>550000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>666000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>811000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>491000</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2888,8 +2945,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2920,12 +2980,12 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3" t="s">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N29" s="3">
-        <v>0</v>
-      </c>
       <c r="O29" s="3">
         <v>0</v>
       </c>
@@ -2933,31 +2993,31 @@
         <v>0</v>
       </c>
       <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
         <v>-321000</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>325000</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>196000</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-3793000</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>354000</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-63000</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>144000</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-288000</v>
-      </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
@@ -2968,23 +3028,23 @@
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>31000</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3">
         <v>506000</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>8</v>
@@ -2998,8 +3058,11 @@
       <c r="AL29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3108,8 +3171,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3218,8 +3284,11 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3250,8 +3319,8 @@
       <c r="L32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
+      <c r="M32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N32" s="3">
         <v>0</v>
@@ -3328,118 +3397,124 @@
       <c r="AL32" s="3">
         <v>0</v>
       </c>
+      <c r="AM32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2109000</v>
+      </c>
+      <c r="E33" s="3">
         <v>595000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1928000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1190000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>331000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1218000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1489000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-5000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1352000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-320000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-303000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-685000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1040000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>634000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>790000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>508000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1595000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1408000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2598000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1126000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1224000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>513000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1707000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>889000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>821000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1261000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-585000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>942000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>678000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>977000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1220000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>637000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>550000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>666000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>811000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>491000</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3548,233 +3623,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2109000</v>
+      </c>
+      <c r="E35" s="3">
         <v>595000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1928000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1190000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>331000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1218000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1489000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-5000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1352000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-320000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-303000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-685000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1040000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>634000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>790000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>508000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1595000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1408000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2598000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1126000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1224000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>513000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1707000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>889000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>821000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1261000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-585000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>942000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>678000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>977000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1220000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>637000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>550000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>666000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>811000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>491000</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3813,8 +3897,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3853,151 +3938,155 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>995000</v>
+      </c>
+      <c r="E41" s="3">
         <v>840000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>704000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>816000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>599000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>850000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>722000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>860000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>699000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>662000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>736000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>786000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>766000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1130000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>763000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>690000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>656000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>709000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>377000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>370000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>547000</v>
-      </c>
-      <c r="X41" s="3">
-        <v>338000</v>
       </c>
       <c r="Y41" s="3">
         <v>338000</v>
       </c>
       <c r="Z41" s="3">
+        <v>338000</v>
+      </c>
+      <c r="AA41" s="3">
         <v>587000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>599000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>551000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>499000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>460000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>489000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>450000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>617000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>690000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>482000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>442000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>436000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>389000</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>9640000</v>
+      </c>
+      <c r="E42" s="3">
         <v>6541000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>4537000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>6995000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>5289000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>4319000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>5146000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>3369000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>5137000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>6724000</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
         <v>0</v>
       </c>
@@ -4073,118 +4162,124 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>11271000</v>
+      </c>
+      <c r="E43" s="3">
         <v>11053000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>10614000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>11041000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>10762000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>10573000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>10044000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>10102000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>9713000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>9483000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>9165000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>9150000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>8824000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>8874000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>8364000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>8406000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>8146000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>7921000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>6479000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>6609000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>6367000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>6401000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>6472000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>6558000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>6380000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>6201000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>6154000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>6196000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>5953000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>5856000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>5786000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>5922000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>5693000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>5649000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>5597000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>5799000</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4215,8 +4310,8 @@
       <c r="L44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -4293,41 +4388,44 @@
       <c r="AL44" s="3">
         <v>0</v>
       </c>
+      <c r="AM44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>11126000</v>
+      </c>
+      <c r="E45" s="3">
         <v>14627000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>12765000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>12904000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>9461000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>9416000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>9472000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>9731000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>9728000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>10088000</v>
       </c>
-      <c r="M45" s="3">
-        <v>0</v>
-      </c>
       <c r="N45" s="3">
         <v>0</v>
       </c>
@@ -4403,41 +4501,44 @@
       <c r="AL45" s="3">
         <v>0</v>
       </c>
+      <c r="AM45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>33032000</v>
+      </c>
+      <c r="E46" s="3">
         <v>33061000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>28620000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>31756000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>26111000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>25158000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>25384000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>24062000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>25277000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>26957000</v>
       </c>
-      <c r="M46" s="3">
-        <v>0</v>
-      </c>
       <c r="N46" s="3">
         <v>0</v>
       </c>
@@ -4513,284 +4614,293 @@
       <c r="AL46" s="3">
         <v>0</v>
       </c>
+      <c r="AM46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>66027000</v>
+      </c>
+      <c r="E47" s="3">
         <v>65840000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>66468000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>64978000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>63524000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>61724000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>59659000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>57656000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>56095000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>54354000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>61829000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>61006000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>61055000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>61768000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>64701000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>61840000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>62570000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>60076000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>94237000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>91197000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>89637000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>84783000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>88221000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>89158000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>86345000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>84018000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>81136000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>83855000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>83140000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>83195000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>82677000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>82680000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>81203000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>81050000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>81707000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>81038000</v>
       </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>619000</v>
+      </c>
+      <c r="E48" s="3">
         <v>632000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>834000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>714000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>777000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>802000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1022000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>909000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>945000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>971000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1221000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1008000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>975000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>966000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1253000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>965000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1026000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1002000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1057000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1076000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1100000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1123000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1628000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1535000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1519000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1521000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1045000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1032000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1040000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1060000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1072000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1067000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1072000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>1067000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>1065000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>1013000</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>9048000</v>
+      </c>
+      <c r="E49" s="3">
         <v>8902000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>9772000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>8957000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>9614000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>9448000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>10408000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>9326000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>9109000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8973000</v>
-      </c>
-      <c r="M49" s="3">
-        <v>3502000</v>
       </c>
       <c r="N49" s="3">
         <v>3502000</v>
       </c>
       <c r="O49" s="3">
+        <v>3502000</v>
+      </c>
+      <c r="P49" s="3">
         <v>3496000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3497000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3502000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3389000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3349000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>3350000</v>
-      </c>
-      <c r="U49" s="3">
-        <v>2544000</v>
       </c>
       <c r="V49" s="3">
         <v>2544000</v>
@@ -4802,22 +4912,22 @@
         <v>2544000</v>
       </c>
       <c r="Y49" s="3">
-        <v>2545000</v>
+        <v>2544000</v>
       </c>
       <c r="Z49" s="3">
         <v>2545000</v>
       </c>
       <c r="AA49" s="3">
-        <v>2547000</v>
+        <v>2545000</v>
       </c>
       <c r="AB49" s="3">
         <v>2547000</v>
       </c>
       <c r="AC49" s="3">
+        <v>2547000</v>
+      </c>
+      <c r="AD49" s="3">
         <v>2530000</v>
-      </c>
-      <c r="AD49" s="3">
-        <v>2189000</v>
       </c>
       <c r="AE49" s="3">
         <v>2189000</v>
@@ -4826,25 +4936,28 @@
         <v>2189000</v>
       </c>
       <c r="AG49" s="3">
+        <v>2189000</v>
+      </c>
+      <c r="AH49" s="3">
         <v>2181000</v>
-      </c>
-      <c r="AH49" s="3">
-        <v>2309000</v>
       </c>
       <c r="AI49" s="3">
         <v>2309000</v>
       </c>
       <c r="AJ49" s="3">
+        <v>2309000</v>
+      </c>
+      <c r="AK49" s="3">
         <v>2295000</v>
-      </c>
-      <c r="AK49" s="3">
-        <v>1219000</v>
       </c>
       <c r="AL49" s="3">
         <v>1219000</v>
       </c>
+      <c r="AM49" s="3">
+        <v>1219000</v>
+      </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4953,8 +5066,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5063,64 +5179,67 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5909000</v>
+      </c>
+      <c r="E52" s="3">
         <v>5453000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4707000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>6386000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>7046000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>6849000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>5505000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>6776000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>6997000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>6432000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>382000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>492000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>118000</v>
       </c>
-      <c r="P52" s="3" t="s">
+      <c r="Q52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
-      </c>
       <c r="R52" s="3">
+        <v>0</v>
+      </c>
+      <c r="S52" s="3">
         <v>36803000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>36969000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>36829000</v>
-      </c>
-      <c r="U52" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="V52" s="3" t="s">
         <v>8</v>
@@ -5137,8 +5256,8 @@
       <c r="Z52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA52" s="3">
-        <v>0</v>
+      <c r="AA52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB52" s="3">
         <v>0</v>
@@ -5173,8 +5292,11 @@
       <c r="AL52" s="3">
         <v>0</v>
       </c>
+      <c r="AM52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5283,118 +5405,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>115894000</v>
+      </c>
+      <c r="E54" s="3">
         <v>115161000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>111617000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>113743000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>108368000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>105241000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>103362000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>101176000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>100514000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>99631000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>97989000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>97676000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>96350000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>97150000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>99440000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>133440000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>132643000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>129811000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>125987000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>122750000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>121266000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>116107000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>119950000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>121073000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>118374000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>115834000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>112249000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>114490000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>113369000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>113289000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>112422000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>113632000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>110865000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>110243000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>108610000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>108537000</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5433,8 +5561,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5473,41 +5602,42 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>45796000</v>
+      </c>
+      <c r="E57" s="3">
         <v>45494000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>43484000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>44470000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>43128000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>41634000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>41211000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>42139000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>41918000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>39977000</v>
       </c>
-      <c r="M57" s="3">
-        <v>0</v>
-      </c>
       <c r="N57" s="3">
         <v>0</v>
       </c>
@@ -5583,41 +5713,44 @@
       <c r="AL57" s="3">
         <v>0</v>
       </c>
+      <c r="AM57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>554000</v>
+      </c>
+      <c r="E58" s="3">
         <v>551000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>684000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>9000</v>
-      </c>
-      <c r="G58" s="3">
-        <v>2000</v>
       </c>
       <c r="H58" s="3">
         <v>2000</v>
       </c>
       <c r="I58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="J58" s="3">
         <v>351000</v>
-      </c>
-      <c r="J58" s="3">
-        <v>2000</v>
       </c>
       <c r="K58" s="3">
         <v>2000</v>
       </c>
       <c r="L58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="M58" s="3">
         <v>3000</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -5693,151 +5826,157 @@
       <c r="AL58" s="3">
         <v>0</v>
       </c>
+      <c r="AM58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>28047000</v>
+      </c>
+      <c r="E59" s="3">
         <v>29543000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>29022000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>29230000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>25932000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>24945000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>24714000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>24527000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>23380000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>22502000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>24843000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>24211000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>23229000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>22429000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>22490000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>21753000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>20853000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>20274000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>49274000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>49140000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>48221000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>46664000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>48503000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>48555000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>48232000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>48055000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>47670000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>48313000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>47936000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>47972000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>48614000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>48542000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>48216000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>48129000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>48185000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>48745000</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>74397000</v>
+      </c>
+      <c r="E60" s="3">
         <v>75588000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>73190000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>73709000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>69062000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>66581000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>66276000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>66668000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>65300000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>62482000</v>
       </c>
-      <c r="M60" s="3">
-        <v>0</v>
-      </c>
       <c r="N60" s="3">
         <v>0</v>
       </c>
@@ -5913,151 +6052,157 @@
       <c r="AL60" s="3">
         <v>0</v>
       </c>
+      <c r="AM60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7537000</v>
+      </c>
+      <c r="E61" s="3">
         <v>7536000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7637000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>8083000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>8082000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>7938000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>7857000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>7946000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>7949000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>8452000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>7964000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>7967000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>7970000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>7973000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>7976000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>7980000</v>
-      </c>
-      <c r="S61" s="3">
-        <v>7996000</v>
       </c>
       <c r="T61" s="3">
         <v>7996000</v>
       </c>
       <c r="U61" s="3">
+        <v>7996000</v>
+      </c>
+      <c r="V61" s="3">
         <v>7825000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>6635000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>6634000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>6633000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>6631000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>6630000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>6628000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>6453000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>6451000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>6450000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>6448000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>6847000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>6350000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>6349000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>6348000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>6346000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>6347000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>5110000</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>9955000</v>
+      </c>
+      <c r="E62" s="3">
         <v>9985000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>9187000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>10902000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>12651000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>12242000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>11270000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>12115000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>11893000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>11324000</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
-      </c>
       <c r="N62" s="3">
         <v>0</v>
       </c>
@@ -6065,76 +6210,79 @@
         <v>0</v>
       </c>
       <c r="P62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="3">
         <v>402000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>833000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>33132000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>33533000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>33876000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1355000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>905000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>842000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>331000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1154000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1079000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>997000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>817000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>425000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>660000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>723000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>725000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>782000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1249000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1104000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>833000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>487000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>935000</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6243,8 +6391,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6353,8 +6504,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6463,118 +6617,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>91889000</v>
+      </c>
+      <c r="E66" s="3">
         <v>93109000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>90250000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>92905000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>89795000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>86761000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>85732000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>86729000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>85142000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>82258000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>80501000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>80003000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>76235000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>73938000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>74261000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>106711000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>104436000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>102992000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>95770000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>95487000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>94280000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>91934000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>93952000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>94933000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>93898000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>92416000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>90937000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>90857000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>90247000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>90012000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>89871000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>91513000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>89364000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>89085000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>88037000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>87603000</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6613,8 +6773,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6723,8 +6884,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6833,8 +6997,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6863,7 +7030,7 @@
         <v>2001000</v>
       </c>
       <c r="L70" s="3">
-        <v>1970000</v>
+        <v>2001000</v>
       </c>
       <c r="M70" s="3">
         <v>1970000</v>
@@ -6884,13 +7051,13 @@
         <v>1970000</v>
       </c>
       <c r="S70" s="3">
-        <v>2170000</v>
+        <v>1970000</v>
       </c>
       <c r="T70" s="3">
         <v>2170000</v>
       </c>
       <c r="U70" s="3">
-        <v>1970000</v>
+        <v>2170000</v>
       </c>
       <c r="V70" s="3">
         <v>1970000</v>
@@ -6902,13 +7069,13 @@
         <v>1970000</v>
       </c>
       <c r="Y70" s="3">
+        <v>1970000</v>
+      </c>
+      <c r="Z70" s="3">
         <v>2248000</v>
       </c>
-      <c r="Z70" s="3">
+      <c r="AA70" s="3">
         <v>3052000</v>
-      </c>
-      <c r="AA70" s="3">
-        <v>1930000</v>
       </c>
       <c r="AB70" s="3">
         <v>1930000</v>
@@ -6917,7 +7084,7 @@
         <v>1930000</v>
       </c>
       <c r="AD70" s="3">
-        <v>2303000</v>
+        <v>1930000</v>
       </c>
       <c r="AE70" s="3">
         <v>2303000</v>
@@ -6926,7 +7093,7 @@
         <v>2303000</v>
       </c>
       <c r="AG70" s="3">
-        <v>1746000</v>
+        <v>2303000</v>
       </c>
       <c r="AH70" s="3">
         <v>1746000</v>
@@ -6943,8 +7110,11 @@
       <c r="AL70" s="3">
         <v>1746000</v>
       </c>
+      <c r="AM70" s="3">
+        <v>1746000</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7053,118 +7223,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>55400000</v>
+      </c>
+      <c r="E72" s="3">
         <v>53586000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>53288000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>51635000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>50718000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>50662000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>49716000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>48491000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>48766000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>50388000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>50970000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>51490000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>52412000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>53688000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>53294000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>52736000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>52464000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>51107000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>52767000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>50336000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>49380000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>48326000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>48074000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>46527000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>45803000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>45148000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>45708000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>46178000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>45508000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>45031000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>43162000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>42125000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>41622000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>41208000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>40678000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>39990000</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7273,8 +7449,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7383,8 +7562,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7493,118 +7675,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>22018000</v>
+      </c>
+      <c r="E76" s="3">
         <v>20054000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>19441000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>18876000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>16592000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>16638000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>15769000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>12592000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>13516000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>15524000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>15518000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>15703000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>18145000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>21242000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>23209000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>24759000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>26037000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>24649000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>28247000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>25293000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>25016000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>22203000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>23750000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>23088000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>22546000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>21488000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>19382000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>21330000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>20819000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>20974000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>20805000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>20373000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>19755000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>19412000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>18827000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>19188000</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7713,233 +7901,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2109000</v>
+      </c>
+      <c r="E81" s="3">
         <v>595000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1928000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1190000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>331000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1218000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1489000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-5000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1352000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-320000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-303000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-685000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1040000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>634000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>790000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>508000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1595000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1408000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2598000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1126000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1224000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>513000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1707000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>889000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>821000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1261000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-585000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>942000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>678000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>977000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1220000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>637000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>550000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>666000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>811000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>491000</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7978,118 +8175,122 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>62000</v>
+      </c>
+      <c r="E83" s="3">
         <v>63000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>82000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>93000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>104000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>96000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>112000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>104000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>129000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>149000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>201000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>194000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>216000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>236000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>268000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>247000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>311000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>260000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>186000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>182000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>163000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>155000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>171000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>159000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>160000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>157000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>135000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>128000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>126000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>122000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>125000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>120000</v>
-      </c>
-      <c r="AI83" s="3">
-        <v>119000</v>
       </c>
       <c r="AJ83" s="3">
         <v>119000</v>
       </c>
       <c r="AK83" s="3">
-        <v>97000</v>
+        <v>119000</v>
       </c>
       <c r="AL83" s="3">
         <v>97000</v>
       </c>
+      <c r="AM83" s="3">
+        <v>97000</v>
+      </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8198,8 +8399,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8308,8 +8512,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8418,8 +8625,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8528,8 +8738,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8638,118 +8851,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E89" s="3">
         <v>1964000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1705000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3201000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2359000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1666000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1225000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1233000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1169000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>601000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>970000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2046000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1673000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>432000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>871000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1329000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1551000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1365000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1319000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1296000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1849000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1027000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1234000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1833000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1348000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>714000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1357000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1728000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1464000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>626000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1100000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1866000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>491000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>857000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1251000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>1384000</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8788,118 +9007,122 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" s="3">
         <v>-92000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-50000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-63000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-56000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-41000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-71000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-55000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-62000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-79000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-68000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-124000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-98000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-130000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-59000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-89000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-136000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-61000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-73000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-69000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-101000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-65000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-140000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-120000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-93000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-80000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-82000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-67000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-66000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-62000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-83000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-70000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-72000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-74000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-123000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9008,8 +9231,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9118,118 +9344,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1293000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1671000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2685000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2524000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1372000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1105000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-845000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-253000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-796000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-447000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1143000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1119000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>981000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>221000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>446000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-670000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>513000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2198000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-285000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1026000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>68000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>428000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2093000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-879000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-263000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>737000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1145000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-60000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1251000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-140000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1127000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>337000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-280000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-1868000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-834000</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9268,16 +9500,17 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3">
         <v>244000</v>
-      </c>
-      <c r="E96" s="3">
-        <v>243000</v>
       </c>
       <c r="F96" s="3">
         <v>243000</v>
@@ -9286,7 +9519,7 @@
         <v>243000</v>
       </c>
       <c r="H96" s="3">
-        <v>233000</v>
+        <v>243000</v>
       </c>
       <c r="I96" s="3">
         <v>233000</v>
@@ -9295,91 +9528,94 @@
         <v>233000</v>
       </c>
       <c r="K96" s="3">
+        <v>233000</v>
+      </c>
+      <c r="L96" s="3">
         <v>235000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>224000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-228000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-232000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-236000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-230000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-235000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-241000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-245000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-164000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-168000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-169000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-172000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-159000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-163000</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-166000</v>
       </c>
       <c r="AA96" s="3">
         <v>-166000</v>
       </c>
       <c r="AB96" s="3">
+        <v>-166000</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-158000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-159000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-160000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-163000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-132000</v>
-      </c>
-      <c r="AG96" s="3">
-        <v>-134000</v>
       </c>
       <c r="AH96" s="3">
         <v>-134000</v>
       </c>
       <c r="AI96" s="3">
+        <v>-134000</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-135000</v>
-      </c>
-      <c r="AJ96" s="3">
-        <v>-122000</v>
       </c>
       <c r="AK96" s="3">
         <v>-122000</v>
       </c>
       <c r="AL96" s="3">
+        <v>-122000</v>
+      </c>
+      <c r="AM96" s="3">
         <v>-124000</v>
       </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9488,8 +9724,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9598,8 +9837,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9708,118 +9950,124 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E100" s="3">
         <v>-334000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-260000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-185000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-86000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-166000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-258000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-227000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-879000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>121000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-573000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-883000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-918000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1046000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1175000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1743000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-842000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1480000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>886000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1188000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-614000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1095000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1911000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>248000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-421000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-399000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-2055000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-612000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1365000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>458000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1033000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-531000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-788000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-571000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>664000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-607000</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9850,8 +10098,8 @@
       <c r="L101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -9928,114 +10176,120 @@
       <c r="AL101" s="3">
         <v>0</v>
       </c>
+      <c r="AM101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>337000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-226000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>331000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-251000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>128000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-138000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>161000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>37000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-74000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-50000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>20000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-364000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>367000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-83000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>32000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>39000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>398000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>7000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-177000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>209000</v>
       </c>
-      <c r="X102" s="3">
-        <v>0</v>
-      </c>
       <c r="Y102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="3">
         <v>-249000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-12000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>48000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>52000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>39000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-29000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>39000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-167000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-73000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>208000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>40000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>6000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>47000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-57000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ALL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ALL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="92">
   <si>
     <t>ALL</t>
   </si>
@@ -656,497 +656,509 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="40" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="14" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="41" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>17345000</v>
+      </c>
+      <c r="E8" s="3">
         <v>17255000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>16633000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>16452000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>16506000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>16627000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>15714000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>15259000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>14832000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>14497000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>13979000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>13786000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>13648000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>13208000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>12219000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>12336000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>13011000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>12480000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>12646000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>12451000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>10962000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>10678000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>10403000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>9866000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>11476000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>11085000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>11156000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>11006000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>9486000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>10469000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>10103000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>9770000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>9854000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>9686000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>9634000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>9496000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>9350000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>9294000</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>9929000</v>
+      </c>
+      <c r="E9" s="3">
         <v>10822000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>12513000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>13235000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>11423000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>12763000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>13093000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>11736000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>10970000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>12340000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>13774000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>12335000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1725000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1683000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1618000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1608000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1602000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1582000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1545000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1523000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1382000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1386000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1344000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1365000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1382000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1425000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1362000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1364000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1336000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1317000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1296000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1273000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1239000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1200000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1176000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1169000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>1157000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>1138000</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>7416000</v>
+      </c>
+      <c r="E10" s="3">
         <v>6433000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4120000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3217000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>5083000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>3864000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2621000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3523000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3862000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2157000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>205000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1451000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>11923000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>11525000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>10601000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>10728000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>11409000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>10898000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>11101000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>10928000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>9580000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>9292000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>9059000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>8501000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>10094000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>9660000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>9794000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>9642000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>8150000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>9152000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>8807000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>8497000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>8615000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>8486000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>8458000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>8327000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>8193000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>8156000</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1187,8 +1199,9 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1303,8 +1316,11 @@
       <c r="AN12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1419,201 +1435,207 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E14" s="3">
         <v>-703000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-875000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>16000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>10000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>28000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>13000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>10000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>28000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>87000</v>
-      </c>
-      <c r="M14" s="3">
-        <v>27000</v>
       </c>
       <c r="N14" s="3">
         <v>27000</v>
       </c>
       <c r="O14" s="3">
+        <v>27000</v>
+      </c>
+      <c r="P14" s="3">
         <v>24000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>14000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>12000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>25000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>23000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>100000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>73000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>39000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>195000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>750000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>213000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>66000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>16000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>74000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>33000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>15000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>16000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>25000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>18000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>163000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>39000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>88000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>70000</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>80000</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>77000</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>56000</v>
+      </c>
+      <c r="E15" s="3">
         <v>59000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>57000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>59000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>70000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>71000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>70000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>69000</v>
-      </c>
-      <c r="K15" s="3">
-        <v>83000</v>
       </c>
       <c r="L15" s="3">
         <v>83000</v>
       </c>
       <c r="M15" s="3">
+        <v>83000</v>
+      </c>
+      <c r="N15" s="3">
         <v>82000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>81000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>89000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>90000</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>87000</v>
       </c>
       <c r="R15" s="3">
         <v>87000</v>
       </c>
       <c r="S15" s="3">
-        <v>109000</v>
+        <v>87000</v>
       </c>
       <c r="T15" s="3">
         <v>109000</v>
       </c>
       <c r="U15" s="3">
+        <v>109000</v>
+      </c>
+      <c r="V15" s="3">
         <v>105000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>53000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>30000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>31000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>29000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>28000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>30000</v>
-      </c>
-      <c r="AB15" s="3">
-        <v>32000</v>
       </c>
       <c r="AC15" s="3">
         <v>32000</v>
@@ -1622,19 +1644,19 @@
         <v>32000</v>
       </c>
       <c r="AE15" s="3">
+        <v>32000</v>
+      </c>
+      <c r="AF15" s="3">
         <v>36000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>24000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>23000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>22000</v>
-      </c>
-      <c r="AI15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AJ15" s="3" t="s">
         <v>8</v>
@@ -1642,8 +1664,8 @@
       <c r="AK15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AL15" s="3">
-        <v>0</v>
+      <c r="AL15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AM15" s="3">
         <v>0</v>
@@ -1651,8 +1673,11 @@
       <c r="AN15" s="3">
         <v>0</v>
       </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1690,240 +1715,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>12312000</v>
+      </c>
+      <c r="E17" s="3">
         <v>13038000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>14705000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>15617000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>13946000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>15077000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>15173000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>13688000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>12870000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>14343000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>15602000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>14079000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>14058000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>14118000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>13530000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>11535000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>11618000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>12254000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>10849000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>9419000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>8098000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>9150000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>9024000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>8835000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>9245000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>9925000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>10078000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>9386000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>10196000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>9291000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>9206000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>8507000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>8697000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>8715000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>8783000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>8484000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>8092000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>8529000</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>5033000</v>
+      </c>
+      <c r="E18" s="3">
         <v>4217000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1928000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>835000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2560000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1550000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>541000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1571000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1962000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>154000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1623000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-293000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-410000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-910000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1311000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>801000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1393000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>226000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1797000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>3032000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2864000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1528000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1379000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1031000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2231000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1160000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1078000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1620000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-710000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1178000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>897000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1263000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1157000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>971000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>851000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>1012000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>1258000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>765000</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1964,8 +1996,9 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2002,8 +2035,8 @@
       <c r="N20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
+      <c r="O20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P20" s="3">
         <v>0</v>
@@ -2080,163 +2113,169 @@
       <c r="AN20" s="3">
         <v>0</v>
       </c>
+      <c r="AO20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>5089000</v>
+      </c>
+      <c r="E21" s="3">
         <v>4276000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1985000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>894000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2630000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1621000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>611000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1640000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2045000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>237000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-1541000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-212000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-209000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-716000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-1095000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1037000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1661000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>473000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2108000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>3292000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>3050000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1710000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1542000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1186000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>2402000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1319000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1238000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1777000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-575000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1306000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1023000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1385000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1282000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1091000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>970000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1131000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>1355000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>862000</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>98000</v>
+      </c>
+      <c r="E22" s="3">
         <v>101000</v>
-      </c>
-      <c r="E22" s="3">
-        <v>100000</v>
       </c>
       <c r="F22" s="3">
         <v>100000</v>
       </c>
       <c r="G22" s="3">
+        <v>100000</v>
+      </c>
+      <c r="H22" s="3">
         <v>101000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>104000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>98000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>97000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>107000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>88000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>98000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>86000</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
       <c r="P22" s="3">
         <v>0</v>
       </c>
@@ -2312,240 +2351,249 @@
       <c r="AN22" s="3">
         <v>0</v>
       </c>
+      <c r="AO22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4915000</v>
+      </c>
+      <c r="E23" s="3">
         <v>4819000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2703000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>719000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2449000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1418000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>430000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1464000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1827000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-21000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1748000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-406000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-410000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-910000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1311000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>801000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1393000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>226000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1797000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>3032000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2864000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1528000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1379000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1031000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>2231000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1160000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1078000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1620000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-710000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1178000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>897000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1263000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1157000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>971000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>851000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>1012000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>1258000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>765000</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1088000</v>
+      </c>
+      <c r="E24" s="3">
         <v>1075000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>604000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>123000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>559000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>254000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>83000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>266000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>340000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-17000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-373000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-85000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-114000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-236000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-289000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>151000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>281000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>20000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>362000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>626000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>594000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>312000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>273000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>194000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>458000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>229000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>227000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>328000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-170000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>230000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>180000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>257000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>414000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>305000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>272000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>317000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>418000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>245000</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2660,240 +2708,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3827000</v>
+      </c>
+      <c r="E26" s="3">
         <v>3744000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2099000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>596000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1890000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1164000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>347000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1198000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1487000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-4000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1375000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-321000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-296000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-674000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1022000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>650000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1112000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>206000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1435000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2406000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2270000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1216000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1106000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>837000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1773000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>931000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>851000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1292000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-540000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>948000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>717000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1006000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>743000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>666000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>579000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>695000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>840000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>520000</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3803000</v>
+      </c>
+      <c r="E27" s="3">
         <v>3717000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2079000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>566000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1899000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1161000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>301000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1189000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1460000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-41000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1389000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-346000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-303000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-685000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1040000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>634000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1111000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>183000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1399000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2385000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2244000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1189000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1080000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>801000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1707000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>889000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>821000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1261000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-583000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>911000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>678000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>977000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>714000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>637000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>550000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>666000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>811000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>491000</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3008,8 +3065,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3046,12 +3106,12 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-      <c r="O29" s="3" t="s">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P29" s="3">
-        <v>0</v>
-      </c>
       <c r="Q29" s="3">
         <v>0</v>
       </c>
@@ -3059,31 +3119,31 @@
         <v>0</v>
       </c>
       <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
         <v>-321000</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>325000</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>196000</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-3793000</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>354000</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-63000</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>144000</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-288000</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
@@ -3094,23 +3154,23 @@
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF29" s="3">
         <v>-2000</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>31000</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>506000</v>
-      </c>
-      <c r="AJ29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AK29" s="3" t="s">
         <v>8</v>
@@ -3124,8 +3184,11 @@
       <c r="AN29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3240,8 +3303,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3356,8 +3422,11 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3394,8 +3463,8 @@
       <c r="N32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
+      <c r="O32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P32" s="3">
         <v>0</v>
@@ -3472,124 +3541,130 @@
       <c r="AN32" s="3">
         <v>0</v>
       </c>
+      <c r="AO32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3832000</v>
+      </c>
+      <c r="E33" s="3">
         <v>3746000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2109000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>595000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1928000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1190000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>331000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1218000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1489000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-5000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1352000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-320000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-303000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-685000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1040000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>634000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>790000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>508000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1595000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-1408000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2598000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1126000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1224000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>513000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1707000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>889000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>821000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1261000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-585000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>942000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>678000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>977000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1220000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>637000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>550000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>666000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>811000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>491000</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3704,245 +3779,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3832000</v>
+      </c>
+      <c r="E35" s="3">
         <v>3746000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2109000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>595000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1928000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1190000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>331000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1218000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1489000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-5000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1352000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-320000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-303000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-685000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1040000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>634000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>790000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>508000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1595000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-1408000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2598000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1126000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1224000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>513000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1707000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>889000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>821000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1261000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-585000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>942000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>678000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>977000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1220000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>637000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>550000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>666000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>811000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>491000</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3983,8 +4067,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4025,163 +4110,167 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>678000</v>
+      </c>
+      <c r="E41" s="3">
         <v>931000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>995000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>840000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>704000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>816000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>599000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>850000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>722000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>860000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>699000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>662000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>736000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>786000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>766000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1130000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>763000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>690000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>656000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>709000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>377000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>370000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>547000</v>
-      </c>
-      <c r="Z41" s="3">
-        <v>338000</v>
       </c>
       <c r="AA41" s="3">
         <v>338000</v>
       </c>
       <c r="AB41" s="3">
+        <v>338000</v>
+      </c>
+      <c r="AC41" s="3">
         <v>587000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>599000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>551000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>499000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>460000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>489000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>450000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>617000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>690000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>482000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>442000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>436000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>389000</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>4887000</v>
+      </c>
+      <c r="E42" s="3">
         <v>8743000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>9640000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>6541000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>4537000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>6995000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>5289000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>4319000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>5146000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>3369000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>5137000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>6724000</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
       <c r="P42" s="3">
         <v>0</v>
       </c>
@@ -4257,124 +4346,130 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>11474000</v>
+      </c>
+      <c r="E43" s="3">
         <v>11745000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>11271000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>11053000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>10614000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>11041000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>10762000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>10573000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>10044000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>10102000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>9713000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>9483000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>9165000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>9150000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>8824000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>8874000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>8364000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>8406000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>8146000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>7921000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>6479000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>6609000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>6367000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>6401000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>6472000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>6558000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>6380000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>6201000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>6154000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>6196000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>5953000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>5856000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>5786000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>5922000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>5693000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>5649000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>5597000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>5799000</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4411,8 +4506,8 @@
       <c r="N44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -4489,47 +4584,50 @@
       <c r="AN44" s="3">
         <v>0</v>
       </c>
+      <c r="AO44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>9356000</v>
+      </c>
+      <c r="E45" s="3">
         <v>10277000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>11126000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>14627000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>12765000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>12904000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>9461000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>9416000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>9472000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>9731000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>9728000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>10088000</v>
       </c>
-      <c r="O45" s="3">
-        <v>0</v>
-      </c>
       <c r="P45" s="3">
         <v>0</v>
       </c>
@@ -4605,47 +4703,50 @@
       <c r="AN45" s="3">
         <v>0</v>
       </c>
+      <c r="AO45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>26395000</v>
+      </c>
+      <c r="E46" s="3">
         <v>31696000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>33032000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>33061000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>28620000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>31756000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>26111000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>25158000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>25384000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>24062000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>25277000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>26957000</v>
       </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
       <c r="P46" s="3">
         <v>0</v>
       </c>
@@ -4721,302 +4822,311 @@
       <c r="AN46" s="3">
         <v>0</v>
       </c>
+      <c r="AO46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>76368000</v>
+      </c>
+      <c r="E47" s="3">
         <v>71750000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>66027000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>65840000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>66468000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>64978000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>63524000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>61724000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>59659000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>57656000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>56095000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>54354000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>61829000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>61006000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>61055000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>61768000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>64701000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>61840000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>62570000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>60076000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>94237000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>91197000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>89637000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>84783000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>88221000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>89158000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>86345000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>84018000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>81136000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>83855000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>83140000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>83195000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>82677000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>82680000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>81203000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>81050000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>81707000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>81038000</v>
       </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>781000</v>
+      </c>
+      <c r="E48" s="3">
         <v>601000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>619000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>632000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>834000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>714000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>777000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>802000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1022000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>909000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>945000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>971000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1221000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1008000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>975000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>966000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1253000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>965000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1026000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1002000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1057000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1076000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1100000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1123000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1628000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1535000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1519000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1521000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1045000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1032000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1040000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1060000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1072000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>1067000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>1072000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>1067000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>1065000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>1013000</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>9839000</v>
+      </c>
+      <c r="E49" s="3">
         <v>9213000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>9048000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>8902000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>9772000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>8957000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>9614000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>9448000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>10408000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>9326000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>9109000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>8973000</v>
-      </c>
-      <c r="O49" s="3">
-        <v>3502000</v>
       </c>
       <c r="P49" s="3">
         <v>3502000</v>
       </c>
       <c r="Q49" s="3">
+        <v>3502000</v>
+      </c>
+      <c r="R49" s="3">
         <v>3496000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3497000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3502000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>3389000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>3349000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3350000</v>
-      </c>
-      <c r="W49" s="3">
-        <v>2544000</v>
       </c>
       <c r="X49" s="3">
         <v>2544000</v>
@@ -5028,22 +5138,22 @@
         <v>2544000</v>
       </c>
       <c r="AA49" s="3">
-        <v>2545000</v>
+        <v>2544000</v>
       </c>
       <c r="AB49" s="3">
         <v>2545000</v>
       </c>
       <c r="AC49" s="3">
-        <v>2547000</v>
+        <v>2545000</v>
       </c>
       <c r="AD49" s="3">
         <v>2547000</v>
       </c>
       <c r="AE49" s="3">
+        <v>2547000</v>
+      </c>
+      <c r="AF49" s="3">
         <v>2530000</v>
-      </c>
-      <c r="AF49" s="3">
-        <v>2189000</v>
       </c>
       <c r="AG49" s="3">
         <v>2189000</v>
@@ -5052,25 +5162,28 @@
         <v>2189000</v>
       </c>
       <c r="AI49" s="3">
+        <v>2189000</v>
+      </c>
+      <c r="AJ49" s="3">
         <v>2181000</v>
-      </c>
-      <c r="AJ49" s="3">
-        <v>2309000</v>
       </c>
       <c r="AK49" s="3">
         <v>2309000</v>
       </c>
       <c r="AL49" s="3">
+        <v>2309000</v>
+      </c>
+      <c r="AM49" s="3">
         <v>2295000</v>
-      </c>
-      <c r="AM49" s="3">
-        <v>1219000</v>
       </c>
       <c r="AN49" s="3">
         <v>1219000</v>
       </c>
+      <c r="AO49" s="3">
+        <v>1219000</v>
+      </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5185,8 +5298,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5301,70 +5417,73 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5023000</v>
+      </c>
+      <c r="E52" s="3">
         <v>5928000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5909000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5453000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4707000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>6386000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>7046000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>6849000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5505000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>6776000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>6997000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6432000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>382000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>492000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>118000</v>
       </c>
-      <c r="R52" s="3" t="s">
+      <c r="S52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S52" s="3">
-        <v>0</v>
-      </c>
       <c r="T52" s="3">
+        <v>0</v>
+      </c>
+      <c r="U52" s="3">
         <v>36803000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>36969000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>36829000</v>
-      </c>
-      <c r="W52" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="X52" s="3" t="s">
         <v>8</v>
@@ -5381,8 +5500,8 @@
       <c r="AB52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC52" s="3">
-        <v>0</v>
+      <c r="AC52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD52" s="3">
         <v>0</v>
@@ -5417,8 +5536,11 @@
       <c r="AN52" s="3">
         <v>0</v>
       </c>
+      <c r="AO52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5533,124 +5655,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>119758000</v>
+      </c>
+      <c r="E54" s="3">
         <v>120402000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>115894000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>115161000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>111617000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>113743000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>108368000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>105241000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>103362000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>101176000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>100514000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>99631000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>97989000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>97676000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>96350000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>97150000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>99440000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>133440000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>132643000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>129811000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>125987000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>122750000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>121266000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>116107000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>119950000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>121073000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>118374000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>115834000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>112249000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>114490000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>113369000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>113289000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>112422000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>113632000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>110865000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>110243000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>108610000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>108537000</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5691,8 +5819,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5733,47 +5862,48 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>42498000</v>
+      </c>
+      <c r="E57" s="3">
         <v>44657000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>45796000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>45494000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>43484000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>44470000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>43128000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>41634000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>41211000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>42139000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>41918000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>39977000</v>
       </c>
-      <c r="O57" s="3">
-        <v>0</v>
-      </c>
       <c r="P57" s="3">
         <v>0</v>
       </c>
@@ -5849,47 +5979,50 @@
       <c r="AN57" s="3">
         <v>0</v>
       </c>
+      <c r="AO57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>618000</v>
+      </c>
+      <c r="E58" s="3">
         <v>601000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>604000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>601000</v>
       </c>
-      <c r="G58" s="3">
-        <v>684000</v>
-      </c>
       <c r="H58" s="3">
+        <v>601000</v>
+      </c>
+      <c r="I58" s="3">
         <v>9000</v>
-      </c>
-      <c r="I58" s="3">
-        <v>2000</v>
       </c>
       <c r="J58" s="3">
         <v>2000</v>
       </c>
       <c r="K58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="L58" s="3">
         <v>351000</v>
-      </c>
-      <c r="L58" s="3">
-        <v>2000</v>
       </c>
       <c r="M58" s="3">
         <v>2000</v>
       </c>
       <c r="N58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="O58" s="3">
         <v>3000</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
@@ -5965,163 +6098,169 @@
       <c r="AN58" s="3">
         <v>0</v>
       </c>
+      <c r="AO58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>29085000</v>
+      </c>
+      <c r="E59" s="3">
         <v>29186000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>28047000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>29543000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>29022000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>29230000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>25932000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>24945000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>24714000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>24527000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>23380000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>22502000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>24843000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>24211000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>23229000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>22429000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>22490000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>21753000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>20853000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>20274000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>49274000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>49140000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>48221000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>46664000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>48503000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>48555000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>48232000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>48055000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>47670000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>48313000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>47936000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>47972000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>48614000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>48542000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>48216000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>48129000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>48185000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>48745000</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>72201000</v>
+      </c>
+      <c r="E60" s="3">
         <v>74444000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>74447000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>75638000</v>
       </c>
-      <c r="G60" s="3">
-        <v>73190000</v>
-      </c>
       <c r="H60" s="3">
+        <v>73107000</v>
+      </c>
+      <c r="I60" s="3">
         <v>73709000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>69062000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>66581000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>66276000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>66668000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>65300000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>62482000</v>
       </c>
-      <c r="O60" s="3">
-        <v>0</v>
-      </c>
       <c r="P60" s="3">
         <v>0</v>
       </c>
@@ -6197,163 +6336,169 @@
       <c r="AN60" s="3">
         <v>0</v>
       </c>
+      <c r="AO60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7057000</v>
+      </c>
+      <c r="E61" s="3">
         <v>7489000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7487000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7486000</v>
       </c>
-      <c r="G61" s="3">
-        <v>7637000</v>
-      </c>
       <c r="H61" s="3">
+        <v>7720000</v>
+      </c>
+      <c r="I61" s="3">
         <v>8083000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>8082000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>7938000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>7857000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>7946000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>7949000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>8452000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>7964000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>7967000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>7970000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>7973000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>7976000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>7980000</v>
-      </c>
-      <c r="U61" s="3">
-        <v>7996000</v>
       </c>
       <c r="V61" s="3">
         <v>7996000</v>
       </c>
       <c r="W61" s="3">
+        <v>7996000</v>
+      </c>
+      <c r="X61" s="3">
         <v>7825000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>6635000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>6634000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>6633000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>6631000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>6630000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>6628000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>6453000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>6451000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>6450000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>6448000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>6847000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>6350000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>6349000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>6348000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>6346000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>6347000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>5110000</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>9511000</v>
+      </c>
+      <c r="E62" s="3">
         <v>10669000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>9955000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>9985000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>9187000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>10902000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>12651000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>12242000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>11270000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>12115000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>11893000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>11324000</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
-      </c>
       <c r="P62" s="3">
         <v>0</v>
       </c>
@@ -6361,76 +6506,79 @@
         <v>0</v>
       </c>
       <c r="R62" s="3">
+        <v>0</v>
+      </c>
+      <c r="S62" s="3">
         <v>402000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>833000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>33132000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>33533000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>33876000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1355000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>905000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>842000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>331000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1154000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1079000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>997000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>817000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>425000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>660000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>723000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>725000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>782000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>1249000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>1104000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>833000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>487000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>935000</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6545,8 +6693,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6661,8 +6812,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6777,124 +6931,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>89169000</v>
+      </c>
+      <c r="E66" s="3">
         <v>92913000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>91889000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>93109000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>90250000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>92905000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>89795000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>86761000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>85732000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>86729000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>85142000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>82258000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>80501000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>80003000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>76235000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>73938000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>74261000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>106711000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>104436000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>102992000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>95770000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>95487000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>94280000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>91934000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>93952000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>94933000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>93898000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>92416000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>90937000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>90857000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>90247000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>90012000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>89871000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>91513000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>89364000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>89085000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>88037000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>87603000</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6935,8 +7095,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7051,8 +7212,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7167,8 +7331,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7203,7 +7370,7 @@
         <v>2001000</v>
       </c>
       <c r="N70" s="3">
-        <v>1970000</v>
+        <v>2001000</v>
       </c>
       <c r="O70" s="3">
         <v>1970000</v>
@@ -7224,13 +7391,13 @@
         <v>1970000</v>
       </c>
       <c r="U70" s="3">
-        <v>2170000</v>
+        <v>1970000</v>
       </c>
       <c r="V70" s="3">
         <v>2170000</v>
       </c>
       <c r="W70" s="3">
-        <v>1970000</v>
+        <v>2170000</v>
       </c>
       <c r="X70" s="3">
         <v>1970000</v>
@@ -7242,13 +7409,13 @@
         <v>1970000</v>
       </c>
       <c r="AA70" s="3">
+        <v>1970000</v>
+      </c>
+      <c r="AB70" s="3">
         <v>2248000</v>
       </c>
-      <c r="AB70" s="3">
+      <c r="AC70" s="3">
         <v>3052000</v>
-      </c>
-      <c r="AC70" s="3">
-        <v>1930000</v>
       </c>
       <c r="AD70" s="3">
         <v>1930000</v>
@@ -7257,7 +7424,7 @@
         <v>1930000</v>
       </c>
       <c r="AF70" s="3">
-        <v>2303000</v>
+        <v>1930000</v>
       </c>
       <c r="AG70" s="3">
         <v>2303000</v>
@@ -7266,7 +7433,7 @@
         <v>2303000</v>
       </c>
       <c r="AI70" s="3">
-        <v>1746000</v>
+        <v>2303000</v>
       </c>
       <c r="AJ70" s="3">
         <v>1746000</v>
@@ -7283,8 +7450,11 @@
       <c r="AN70" s="3">
         <v>1746000</v>
       </c>
+      <c r="AO70" s="3">
+        <v>1746000</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7399,124 +7569,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>62393000</v>
+      </c>
+      <c r="E72" s="3">
         <v>58853000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>55400000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>53586000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>53288000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>51635000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>50718000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>50662000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>49716000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>48491000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>48766000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>50388000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>50970000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>51490000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>52412000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>53688000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>53294000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>52736000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>52464000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>51107000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>52767000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>50336000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>49380000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>48326000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>48074000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>46527000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>45803000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>45148000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>45708000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>46178000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>45508000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>45031000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>43162000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>42125000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>41622000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>41208000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>40678000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>39990000</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7631,8 +7807,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7747,8 +7926,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7863,124 +8045,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>28609000</v>
+      </c>
+      <c r="E76" s="3">
         <v>25504000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>22018000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>20054000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>19441000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>18876000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>16592000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>16638000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>15769000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>12592000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>13516000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>15524000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>15518000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>15703000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>18145000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>21242000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>23209000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>24759000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>26037000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>24649000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>28247000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>25293000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>25016000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>22203000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>23750000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>23088000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>22546000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>21488000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>19382000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>21330000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>20819000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>20974000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>20805000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>20373000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>19755000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>19412000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>18827000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>19188000</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8095,245 +8283,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3832000</v>
+      </c>
+      <c r="E81" s="3">
         <v>3746000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2109000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>595000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1928000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1190000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>331000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1218000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1489000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-5000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1352000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-320000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-303000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-685000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1040000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>634000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>790000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>508000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1595000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-1408000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2598000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1126000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1224000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>513000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1707000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>889000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>821000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1261000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-585000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>942000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>678000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>977000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1220000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>637000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>550000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>666000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>811000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>491000</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8374,124 +8571,128 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>81000</v>
+      </c>
+      <c r="E83" s="3">
         <v>69000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>62000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>63000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>82000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>93000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>104000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>96000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>112000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>104000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>129000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>149000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>201000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>194000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>216000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>236000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>268000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>247000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>311000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>260000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>186000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>182000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>163000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>155000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>171000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>159000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>160000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>157000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>135000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>128000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>126000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>122000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>125000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>120000</v>
-      </c>
-      <c r="AK83" s="3">
-        <v>119000</v>
       </c>
       <c r="AL83" s="3">
         <v>119000</v>
       </c>
       <c r="AM83" s="3">
-        <v>97000</v>
+        <v>119000</v>
       </c>
       <c r="AN83" s="3">
         <v>97000</v>
       </c>
+      <c r="AO83" s="3">
+        <v>97000</v>
+      </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8606,8 +8807,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8722,8 +8926,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8838,8 +9045,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8954,8 +9164,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9070,124 +9283,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2989000</v>
+      </c>
+      <c r="E89" s="3">
         <v>3284000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1873000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1964000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1705000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3201000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2359000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1666000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1225000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1233000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1169000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>601000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>970000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2046000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1673000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>432000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>871000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1329000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1551000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1365000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1319000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1296000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1849000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1027000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1234000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1833000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1348000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>714000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1357000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1728000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1464000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>626000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1100000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1866000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>491000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>857000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>1251000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>1384000</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9228,124 +9447,128 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-89000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-48000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>1000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-92000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-50000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-63000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-56000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-41000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-71000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-55000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-62000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-79000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-68000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-124000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-98000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-130000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-59000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-89000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-136000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-61000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-73000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-69000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-101000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-65000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-140000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-120000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-93000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-80000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-82000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-67000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-66000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-62000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-83000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-70000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-72000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-74000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-123000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9460,8 +9683,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9576,124 +9802,130 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1949000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2805000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1208000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1293000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1671000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2685000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2524000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1372000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1105000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-845000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-253000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-796000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-447000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1143000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1119000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>981000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>221000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>446000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-670000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>513000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2198000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-285000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1026000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>68000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>428000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-2093000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-879000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-263000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>737000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1145000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-60000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1251000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-140000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-1127000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>337000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-280000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-1868000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-834000</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9734,22 +9966,23 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>263000</v>
+      </c>
+      <c r="E96" s="3">
         <v>264000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>265000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>244000</v>
-      </c>
-      <c r="G96" s="3">
-        <v>243000</v>
       </c>
       <c r="H96" s="3">
         <v>243000</v>
@@ -9758,7 +9991,7 @@
         <v>243000</v>
       </c>
       <c r="J96" s="3">
-        <v>233000</v>
+        <v>243000</v>
       </c>
       <c r="K96" s="3">
         <v>233000</v>
@@ -9767,91 +10000,94 @@
         <v>233000</v>
       </c>
       <c r="M96" s="3">
+        <v>233000</v>
+      </c>
+      <c r="N96" s="3">
         <v>235000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>224000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-228000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-232000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-236000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-230000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-235000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-241000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-245000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-164000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-168000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-169000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-172000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-159000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-163000</v>
-      </c>
-      <c r="AB96" s="3">
-        <v>-166000</v>
       </c>
       <c r="AC96" s="3">
         <v>-166000</v>
       </c>
       <c r="AD96" s="3">
+        <v>-166000</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-158000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-159000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-160000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-163000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-132000</v>
-      </c>
-      <c r="AI96" s="3">
-        <v>-134000</v>
       </c>
       <c r="AJ96" s="3">
         <v>-134000</v>
       </c>
       <c r="AK96" s="3">
+        <v>-134000</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-135000</v>
-      </c>
-      <c r="AL96" s="3">
-        <v>-122000</v>
       </c>
       <c r="AM96" s="3">
         <v>-122000</v>
       </c>
       <c r="AN96" s="3">
+        <v>-122000</v>
+      </c>
+      <c r="AO96" s="3">
         <v>-124000</v>
       </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9966,8 +10202,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10082,8 +10321,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10198,124 +10440,130 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1293000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-634000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-620000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-334000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-260000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-185000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-86000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-166000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-258000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-227000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-879000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>121000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-573000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-883000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-918000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1046000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1175000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1743000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-842000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1480000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>886000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1188000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-614000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1095000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1911000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>248000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-421000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-399000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-2055000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-612000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1365000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>458000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1033000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-531000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-788000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-571000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>664000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-607000</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10352,8 +10600,8 @@
       <c r="N101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -10430,120 +10678,126 @@
       <c r="AN101" s="3">
         <v>0</v>
       </c>
+      <c r="AO101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-253000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-155000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>45000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>337000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-226000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>331000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-251000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>128000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-138000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>161000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>37000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-74000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-50000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>20000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-364000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>367000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-83000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>32000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>39000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>398000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>7000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-177000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>209000</v>
       </c>
-      <c r="Z102" s="3">
-        <v>0</v>
-      </c>
       <c r="AA102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB102" s="3">
         <v>-249000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-12000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>48000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>52000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>39000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-29000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>39000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-167000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-73000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>208000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>40000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>6000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>47000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-57000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ALL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ALL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="92">
   <si>
     <t>ALL</t>
   </si>
@@ -656,509 +656,521 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="14" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="41" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="42" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>16941000</v>
+      </c>
+      <c r="E8" s="3">
         <v>17345000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>17255000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>16633000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>16452000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>16506000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>16627000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>15714000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>15259000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>14832000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>14497000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>13979000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>13786000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>13648000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>13208000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>12219000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>12336000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>13011000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>12480000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>12646000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>12451000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>10962000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>10678000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>10403000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>9866000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>11476000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>11085000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>11156000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>11006000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>9486000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>10469000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>10103000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>9770000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>9854000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>9686000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>9634000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>9496000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>9350000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>9294000</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>11439000</v>
+      </c>
+      <c r="E9" s="3">
         <v>9929000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>10822000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>12513000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>13235000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>11423000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>12763000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>13093000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>11736000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>10970000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>12340000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>13774000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>12335000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1725000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1683000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1618000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1608000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1602000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1582000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1545000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1523000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1382000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1386000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1344000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1365000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1382000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1425000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1362000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1364000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1336000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1317000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1296000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1273000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1239000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1200000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1176000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>1169000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>1157000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>1138000</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>5502000</v>
+      </c>
+      <c r="E10" s="3">
         <v>7416000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>6433000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4120000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3217000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>5083000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3864000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2621000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3523000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3862000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2157000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>205000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1451000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>11923000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>11525000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>10601000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>10728000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>11409000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>10898000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>11101000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>10928000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>9580000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>9292000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>9059000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>8501000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>10094000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>9660000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>9794000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>9642000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>8150000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>9152000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>8807000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>8497000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>8615000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>8486000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>8458000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>8327000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>8193000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>8156000</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1200,8 +1212,9 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1319,8 +1332,11 @@
       <c r="AO12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1438,207 +1454,213 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E14" s="3">
         <v>20000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-703000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-875000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>16000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>10000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>28000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>13000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>10000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>28000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>87000</v>
-      </c>
-      <c r="N14" s="3">
-        <v>27000</v>
       </c>
       <c r="O14" s="3">
         <v>27000</v>
       </c>
       <c r="P14" s="3">
+        <v>27000</v>
+      </c>
+      <c r="Q14" s="3">
         <v>24000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>14000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>12000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>25000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>23000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>100000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>73000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>39000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>195000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>750000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>213000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>66000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>16000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>74000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>33000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>15000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>16000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>25000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>18000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>163000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>39000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>88000</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>70000</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>80000</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>77000</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>47000</v>
+      </c>
+      <c r="E15" s="3">
         <v>56000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>59000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>57000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>59000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>70000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>71000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>70000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>69000</v>
-      </c>
-      <c r="L15" s="3">
-        <v>83000</v>
       </c>
       <c r="M15" s="3">
         <v>83000</v>
       </c>
       <c r="N15" s="3">
+        <v>83000</v>
+      </c>
+      <c r="O15" s="3">
         <v>82000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>81000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>89000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>90000</v>
-      </c>
-      <c r="R15" s="3">
-        <v>87000</v>
       </c>
       <c r="S15" s="3">
         <v>87000</v>
       </c>
       <c r="T15" s="3">
-        <v>109000</v>
+        <v>87000</v>
       </c>
       <c r="U15" s="3">
         <v>109000</v>
       </c>
       <c r="V15" s="3">
+        <v>109000</v>
+      </c>
+      <c r="W15" s="3">
         <v>105000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>53000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>30000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>31000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>29000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>28000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>30000</v>
-      </c>
-      <c r="AC15" s="3">
-        <v>32000</v>
       </c>
       <c r="AD15" s="3">
         <v>32000</v>
@@ -1647,28 +1669,28 @@
         <v>32000</v>
       </c>
       <c r="AF15" s="3">
+        <v>32000</v>
+      </c>
+      <c r="AG15" s="3">
         <v>36000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>24000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>23000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>22000</v>
       </c>
-      <c r="AJ15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK15" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AL15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AM15" s="3">
-        <v>0</v>
+      <c r="AM15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AN15" s="3">
         <v>0</v>
@@ -1676,8 +1698,11 @@
       <c r="AO15" s="3">
         <v>0</v>
       </c>
+      <c r="AP15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1716,246 +1741,253 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>13730000</v>
+      </c>
+      <c r="E17" s="3">
         <v>12312000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>13038000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>14705000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>15617000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>13946000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>15077000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>15173000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>13688000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>12870000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>14343000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>15602000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>14079000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>14058000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>14118000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>13530000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>11535000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>11618000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>12254000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>10849000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>9419000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>8098000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>9150000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>9024000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>8835000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>9245000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>9925000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>10078000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>9386000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>10196000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>9291000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>9206000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>8507000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>8697000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>8715000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>8783000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>8484000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>8092000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>8529000</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>3211000</v>
+      </c>
+      <c r="E18" s="3">
         <v>5033000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>4217000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1928000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>835000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2560000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1550000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>541000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1571000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1962000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>154000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1623000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-293000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-410000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-910000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1311000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>801000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1393000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>226000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1797000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>3032000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2864000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1528000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1379000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1031000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2231000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1160000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1078000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1620000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-710000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1178000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>897000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1263000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1157000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>971000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>851000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>1012000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>1258000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>765000</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1997,8 +2029,9 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2038,8 +2071,8 @@
       <c r="O20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
+      <c r="P20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q20" s="3">
         <v>0</v>
@@ -2116,127 +2149,133 @@
       <c r="AO20" s="3">
         <v>0</v>
       </c>
+      <c r="AP20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>3258000</v>
+      </c>
+      <c r="E21" s="3">
         <v>5089000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>4276000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1985000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>894000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2630000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1621000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>611000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1640000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2045000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>237000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-1541000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-212000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-209000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-716000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-1095000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1037000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1661000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>473000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2108000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>3292000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>3050000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1710000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1542000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1186000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>2402000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1319000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1238000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1777000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-575000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1306000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1023000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1385000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1282000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1091000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>970000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>1131000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>1355000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>862000</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2244,41 +2283,41 @@
         <v>98000</v>
       </c>
       <c r="E22" s="3">
+        <v>98000</v>
+      </c>
+      <c r="F22" s="3">
         <v>101000</v>
-      </c>
-      <c r="F22" s="3">
-        <v>100000</v>
       </c>
       <c r="G22" s="3">
         <v>100000</v>
       </c>
       <c r="H22" s="3">
+        <v>100000</v>
+      </c>
+      <c r="I22" s="3">
         <v>101000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>104000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>98000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>97000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>107000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>88000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>98000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>86000</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
       <c r="Q22" s="3">
         <v>0</v>
       </c>
@@ -2354,246 +2393,255 @@
       <c r="AO22" s="3">
         <v>0</v>
       </c>
+      <c r="AP22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3108000</v>
+      </c>
+      <c r="E23" s="3">
         <v>4915000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>4819000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2703000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>719000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2449000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1418000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>430000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1464000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1827000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-21000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1748000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-406000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-410000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-910000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1311000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>801000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1393000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>226000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1797000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>3032000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2864000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1528000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1379000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1031000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2231000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1160000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1078000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1620000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-710000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1178000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>897000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1263000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1157000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>971000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>851000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>1012000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>1258000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>765000</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>650000</v>
+      </c>
+      <c r="E24" s="3">
         <v>1088000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1075000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>604000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>123000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>559000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>254000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>83000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>266000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>340000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-17000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-373000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-85000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-114000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-236000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-289000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>151000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>281000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>20000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>362000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>626000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>594000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>312000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>273000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>194000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>458000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>229000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>227000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>328000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-170000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>230000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>180000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>257000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>414000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>305000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>272000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>317000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>418000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>245000</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2711,246 +2759,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2458000</v>
+      </c>
+      <c r="E26" s="3">
         <v>3827000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3744000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2099000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>596000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1890000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1164000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>347000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1198000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1487000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-4000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1375000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-321000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-296000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-674000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-1022000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>650000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1112000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>206000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1435000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2406000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2270000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1216000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1106000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>837000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1773000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>931000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>851000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1292000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-540000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>948000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>717000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1006000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>743000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>666000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>579000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>695000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>840000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>520000</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2428000</v>
+      </c>
+      <c r="E27" s="3">
         <v>3803000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3717000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2079000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>566000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1899000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1161000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>301000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1189000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1460000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-41000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1389000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-346000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-303000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-685000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1040000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>634000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1111000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>183000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1399000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2385000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2244000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1189000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1080000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>801000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1707000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>889000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>821000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1261000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-583000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>911000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>678000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>977000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>714000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>637000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>550000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>666000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>811000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>491000</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3068,8 +3125,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3109,11 +3169,11 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q29" s="3">
-        <v>0</v>
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R29" s="3">
         <v>0</v>
@@ -3122,32 +3182,32 @@
         <v>0</v>
       </c>
       <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
         <v>-321000</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>325000</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>196000</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-3793000</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>354000</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-63000</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>144000</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-288000</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3157,24 +3217,24 @@
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG29" s="3">
         <v>-2000</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>31000</v>
       </c>
-      <c r="AH29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK29" s="3">
         <v>506000</v>
       </c>
-      <c r="AK29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AL29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3187,8 +3247,11 @@
       <c r="AO29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3306,8 +3369,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3425,8 +3491,11 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3466,8 +3535,8 @@
       <c r="O32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
+      <c r="P32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q32" s="3">
         <v>0</v>
@@ -3544,127 +3613,133 @@
       <c r="AO32" s="3">
         <v>0</v>
       </c>
+      <c r="AP32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2457000</v>
+      </c>
+      <c r="E33" s="3">
         <v>3832000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3746000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2109000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>595000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1928000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1190000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>331000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1218000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1489000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-5000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1352000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-320000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-303000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-685000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1040000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>634000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>790000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>508000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1595000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-1408000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2598000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1126000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1224000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>513000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1707000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>889000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>821000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1261000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-585000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>942000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>678000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>977000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>1220000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>637000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>550000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>666000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>811000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>491000</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3782,251 +3857,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2457000</v>
+      </c>
+      <c r="E35" s="3">
         <v>3832000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3746000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2109000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>595000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1928000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1190000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>331000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1218000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1489000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-5000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1352000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-320000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-303000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-685000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1040000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>634000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>790000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>508000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1595000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-1408000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2598000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1126000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1224000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>513000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1707000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>889000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>821000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1261000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-585000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>942000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>678000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>977000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>1220000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>637000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>550000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>666000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>811000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>491000</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4068,8 +4152,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4111,169 +4196,173 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>697000</v>
+      </c>
+      <c r="E41" s="3">
         <v>678000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>931000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>995000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>840000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>704000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>816000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>599000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>850000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>722000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>860000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>699000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>662000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>736000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>786000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>766000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1130000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>763000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>690000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>656000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>709000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>377000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>370000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>547000</v>
-      </c>
-      <c r="AA41" s="3">
-        <v>338000</v>
       </c>
       <c r="AB41" s="3">
         <v>338000</v>
       </c>
       <c r="AC41" s="3">
+        <v>338000</v>
+      </c>
+      <c r="AD41" s="3">
         <v>587000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>599000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>551000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>499000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>460000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>489000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>450000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>617000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>690000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>482000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>442000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>436000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>389000</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>4705000</v>
+      </c>
+      <c r="E42" s="3">
         <v>4887000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>8743000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>9640000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>6541000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>4537000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>6995000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>5289000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>4319000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>5146000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>3369000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>5137000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>6724000</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
       <c r="Q42" s="3">
         <v>0</v>
       </c>
@@ -4349,127 +4438,133 @@
       <c r="AO42" s="3">
         <v>0</v>
       </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>11648000</v>
+      </c>
+      <c r="E43" s="3">
         <v>11474000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>11745000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>11271000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>11053000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>10614000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>11041000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>10762000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>10573000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>10044000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>10102000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>9713000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>9483000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>9165000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>9150000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>8824000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>8874000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>8364000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>8406000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>8146000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>7921000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>6479000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>6609000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>6367000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>6401000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>6472000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>6558000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>6380000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>6201000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>6154000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>6196000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>5953000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>5856000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>5786000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>5922000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>5693000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>5649000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>5597000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>5799000</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4509,8 +4604,8 @@
       <c r="O44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -4587,50 +4682,53 @@
       <c r="AO44" s="3">
         <v>0</v>
       </c>
+      <c r="AP44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>9216000</v>
+      </c>
+      <c r="E45" s="3">
         <v>9356000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>10277000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>11126000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>14627000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>12765000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>12904000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>9461000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>9416000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>9472000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>9731000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>9728000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>10088000</v>
       </c>
-      <c r="P45" s="3">
-        <v>0</v>
-      </c>
       <c r="Q45" s="3">
         <v>0</v>
       </c>
@@ -4706,50 +4804,53 @@
       <c r="AO45" s="3">
         <v>0</v>
       </c>
+      <c r="AP45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>26266000</v>
+      </c>
+      <c r="E46" s="3">
         <v>26395000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>31696000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>33032000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>33061000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>28620000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>31756000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>26111000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>25158000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>25384000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>24062000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>25277000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>26957000</v>
       </c>
-      <c r="P46" s="3">
-        <v>0</v>
-      </c>
       <c r="Q46" s="3">
         <v>0</v>
       </c>
@@ -4825,311 +4926,320 @@
       <c r="AO46" s="3">
         <v>0</v>
       </c>
+      <c r="AP46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>78445000</v>
+      </c>
+      <c r="E47" s="3">
         <v>76368000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>71750000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>66027000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>65840000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>66468000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>64978000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>63524000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>61724000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>59659000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>57656000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>56095000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>54354000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>61829000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>61006000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>61055000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>61768000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>64701000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>61840000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>62570000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>60076000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>94237000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>91197000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>89637000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>84783000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>88221000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>89158000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>86345000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>84018000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>81136000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>83855000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>83140000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>83195000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>82677000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>82680000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>81203000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>81050000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>81707000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>81038000</v>
       </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>606000</v>
+      </c>
+      <c r="E48" s="3">
         <v>781000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>601000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>619000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>632000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>834000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>714000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>777000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>802000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1022000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>909000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>945000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>971000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1221000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1008000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>975000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>966000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1253000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>965000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1026000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1002000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1057000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1076000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1100000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1123000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1628000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1535000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1519000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1521000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1045000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1032000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1040000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1060000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>1072000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>1067000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>1072000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>1067000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>1065000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>1013000</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>9188000</v>
+      </c>
+      <c r="E49" s="3">
         <v>9839000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>9213000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>9048000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>8902000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>9772000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>8957000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>9614000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>9448000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>10408000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>9326000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>9109000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>8973000</v>
-      </c>
-      <c r="P49" s="3">
-        <v>3502000</v>
       </c>
       <c r="Q49" s="3">
         <v>3502000</v>
       </c>
       <c r="R49" s="3">
+        <v>3502000</v>
+      </c>
+      <c r="S49" s="3">
         <v>3496000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3497000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>3502000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>3389000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3349000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3350000</v>
-      </c>
-      <c r="X49" s="3">
-        <v>2544000</v>
       </c>
       <c r="Y49" s="3">
         <v>2544000</v>
@@ -5141,22 +5251,22 @@
         <v>2544000</v>
       </c>
       <c r="AB49" s="3">
-        <v>2545000</v>
+        <v>2544000</v>
       </c>
       <c r="AC49" s="3">
         <v>2545000</v>
       </c>
       <c r="AD49" s="3">
-        <v>2547000</v>
+        <v>2545000</v>
       </c>
       <c r="AE49" s="3">
         <v>2547000</v>
       </c>
       <c r="AF49" s="3">
+        <v>2547000</v>
+      </c>
+      <c r="AG49" s="3">
         <v>2530000</v>
-      </c>
-      <c r="AG49" s="3">
-        <v>2189000</v>
       </c>
       <c r="AH49" s="3">
         <v>2189000</v>
@@ -5165,25 +5275,28 @@
         <v>2189000</v>
       </c>
       <c r="AJ49" s="3">
+        <v>2189000</v>
+      </c>
+      <c r="AK49" s="3">
         <v>2181000</v>
-      </c>
-      <c r="AK49" s="3">
-        <v>2309000</v>
       </c>
       <c r="AL49" s="3">
         <v>2309000</v>
       </c>
       <c r="AM49" s="3">
+        <v>2309000</v>
+      </c>
+      <c r="AN49" s="3">
         <v>2295000</v>
-      </c>
-      <c r="AN49" s="3">
-        <v>1219000</v>
       </c>
       <c r="AO49" s="3">
         <v>1219000</v>
       </c>
+      <c r="AP49" s="3">
+        <v>1219000</v>
+      </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5301,8 +5414,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5420,74 +5536,77 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>8067000</v>
+      </c>
+      <c r="E52" s="3">
         <v>5023000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5928000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5909000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5453000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4707000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>6386000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>7046000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>6849000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>5505000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>6776000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6997000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6432000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>382000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>492000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>118000</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T52" s="3">
-        <v>0</v>
+      <c r="T52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U52" s="3">
+        <v>0</v>
+      </c>
+      <c r="V52" s="3">
         <v>36803000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>36969000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>36829000</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y52" s="3" t="s">
         <v>8</v>
       </c>
@@ -5503,8 +5622,8 @@
       <c r="AC52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD52" s="3">
-        <v>0</v>
+      <c r="AD52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE52" s="3">
         <v>0</v>
@@ -5539,8 +5658,11 @@
       <c r="AO52" s="3">
         <v>0</v>
       </c>
+      <c r="AP52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5658,127 +5780,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>123972000</v>
+      </c>
+      <c r="E54" s="3">
         <v>119758000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>120402000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>115894000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>115161000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>111617000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>113743000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>108368000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>105241000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>103362000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>101176000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>100514000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>99631000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>97989000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>97676000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>96350000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>97150000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>99440000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>133440000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>132643000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>129811000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>125987000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>122750000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>121266000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>116107000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>119950000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>121073000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>118374000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>115834000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>112249000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>114490000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>113369000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>113289000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>112422000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>113632000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>110865000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>110243000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>108610000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>108537000</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5820,8 +5948,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5863,50 +5992,51 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>42793000</v>
+      </c>
+      <c r="E57" s="3">
         <v>42498000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>44657000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>45796000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>45494000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>43484000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>44470000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>43128000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>41634000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>41211000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>42139000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>41918000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>39977000</v>
       </c>
-      <c r="P57" s="3">
-        <v>0</v>
-      </c>
       <c r="Q57" s="3">
         <v>0</v>
       </c>
@@ -5982,50 +6112,53 @@
       <c r="AO57" s="3">
         <v>0</v>
       </c>
+      <c r="AP57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>551000</v>
+      </c>
+      <c r="E58" s="3">
         <v>618000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>601000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>604000</v>
-      </c>
-      <c r="G58" s="3">
-        <v>601000</v>
       </c>
       <c r="H58" s="3">
         <v>601000</v>
       </c>
       <c r="I58" s="3">
+        <v>601000</v>
+      </c>
+      <c r="J58" s="3">
         <v>9000</v>
-      </c>
-      <c r="J58" s="3">
-        <v>2000</v>
       </c>
       <c r="K58" s="3">
         <v>2000</v>
       </c>
       <c r="L58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="M58" s="3">
         <v>351000</v>
-      </c>
-      <c r="M58" s="3">
-        <v>2000</v>
       </c>
       <c r="N58" s="3">
         <v>2000</v>
       </c>
       <c r="O58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="P58" s="3">
         <v>3000</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
@@ -6101,169 +6234,175 @@
       <c r="AO58" s="3">
         <v>0</v>
       </c>
+      <c r="AP58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>28865000</v>
+      </c>
+      <c r="E59" s="3">
         <v>29085000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>29186000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>28047000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>29543000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>29022000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>29230000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>25932000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>24945000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>24714000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>24527000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>23380000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>22502000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>24843000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>24211000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>23229000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>22429000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>22490000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>21753000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>20853000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>20274000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>49274000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>49140000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>48221000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>46664000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>48503000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>48555000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>48232000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>48055000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>47670000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>48313000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>47936000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>47972000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>48614000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>48542000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>48216000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>48129000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>48185000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>48745000</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>72209000</v>
+      </c>
+      <c r="E60" s="3">
         <v>72201000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>74444000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>74447000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>75638000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>73107000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>73709000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>69062000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>66581000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>66276000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>66668000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>65300000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>62482000</v>
       </c>
-      <c r="P60" s="3">
-        <v>0</v>
-      </c>
       <c r="Q60" s="3">
         <v>0</v>
       </c>
@@ -6339,169 +6478,175 @@
       <c r="AO60" s="3">
         <v>0</v>
       </c>
+      <c r="AP60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6941000</v>
+      </c>
+      <c r="E61" s="3">
         <v>7057000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7489000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7487000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7486000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>7720000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>8083000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>8082000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>7938000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>7857000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>7946000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>7949000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>8452000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>7964000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>7967000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>7970000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>7973000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>7976000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>7980000</v>
-      </c>
-      <c r="V61" s="3">
-        <v>7996000</v>
       </c>
       <c r="W61" s="3">
         <v>7996000</v>
       </c>
       <c r="X61" s="3">
+        <v>7996000</v>
+      </c>
+      <c r="Y61" s="3">
         <v>7825000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>6635000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>6634000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>6633000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>6631000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>6630000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>6628000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>6453000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>6451000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>6450000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>6448000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>6847000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>6350000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>6349000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>6348000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>6346000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>6347000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>5110000</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>13235000</v>
+      </c>
+      <c r="E62" s="3">
         <v>9511000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>10669000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>9955000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>9985000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>9187000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>10902000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>12651000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>12242000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>11270000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>12115000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>11893000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>11324000</v>
       </c>
-      <c r="P62" s="3">
-        <v>0</v>
-      </c>
       <c r="Q62" s="3">
         <v>0</v>
       </c>
@@ -6509,76 +6654,79 @@
         <v>0</v>
       </c>
       <c r="S62" s="3">
+        <v>0</v>
+      </c>
+      <c r="T62" s="3">
         <v>402000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>833000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>33132000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>33533000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>33876000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1355000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>905000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>842000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>331000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1154000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1079000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>997000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>817000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>425000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>660000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>723000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>725000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>782000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>1249000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>1104000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>833000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>487000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>935000</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6696,8 +6844,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6815,8 +6966,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6934,127 +7088,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>92385000</v>
+      </c>
+      <c r="E66" s="3">
         <v>89169000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>92913000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>91889000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>93109000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>90250000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>92905000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>89795000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>86761000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>85732000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>86729000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>85142000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>82258000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>80501000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>80003000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>76235000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>73938000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>74261000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>106711000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>104436000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>102992000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>95770000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>95487000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>94280000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>91934000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>93952000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>94933000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>93898000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>92416000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>90937000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>90857000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>90247000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>90012000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>89871000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>91513000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>89364000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>89085000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>88037000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>87603000</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7096,8 +7256,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7215,8 +7376,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7334,8 +7498,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7373,7 +7540,7 @@
         <v>2001000</v>
       </c>
       <c r="O70" s="3">
-        <v>1970000</v>
+        <v>2001000</v>
       </c>
       <c r="P70" s="3">
         <v>1970000</v>
@@ -7394,13 +7561,13 @@
         <v>1970000</v>
       </c>
       <c r="V70" s="3">
-        <v>2170000</v>
+        <v>1970000</v>
       </c>
       <c r="W70" s="3">
         <v>2170000</v>
       </c>
       <c r="X70" s="3">
-        <v>1970000</v>
+        <v>2170000</v>
       </c>
       <c r="Y70" s="3">
         <v>1970000</v>
@@ -7412,13 +7579,13 @@
         <v>1970000</v>
       </c>
       <c r="AB70" s="3">
+        <v>1970000</v>
+      </c>
+      <c r="AC70" s="3">
         <v>2248000</v>
       </c>
-      <c r="AC70" s="3">
+      <c r="AD70" s="3">
         <v>3052000</v>
-      </c>
-      <c r="AD70" s="3">
-        <v>1930000</v>
       </c>
       <c r="AE70" s="3">
         <v>1930000</v>
@@ -7427,7 +7594,7 @@
         <v>1930000</v>
       </c>
       <c r="AG70" s="3">
-        <v>2303000</v>
+        <v>1930000</v>
       </c>
       <c r="AH70" s="3">
         <v>2303000</v>
@@ -7436,7 +7603,7 @@
         <v>2303000</v>
       </c>
       <c r="AJ70" s="3">
-        <v>1746000</v>
+        <v>2303000</v>
       </c>
       <c r="AK70" s="3">
         <v>1746000</v>
@@ -7453,8 +7620,11 @@
       <c r="AO70" s="3">
         <v>1746000</v>
       </c>
+      <c r="AP70" s="3">
+        <v>1746000</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7572,127 +7742,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>64540000</v>
+      </c>
+      <c r="E72" s="3">
         <v>62393000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>58853000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>55400000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>53586000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>53288000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>51635000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>50718000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>50662000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>49716000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>48491000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>48766000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>50388000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>50970000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>51490000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>52412000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>53688000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>53294000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>52736000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>52464000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>51107000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>52767000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>50336000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>49380000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>48326000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>48074000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>46527000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>45803000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>45148000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>45708000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>46178000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>45508000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>45031000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>43162000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>42125000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>41622000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>41208000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>40678000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>39990000</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7810,8 +7986,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7929,8 +8108,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8048,127 +8230,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>29606000</v>
+      </c>
+      <c r="E76" s="3">
         <v>28609000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>25504000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>22018000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>20054000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>19441000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>18876000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>16592000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>16638000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>15769000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>12592000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>13516000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>15524000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>15518000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>15703000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>18145000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>21242000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>23209000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>24759000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>26037000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>24649000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>28247000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>25293000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>25016000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>22203000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>23750000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>23088000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>22546000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>21488000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>19382000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>21330000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>20819000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>20974000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>20805000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>20373000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>19755000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>19412000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>18827000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>19188000</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8286,251 +8474,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2457000</v>
+      </c>
+      <c r="E81" s="3">
         <v>3832000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3746000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2109000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>595000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1928000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1190000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>331000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1218000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1489000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-5000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1352000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-320000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-303000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-685000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1040000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>634000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>790000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>508000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1595000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-1408000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2598000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1126000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1224000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>513000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1707000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>889000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>821000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1261000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-585000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>942000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>678000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>977000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>1220000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>637000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>550000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>666000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>811000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>491000</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8572,127 +8769,131 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>73000</v>
+      </c>
+      <c r="E83" s="3">
         <v>81000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>69000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>62000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>63000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>82000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>93000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>104000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>96000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>112000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>104000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>129000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>149000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>201000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>194000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>216000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>236000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>268000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>247000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>311000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>260000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>186000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>182000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>163000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>155000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>171000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>159000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>160000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>157000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>135000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>128000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>126000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>122000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>125000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>120000</v>
-      </c>
-      <c r="AL83" s="3">
-        <v>119000</v>
       </c>
       <c r="AM83" s="3">
         <v>119000</v>
       </c>
       <c r="AN83" s="3">
-        <v>97000</v>
+        <v>119000</v>
       </c>
       <c r="AO83" s="3">
         <v>97000</v>
       </c>
+      <c r="AP83" s="3">
+        <v>97000</v>
+      </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8810,8 +9011,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8929,8 +9133,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9048,8 +9255,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9167,8 +9377,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9286,127 +9499,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3562000</v>
+      </c>
+      <c r="E89" s="3">
         <v>2989000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3284000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1873000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1964000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1705000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3201000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2359000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1666000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1225000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1233000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1169000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>601000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>970000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2046000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1673000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>432000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>871000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1329000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1551000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1365000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1319000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1296000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1849000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1027000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1234000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1833000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1348000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>714000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1357000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1728000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1464000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>626000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1100000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1866000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>491000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>857000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>1251000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>1384000</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9448,127 +9667,131 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-40000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-89000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-48000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>1000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-92000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-50000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-63000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-56000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-41000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-71000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-55000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-62000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-79000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-68000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-124000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-98000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-130000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-59000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-89000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-136000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-61000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-73000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-69000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-101000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-65000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-140000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-120000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-93000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-80000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-82000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-67000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-66000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-62000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-83000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-70000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-72000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-74000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-123000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9686,8 +9909,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9805,127 +10031,133 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2627000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1949000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2805000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1208000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1293000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1671000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2685000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2524000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1372000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1105000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-845000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-253000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-796000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-447000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1143000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1119000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>981000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>221000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>446000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-670000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>513000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-2198000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-285000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1026000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>68000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>428000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2093000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-879000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-263000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>737000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1145000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-60000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1251000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-140000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-1127000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>337000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-280000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-1868000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-834000</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9967,25 +10199,26 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>261000</v>
+      </c>
+      <c r="E96" s="3">
         <v>263000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>264000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>265000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>244000</v>
-      </c>
-      <c r="H96" s="3">
-        <v>243000</v>
       </c>
       <c r="I96" s="3">
         <v>243000</v>
@@ -9994,7 +10227,7 @@
         <v>243000</v>
       </c>
       <c r="K96" s="3">
-        <v>233000</v>
+        <v>243000</v>
       </c>
       <c r="L96" s="3">
         <v>233000</v>
@@ -10003,91 +10236,94 @@
         <v>233000</v>
       </c>
       <c r="N96" s="3">
+        <v>233000</v>
+      </c>
+      <c r="O96" s="3">
         <v>235000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>224000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-228000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-232000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-236000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-230000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-235000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-241000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-245000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-164000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-168000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-169000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-172000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-159000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-163000</v>
-      </c>
-      <c r="AC96" s="3">
-        <v>-166000</v>
       </c>
       <c r="AD96" s="3">
         <v>-166000</v>
       </c>
       <c r="AE96" s="3">
+        <v>-166000</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-158000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-159000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-160000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-163000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-132000</v>
-      </c>
-      <c r="AJ96" s="3">
-        <v>-134000</v>
       </c>
       <c r="AK96" s="3">
         <v>-134000</v>
       </c>
       <c r="AL96" s="3">
+        <v>-134000</v>
+      </c>
+      <c r="AM96" s="3">
         <v>-135000</v>
-      </c>
-      <c r="AM96" s="3">
-        <v>-122000</v>
       </c>
       <c r="AN96" s="3">
         <v>-122000</v>
       </c>
       <c r="AO96" s="3">
+        <v>-122000</v>
+      </c>
+      <c r="AP96" s="3">
         <v>-124000</v>
       </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10205,8 +10441,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10324,8 +10563,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10443,127 +10685,133 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-916000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1293000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-634000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-620000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-334000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-260000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-185000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-86000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-166000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-258000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-227000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-879000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>121000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-573000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-883000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-918000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1046000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1175000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1743000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-842000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1480000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>886000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1188000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-614000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1095000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1911000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>248000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-421000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-399000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-2055000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-612000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-1365000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>458000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-1033000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-531000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-788000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-571000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>664000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-607000</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10603,8 +10851,8 @@
       <c r="O101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -10681,123 +10929,129 @@
       <c r="AO101" s="3">
         <v>0</v>
       </c>
+      <c r="AP101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-253000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-155000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>45000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>337000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-226000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>331000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-251000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>128000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-138000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>161000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>37000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-74000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-50000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>20000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-364000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>367000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-83000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>32000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>39000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>398000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>7000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-177000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>209000</v>
       </c>
-      <c r="AA102" s="3">
-        <v>0</v>
-      </c>
       <c r="AB102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="3">
         <v>-249000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-12000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>48000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>52000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>39000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-29000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>39000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-167000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-73000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>208000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>40000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>6000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>47000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-57000</v>
       </c>
     </row>
